--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -798,17 +798,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Stanford University Scholarship for Master’s and PhD Programs for International Students</t>
+          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-stanford-university-scholarship-for-masters-and-phd-programs-for-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
+          <t>Fully Funded Master’s Opportunity at the University of Cambridge 2027 with Funding of Up to GBP 70,000</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-opportunity-at-the-university-of-cambridge-2027-with-funding-of-up-to-gbp-70000</t>
         </is>
       </c>
     </row>
@@ -842,17 +842,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Master’s Opportunity at the University of Cambridge 2027 with Funding of Up to GBP 70,000</t>
+          <t>University of Sydney Scholarship for International Students to Pursue Bachelor’s and Master’s Studies with Funding of Up to AUD 60,000</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-opportunity-at-the-university-of-cambridge-2027-with-funding-of-up-to-gbp-70000</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-sydney-scholarship-for-international-students-to-pursue-bachelors-and-masters-studies-with-funding-of-up-to-aud-60000</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>University of Sydney Scholarship for International Students to Pursue Bachelor’s and Master’s Studies with Funding of Up to AUD 60,000</t>
+          <t>Funded UNSW Scholarship in Australia for Undergraduate and Master’s Studies</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-sydney-scholarship-for-international-students-to-pursue-bachelors-and-masters-studies-with-funding-of-up-to-aud-60000</t>
+          <t>https://www.for9a.com/en/opportunity/funded-unsw-scholarship-australia-undergraduate-masters-studies</t>
         </is>
       </c>
     </row>
@@ -886,17 +886,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Funded UNSW Scholarship in Australia for Undergraduate and Master’s Studies</t>
+          <t>Fully Funded Master’s Scholarship at Peking University 2027 for International Students</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-unsw-scholarship-australia-undergraduate-masters-studies</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-scholarship-at-peking-university-international-students</t>
         </is>
       </c>
     </row>
@@ -908,17 +908,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Master’s Scholarship at Peking University 2027 for International Students</t>
+          <t>Partially Funded Master’s Scholarship in Australia Worth AUD 20,000 for International Students</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-scholarship-at-peking-university-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/partially-funded-masters-scholarship-in-australia-worth-aud-20000</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Partially Funded Master’s Scholarship in Australia Worth AUD 20,000 for International Students</t>
+          <t>Funded Master’s in Canada at the University of Waterloo in Artificial Intelligence and Cybersecurity for International Students</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/partially-funded-masters-scholarship-in-australia-worth-aud-20000</t>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-in-canada-at-the-university-of-waterloo-in-artificial-intelligence-and-cybersecurity-for-international-students</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s in Canada at the University of Waterloo in Artificial Intelligence and Cybersecurity for International Students</t>
+          <t>Al Akhawayn University Scholarship for International Students 2027 to Pursue a Master’s Degree in Morocco</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-in-canada-at-the-university-of-waterloo-in-artificial-intelligence-and-cybersecurity-for-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/al-akhawayn-university-scholarship-for-international-students-pursue-masters-degree-in-morocco</t>
         </is>
       </c>
     </row>
@@ -974,17 +974,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Al Akhawayn University Scholarship for International Students 2027 to Pursue a Master’s Degree in Morocco</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/al-akhawayn-university-scholarship-for-international-students-pursue-masters-degree-in-morocco</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
@@ -996,17 +996,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>Kolding School of Design Scholarship 2027 for a Master’s in Design in Denmark</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>https://www.for9a.com/en/opportunity/kolding-school-of-design-scholarship-for-a-masters-in-design-in-denmark-bwlon</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Kolding School of Design Scholarship 2027 for a Master’s in Design in Denmark</t>
+          <t>IT University of Copenhagen Scholarship 2027 for Master’s Study in Denmark</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/kolding-school-of-design-scholarship-for-a-masters-in-design-in-denmark-bwlon</t>
+          <t>https://www.for9a.com/en/opportunity/it-university-of-copenhagen-scholarship-2027-for-masters-study-in-denmark</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>IT University of Copenhagen Scholarship 2027 for Master’s Study in Denmark</t>
+          <t>Erasmus Mundus CYBERSURE Scholarship 2027 for a Master’s in Cybersecurity with a EUR 1,400 Monthly Stipend</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/it-university-of-copenhagen-scholarship-2027-for-masters-study-in-denmark</t>
+          <t>https://www.for9a.com/en/opportunity/erasmus-mundus-cybersure-scholarship-a-masters-in-cybersecurity-with-monthly-stipend</t>
         </is>
       </c>
     </row>
@@ -1062,17 +1062,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Erasmus Mundus CYBERSURE Scholarship 2027 for a Master’s in Cybersecurity with a EUR 1,400 Monthly Stipend</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/erasmus-mundus-cybersure-scholarship-a-masters-in-cybersecurity-with-monthly-stipend</t>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>LUT University Master’s Scholarships in Finland with Discounts and Funding of up to €10,000</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>https://www.for9a.com/en/opportunity/lut-university-scholarships-international-students-finland</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>LUT University Master’s Scholarships in Finland with Discounts and Funding of up to €10,000</t>
+          <t>University of Jyväskylä Bachelor’s and Master’s Scholarships with Discounts of up to €6,000 in 2027</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/lut-university-scholarships-international-students-finland</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-jyv%C3%A4skyl%C3%A4-bachelors-and-masters-scholarships-with-discounts-of-up-to-6000-in-2027</t>
         </is>
       </c>
     </row>
@@ -1128,17 +1128,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Stanford University Scholarship for Master’s and PhD Programs for International Students</t>
+          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-stanford-university-scholarship-for-masters-and-phd-programs-for-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
         </is>
       </c>
     </row>
@@ -1150,17 +1150,17 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
+          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
         </is>
       </c>
     </row>
@@ -1172,17 +1172,17 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
+          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
+          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
         </is>
       </c>
     </row>
@@ -1194,17 +1194,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
+          <t>Funded PhD Scholarship in New Zealand 2027 at the University of Canterbury for International Students with Funding of up to NZD 32,650</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
+          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-new-zealand-the-university-of-canterbury-for-international-students</t>
         </is>
       </c>
     </row>
@@ -1216,17 +1216,17 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship in New Zealand 2027 at the University of Canterbury for International Students with Funding of up to NZD 32,650</t>
+          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-new-zealand-the-university-of-canterbury-for-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
+          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
         </is>
       </c>
     </row>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
@@ -1282,17 +1282,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
         </is>
       </c>
     </row>
@@ -1304,17 +1304,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>Fully Funded GEMS PhD Scholarship 2026 at Monash University Malaysia with a Monthly Stipend</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-gems-phd-scholarship-2026-at-monash-university-malaysia-with-a-monthly-stipend</t>
         </is>
       </c>
     </row>
@@ -1348,17 +1348,17 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded GEMS PhD Scholarship 2026 at Monash University Malaysia with a Monthly Stipend</t>
+          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-gems-phd-scholarship-2026-at-monash-university-malaysia-with-a-monthly-stipend</t>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
         </is>
       </c>
     </row>
@@ -1370,17 +1370,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
+          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
+          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
+          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
+          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
+          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
+          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
+          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
+          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
         </is>
       </c>
     </row>

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -798,17 +798,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
+          <t>Fully Funded Stanford University Scholarship for Master’s and PhD Programs for International Students</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-stanford-university-scholarship-for-masters-and-phd-programs-for-international-students</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Master’s Opportunity at the University of Cambridge 2027 with Funding of Up to GBP 70,000</t>
+          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-opportunity-at-the-university-of-cambridge-2027-with-funding-of-up-to-gbp-70000</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
         </is>
       </c>
     </row>
@@ -842,17 +842,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>University of Sydney Scholarship for International Students to Pursue Bachelor’s and Master’s Studies with Funding of Up to AUD 60,000</t>
+          <t>Fully Funded Master’s Opportunity at the University of Cambridge 2027 with Funding of Up to GBP 70,000</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-sydney-scholarship-for-international-students-to-pursue-bachelors-and-masters-studies-with-funding-of-up-to-aud-60000</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-opportunity-at-the-university-of-cambridge-2027-with-funding-of-up-to-gbp-70000</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Funded UNSW Scholarship in Australia for Undergraduate and Master’s Studies</t>
+          <t>University of Sydney Scholarship for International Students to Pursue Bachelor’s and Master’s Studies with Funding of Up to AUD 60,000</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-unsw-scholarship-australia-undergraduate-masters-studies</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-sydney-scholarship-for-international-students-to-pursue-bachelors-and-masters-studies-with-funding-of-up-to-aud-60000</t>
         </is>
       </c>
     </row>
@@ -886,17 +886,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Master’s Scholarship at Peking University 2027 for International Students</t>
+          <t>Funded UNSW Scholarship in Australia for Undergraduate and Master’s Studies</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-scholarship-at-peking-university-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/funded-unsw-scholarship-australia-undergraduate-masters-studies</t>
         </is>
       </c>
     </row>
@@ -908,17 +908,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Partially Funded Master’s Scholarship in Australia Worth AUD 20,000 for International Students</t>
+          <t>Fully Funded Master’s Scholarship at Peking University 2027 for International Students</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/partially-funded-masters-scholarship-in-australia-worth-aud-20000</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-scholarship-at-peking-university-international-students</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s in Canada at the University of Waterloo in Artificial Intelligence and Cybersecurity for International Students</t>
+          <t>Partially Funded Master’s Scholarship in Australia Worth AUD 20,000 for International Students</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-in-canada-at-the-university-of-waterloo-in-artificial-intelligence-and-cybersecurity-for-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/partially-funded-masters-scholarship-in-australia-worth-aud-20000</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Al Akhawayn University Scholarship for International Students 2027 to Pursue a Master’s Degree in Morocco</t>
+          <t>Funded Master’s in Canada at the University of Waterloo in Artificial Intelligence and Cybersecurity for International Students</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/al-akhawayn-university-scholarship-for-international-students-pursue-masters-degree-in-morocco</t>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-in-canada-at-the-university-of-waterloo-in-artificial-intelligence-and-cybersecurity-for-international-students</t>
         </is>
       </c>
     </row>
@@ -974,17 +974,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>Al Akhawayn University Scholarship for International Students 2027 to Pursue a Master’s Degree in Morocco</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>https://www.for9a.com/en/opportunity/al-akhawayn-university-scholarship-for-international-students-pursue-masters-degree-in-morocco</t>
         </is>
       </c>
     </row>
@@ -996,17 +996,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Kolding School of Design Scholarship 2027 for a Master’s in Design in Denmark</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/kolding-school-of-design-scholarship-for-a-masters-in-design-in-denmark-bwlon</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>IT University of Copenhagen Scholarship 2027 for Master’s Study in Denmark</t>
+          <t>Kolding School of Design Scholarship 2027 for a Master’s in Design in Denmark</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/it-university-of-copenhagen-scholarship-2027-for-masters-study-in-denmark</t>
+          <t>https://www.for9a.com/en/opportunity/kolding-school-of-design-scholarship-for-a-masters-in-design-in-denmark-bwlon</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Erasmus Mundus CYBERSURE Scholarship 2027 for a Master’s in Cybersecurity with a EUR 1,400 Monthly Stipend</t>
+          <t>IT University of Copenhagen Scholarship 2027 for Master’s Study in Denmark</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/erasmus-mundus-cybersure-scholarship-a-masters-in-cybersecurity-with-monthly-stipend</t>
+          <t>https://www.for9a.com/en/opportunity/it-university-of-copenhagen-scholarship-2027-for-masters-study-in-denmark</t>
         </is>
       </c>
     </row>
@@ -1062,17 +1062,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>Erasmus Mundus CYBERSURE Scholarship 2027 for a Master’s in Cybersecurity with a EUR 1,400 Monthly Stipend</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>https://www.for9a.com/en/opportunity/erasmus-mundus-cybersure-scholarship-a-masters-in-cybersecurity-with-monthly-stipend</t>
         </is>
       </c>
     </row>
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>LUT University Master’s Scholarships in Finland with Discounts and Funding of up to €10,000</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/lut-university-scholarships-international-students-finland</t>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>University of Jyväskylä Bachelor’s and Master’s Scholarships with Discounts of up to €6,000 in 2027</t>
+          <t>LUT University Master’s Scholarships in Finland with Discounts and Funding of up to €10,000</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-jyv%C3%A4skyl%C3%A4-bachelors-and-masters-scholarships-with-discounts-of-up-to-6000-in-2027</t>
+          <t>https://www.for9a.com/en/opportunity/lut-university-scholarships-international-students-finland</t>
         </is>
       </c>
     </row>
@@ -1128,17 +1128,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
+          <t>Fully Funded Stanford University Scholarship for Master’s and PhD Programs for International Students</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-stanford-university-scholarship-for-masters-and-phd-programs-for-international-students</t>
         </is>
       </c>
     </row>
@@ -1150,17 +1150,17 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
+          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
         </is>
       </c>
     </row>
@@ -1172,17 +1172,17 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
+          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
         </is>
       </c>
     </row>
@@ -1194,17 +1194,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship in New Zealand 2027 at the University of Canterbury for International Students with Funding of up to NZD 32,650</t>
+          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-new-zealand-the-university-of-canterbury-for-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
         </is>
       </c>
     </row>
@@ -1216,17 +1216,17 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
+          <t>Funded PhD Scholarship in New Zealand 2027 at the University of Canterbury for International Students with Funding of up to NZD 32,650</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
+          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-new-zealand-the-university-of-canterbury-for-international-students</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
+          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
         </is>
       </c>
     </row>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
         </is>
       </c>
     </row>
@@ -1282,17 +1282,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
@@ -1304,17 +1304,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded GEMS PhD Scholarship 2026 at Monash University Malaysia with a Monthly Stipend</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-gems-phd-scholarship-2026-at-monash-university-malaysia-with-a-monthly-stipend</t>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
@@ -1348,17 +1348,17 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
+          <t>Fully Funded GEMS PhD Scholarship 2026 at Monash University Malaysia with a Monthly Stipend</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-gems-phd-scholarship-2026-at-monash-university-malaysia-with-a-monthly-stipend</t>
         </is>
       </c>
     </row>
@@ -1370,17 +1370,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
+          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
+          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
+          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
+          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
+          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
+          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
+          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
         </is>
       </c>
     </row>

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -429,13 +429,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -456,6 +457,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Deadline</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Link</t>
         </is>
       </c>
@@ -478,6 +484,11 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>Application closes in 39 days</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>https://www.for9a.com/en/opportunity/university-of-sydney-scholarship-for-international-students-to-pursue-bachelors-and-masters-studies-with-funding-of-up-to-aud-60000</t>
         </is>
       </c>
@@ -500,6 +511,11 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>Application closes in 22 days</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>https://www.for9a.com/en/opportunity/funded-unsw-scholarship-australia-undergraduate-masters-studies</t>
         </is>
       </c>
@@ -522,6 +538,11 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>Application closes in 54 days</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>https://www.for9a.com/en/opportunity/undergraduate-scholarship-in-china-2027-with-funding-of-up-to-rmb-187000-per-year</t>
         </is>
       </c>
@@ -544,6 +565,11 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>Application closes in 24 days</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>https://www.for9a.com/en/opportunity/undergraduate-scholarship-in-artificial-intelligence-in-the-uae-for-2027-with-up-to-100-funding</t>
         </is>
       </c>
@@ -566,6 +592,11 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>Application closes in 99 days</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>https://www.for9a.com/en/opportunity/funded-undergraduate-scholarship-american-university-the-us-covering-tuition-housing-meals</t>
         </is>
       </c>
@@ -588,6 +619,11 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>Application closes in 54 days</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>https://www.for9a.com/en/opportunity/bachelors-scholarship-vanderbilt-university-the-usa-for-international</t>
         </is>
       </c>
@@ -610,6 +646,11 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>Application closes in 39 days</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>https://www.for9a.com/en/opportunity/university-of-reading-scholarship-international-students</t>
         </is>
       </c>
@@ -632,6 +673,11 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>https://www.for9a.com/en/opportunity/scholarship-in-new-zealand-for-international-students-worth-nzd-10000</t>
         </is>
       </c>
@@ -654,6 +700,11 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>https://www.for9a.com/en/opportunity/university-of-jyv%C3%A4skyl%C3%A4-bachelors-and-masters-scholarships-with-discounts-of-up-to-6000-in-2027</t>
         </is>
       </c>
@@ -676,6 +727,11 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>https://www.for9a.com/en/opportunity/partially-funded-bachelors-and-masters-scholarships-at-the-university-of-turku-in-finland</t>
         </is>
       </c>
@@ -698,6 +754,11 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>https://www.for9a.com/en/opportunity/university-of-eastern-finland-bachelors-and-masters-scholarships-for-international-students</t>
         </is>
       </c>
@@ -720,6 +781,11 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
         </is>
       </c>
@@ -742,6 +808,11 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>https://www.for9a.com/en/opportunity/kas-scholarships-in-germany-2026-for-masters-phd-and-international-students</t>
         </is>
       </c>
@@ -764,6 +835,11 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>https://www.for9a.com/en/opportunity/najran-university-scholarships-in-saudi-arabia-for-international-students-2026</t>
         </is>
       </c>
@@ -786,6 +862,11 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>https://www.for9a.com/en/opportunity/prince-sultan-university-undergraduate-scholarships-in-saudi-arabia-with-partial-funding</t>
         </is>
       </c>
@@ -798,17 +879,22 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Stanford University Scholarship for Master’s and PhD Programs for International Students</t>
+          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-stanford-university-scholarship-for-masters-and-phd-programs-for-international-students</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
         </is>
       </c>
     </row>
@@ -820,7 +906,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
+          <t>Fully Funded Master’s Opportunity at the University of Cambridge 2027 with Funding of Up to GBP 70,000</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -830,7 +916,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
+          <t>Application closes in 90 days</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-opportunity-at-the-university-of-cambridge-2027-with-funding-of-up-to-gbp-70000</t>
         </is>
       </c>
     </row>
@@ -842,17 +933,22 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Master’s Opportunity at the University of Cambridge 2027 with Funding of Up to GBP 70,000</t>
+          <t>University of Sydney Scholarship for International Students to Pursue Bachelor’s and Master’s Studies with Funding of Up to AUD 60,000</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-opportunity-at-the-university-of-cambridge-2027-with-funding-of-up-to-gbp-70000</t>
+          <t>Application closes in 39 days</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/university-of-sydney-scholarship-for-international-students-to-pursue-bachelors-and-masters-studies-with-funding-of-up-to-aud-60000</t>
         </is>
       </c>
     </row>
@@ -864,7 +960,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>University of Sydney Scholarship for International Students to Pursue Bachelor’s and Master’s Studies with Funding of Up to AUD 60,000</t>
+          <t>Funded UNSW Scholarship in Australia for Undergraduate and Master’s Studies</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -874,7 +970,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-sydney-scholarship-for-international-students-to-pursue-bachelors-and-masters-studies-with-funding-of-up-to-aud-60000</t>
+          <t>Application closes in 22 days</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/funded-unsw-scholarship-australia-undergraduate-masters-studies</t>
         </is>
       </c>
     </row>
@@ -886,17 +987,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Funded UNSW Scholarship in Australia for Undergraduate and Master’s Studies</t>
+          <t>Fully Funded Master’s Scholarship at Peking University 2027 for International Students</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-unsw-scholarship-australia-undergraduate-masters-studies</t>
+          <t>Application closes in 53 days</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-scholarship-at-peking-university-international-students</t>
         </is>
       </c>
     </row>
@@ -908,17 +1014,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Master’s Scholarship at Peking University 2027 for International Students</t>
+          <t>Partially Funded Master’s Scholarship in Australia Worth AUD 20,000 for International Students</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-scholarship-at-peking-university-international-students</t>
+          <t>Application closes in 53 days</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/partially-funded-masters-scholarship-in-australia-worth-aud-20000</t>
         </is>
       </c>
     </row>
@@ -930,17 +1041,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Partially Funded Master’s Scholarship in Australia Worth AUD 20,000 for International Students</t>
+          <t>Funded Master’s in Canada at the University of Waterloo in Artificial Intelligence and Cybersecurity for International Students</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/partially-funded-masters-scholarship-in-australia-worth-aud-20000</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-in-canada-at-the-university-of-waterloo-in-artificial-intelligence-and-cybersecurity-for-international-students</t>
         </is>
       </c>
     </row>
@@ -952,17 +1068,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s in Canada at the University of Waterloo in Artificial Intelligence and Cybersecurity for International Students</t>
+          <t>Al Akhawayn University Scholarship for International Students 2027 to Pursue a Master’s Degree in Morocco</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-in-canada-at-the-university-of-waterloo-in-artificial-intelligence-and-cybersecurity-for-international-students</t>
+          <t>Application closes in 23 days</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/al-akhawayn-university-scholarship-for-international-students-pursue-masters-degree-in-morocco</t>
         </is>
       </c>
     </row>
@@ -974,17 +1095,22 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Al Akhawayn University Scholarship for International Students 2027 to Pursue a Master’s Degree in Morocco</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/al-akhawayn-university-scholarship-for-international-students-pursue-masters-degree-in-morocco</t>
+          <t>Application closes in 12 days</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
@@ -996,17 +1122,22 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>Kolding School of Design Scholarship 2027 for a Master’s in Design in Denmark</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/kolding-school-of-design-scholarship-for-a-masters-in-design-in-denmark-bwlon</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1149,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Kolding School of Design Scholarship 2027 for a Master’s in Design in Denmark</t>
+          <t>IT University of Copenhagen Scholarship 2027 for Master’s Study in Denmark</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1028,7 +1159,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/kolding-school-of-design-scholarship-for-a-masters-in-design-in-denmark-bwlon</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/it-university-of-copenhagen-scholarship-2027-for-masters-study-in-denmark</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1176,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>IT University of Copenhagen Scholarship 2027 for Master’s Study in Denmark</t>
+          <t>Erasmus Mundus CYBERSURE Scholarship 2027 for a Master’s in Cybersecurity with a EUR 1,400 Monthly Stipend</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1050,7 +1186,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/it-university-of-copenhagen-scholarship-2027-for-masters-study-in-denmark</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/erasmus-mundus-cybersure-scholarship-a-masters-in-cybersecurity-with-monthly-stipend</t>
         </is>
       </c>
     </row>
@@ -1062,17 +1203,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Erasmus Mundus CYBERSURE Scholarship 2027 for a Master’s in Cybersecurity with a EUR 1,400 Monthly Stipend</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/erasmus-mundus-cybersure-scholarship-a-masters-in-cybersecurity-with-monthly-stipend</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
@@ -1084,17 +1230,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>LUT University Master’s Scholarships in Finland with Discounts and Funding of up to €10,000</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/lut-university-scholarships-international-students-finland</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1257,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>LUT University Master’s Scholarships in Finland with Discounts and Funding of up to €10,000</t>
+          <t>University of Jyväskylä Bachelor’s and Master’s Scholarships with Discounts of up to €6,000 in 2027</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1116,7 +1267,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/lut-university-scholarships-international-students-finland</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/university-of-jyv%C3%A4skyl%C3%A4-bachelors-and-masters-scholarships-with-discounts-of-up-to-6000-in-2027</t>
         </is>
       </c>
     </row>
@@ -1128,17 +1284,22 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Stanford University Scholarship for Master’s and PhD Programs for International Students</t>
+          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-stanford-university-scholarship-for-masters-and-phd-programs-for-international-students</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
         </is>
       </c>
     </row>
@@ -1150,17 +1311,22 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
+          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
+          <t>Application closes in 54 days</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
         </is>
       </c>
     </row>
@@ -1172,17 +1338,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
+          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
+          <t>Application closes in 17 days</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
         </is>
       </c>
     </row>
@@ -1194,17 +1365,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
+          <t>Funded PhD Scholarship in New Zealand 2027 at the University of Canterbury for International Students with Funding of up to NZD 32,650</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
+          <t>Application closes in 7 days</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-new-zealand-the-university-of-canterbury-for-international-students</t>
         </is>
       </c>
     </row>
@@ -1216,17 +1392,22 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship in New Zealand 2027 at the University of Canterbury for International Students with Funding of up to NZD 32,650</t>
+          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-new-zealand-the-university-of-canterbury-for-international-students</t>
+          <t>Application closes in 38 days</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1419,22 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
+          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
         </is>
       </c>
     </row>
@@ -1260,17 +1446,22 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
+          <t>Application closes in 12 days</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
@@ -1282,17 +1473,22 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
         </is>
       </c>
     </row>
@@ -1304,17 +1500,22 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1527,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>Fully Funded GEMS PhD Scholarship 2026 at Monash University Malaysia with a Monthly Stipend</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1336,7 +1537,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>Application closes in 7 days</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-gems-phd-scholarship-2026-at-monash-university-malaysia-with-a-monthly-stipend</t>
         </is>
       </c>
     </row>
@@ -1348,17 +1554,22 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded GEMS PhD Scholarship 2026 at Monash University Malaysia with a Monthly Stipend</t>
+          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-gems-phd-scholarship-2026-at-monash-university-malaysia-with-a-monthly-stipend</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
         </is>
       </c>
     </row>
@@ -1370,17 +1581,22 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
+          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1608,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
+          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1402,7 +1618,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1635,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
+          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -1424,7 +1645,12 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1662,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
+          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1446,7 +1672,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
         </is>
       </c>
     </row>

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 39 days</t>
+          <t>Application closes in 38 days</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 22 days</t>
+          <t>Application closes in 21 days</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 54 days</t>
+          <t>Application closes in 53 days</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 24 days</t>
+          <t>Application closes in 23 days</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 99 days</t>
+          <t>Application closes in 98 days</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 54 days</t>
+          <t>Application closes in 53 days</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 39 days</t>
+          <t>Application closes in 38 days</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 90 days</t>
+          <t>Application closes in 89 days</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 39 days</t>
+          <t>Application closes in 38 days</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 22 days</t>
+          <t>Application closes in 21 days</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 53 days</t>
+          <t>Application closes in 52 days</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 53 days</t>
+          <t>Application closes in 52 days</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 23 days</t>
+          <t>Application closes in 22 days</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 12 days</t>
+          <t>Application closes in 11 days</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 54 days</t>
+          <t>Application closes in 53 days</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 17 days</t>
+          <t>Application closes in 16 days</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 7 days</t>
+          <t>Application closes in 6 days</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 38 days</t>
+          <t>Application closes in 37 days</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 12 days</t>
+          <t>Application closes in 11 days</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 7 days</t>
+          <t>Application closes in 6 days</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1681,6 +1681,1788 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>bachelor</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Mastercard Foundation Scholars Program at the University of Rwanda 2026/2027 (Fully-funded)</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/10/01/mastercard-foundation-scholars-program-at-the-university-of-rwanda-2026-2027/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>bachelor</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Lester B. Pearson International Student Scholarships 2027</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/08/22/lester-b-pearson-international-student-scholarships-2027/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>bachelor</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SHE-CAN Scholar Program 2026-2027 (Funded)</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/07/28/she-can-scholar-program-2026-2027/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>bachelor</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Girls On Campus She Leads Scholarship 2026 (up to $1,500)</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/07/27/girls-on-campus-she-leads-scholarship-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>bachelor</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>50 Scholarships, Grants and Global Opportunities With Deadline Fast Approaching  – February 24, 2026</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/02/24/50-scholarships-grants-and-global-opportunities-with-deadline-fast-approaching-february-24-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>bachelor</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>12 Global Scholarships Currently Open – December 18,2025</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2025/12/18/12-global-scholarships-currently-open-december-12025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>bachelor</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>40 Grants, Scholarships, Awards, Fellowships, Prizes and Internships Closing Before January 2026</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2025/11/22/40-grants-scholarships-awards-fellowships-prizes-and-internships-closing-before-january-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>bachelor</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>NL Scholarship 2026/2027 to Study in The Netherlands (up to €5,000)</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2025/11/08/nl-scholarship-2026-2027/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>bachelor</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Sterling Bank/Miva Open University Scholarship 2025</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2025/06/19/sterling-bank-miva-open-university-scholarship-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>bachelor</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Mastercard Foundation Scholars Program at Pan-Atlantic University 2025-2026 for Nigerians</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2025/05/27/mastercard-foundation-scholars-program-at-pan-atlantic-university-2025-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>bachelor</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>10 Scholarship Opportunities for Graduate and Postgraduate Studies Currently Open – March 23, 2025</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2025/03/23/10-scholarship-opportunities-for-graduate-and-postgraduate-studies-currently-open-march-23-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>bachelor</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>22 Scholarship Opportunities for Postgraduate and Undergraduate Students Closing Soon – December 27, 2024</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2024/12/27/22-scholarship-opportunities-for-postgraduate-and-undergraduate-students-closing-soon-december-27-2024/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>bachelor</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>VLIRUOS ICP Connect Study Scholarship 2025 (Fully-funded)</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2024/10/31/vliruos-icp-connect-study-scholarship-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>bachelor</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>20 Global Opportunities for Postgraduate &amp; Undergraduate Students Currently Open – October 15, 2024</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2024/10/15/20-global-opportunities-for-postgraduate-undergraduate-students-currently-open-october-15-2024/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>University of Global Health Equity Master of Science in Health Professions Education Program (MSc-HPE) 2027</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/10/07/university-of-global-health-equity-master-of-science-in-health-professions-education-program-2027/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Gates Cambridge Scholarships 2027-2028 (Fully-funded)</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/09/15/gates-cambridge-scholarships-2027-2028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Commonwealth Master’s Scholarships 2027/2028 (Fully-funded)</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/09/09/commonwealth-masters-scholarships-2027-2028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Glendon Chase McCormick Scholarship 2026</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Johns Hopkins SAIS Public Service Scholars – Scholarship Program 2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/06/13/johns-hopkins-sais-public-service-scholars-scholarship-program-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Johns Hopkins SAIS Public Service Fellows – Scholarship Program 2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/06/13/johns-hopkins-sais-public-service-fellows-scholarship-program-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Professor Tagirin A. Fregene Scholarship Fund for Masters in Medical Physics 2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/06/10/professor-tagirin-a-fregene-scholarship-fund-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Rhodes Scholarships 2027 for Study at the University of Oxford (Fully-funded)</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/06/01/rhodes-scholarships-2027/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>66 Grants, Study Abroad, Trainings and Professional Development Opportunities Currently Open – May 9, 2026</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/05/09/66-grants-study-abroad-trainings-and-professional-development-opportunities-currently-open-saturday-may-9-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>IHE Delft Sahel, Middle East and Horn of Africa Scholarships 2026</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/04/24/ihe-delft-sahel-middle-east-and-horn-of-africa-scholarships-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>20 Fully Sponsored, Study Abroad, Mentorship and Other Global Opportunities Currently Open – April 6, 2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/04/06/20-fully-sponsored-study-abroad-mentorship-and-other-global-opportunities-currently-open-april-6-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>50 Scholarships, Grants and Global Opportunities With Deadline Fast Approaching  – February 24, 2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/02/24/50-scholarships-grants-and-global-opportunities-with-deadline-fast-approaching-february-24-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>15 Global Opportunities for Graduate and Postgraduate Studies Currently Open – February 1, 2026</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/02/01/15-global-opportunities-for-graduate-and-postgraduate-studies-currently-open-february-1-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>AHRC Doctoral Landscape Award at the University of Sheffield 2027/2028</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/10/01/ahrc-doctoral-landscape-award-2027-2028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Gates Cambridge Scholarships 2027-2028 (Fully-funded)</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/09/15/gates-cambridge-scholarships-2027-2028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Commonwealth PhD Scholarships 2027/2028 (Fully-Funded)</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/09/09/commonwealth-phd-scholarships-2027-2028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Glendon Chase McCormick Scholarship 2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Mastercard Foundation Doctoral Scholarships 2026-2027 at the University of Toronto</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/05/11/mastercard-foundation-doctoral-scholarships-2026-2027-at-the-university-of-toronto/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>UNU-IIGH Global Health PhD Fellowship Programme 2026</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/03/03/unu-iigh-global-health-phd-fellowship-programme-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>14 Scholarships, Grants and Global Opportunities Open this Valentine Season – February 10, 2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/02/11/14-scholarships-grants-and-global-opportunities-open-this-valentine-season-february-10-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>15 Global Opportunities for Graduate and Postgraduate Studies Currently Open – February 1, 2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/02/01/15-global-opportunities-for-graduate-and-postgraduate-studies-currently-open-february-1-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>85 Scholarships, Contests, Grants and other Global Opportunities Currently Open – January 25, 2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/01/25/85-scholarships-contests-grants-and-other-global-opportunities-currently-open-january-25-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>40 Grants, Scholarships, Awards, Fellowships, Prizes and Internships Closing Before January 2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2025/11/22/40-grants-scholarships-awards-fellowships-prizes-and-internships-closing-before-january-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Commonwealth PhD Scholarships 2026/2027 (Fully-funded)</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2025/09/03/commonwealth-phd-scholarships-2026-2027/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>23 Scholarships and Opportunities for Postgraduate Studies and Students Currently Open –  August 10, 2025</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2025/08/10/__trashed-6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Cambridge Africa Changemakers Scholarship 2025 for PhD students (Fully-funded)</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2025/06/18/cambridge-africa-changemakers-scholarship-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Call for Applications: CLARITY-Africa PhD Scholarship 2025 (Fully-funded)</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2025/03/28/clarity-africa-phd-scholarship-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>10 Scholarship Opportunities for Graduate and Postgraduate Studies Currently Open – March 23, 2025</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2025/03/23/10-scholarship-opportunities-for-graduate-and-postgraduate-studies-currently-open-march-23-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>20 Scholarship Opportunities for Graduate and Postgraduate Studies With  Deadline Fast Approaching- March 11, 2025</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2025/03/11/20-scholarship-opportunities-for-graduates-and-postgraduates-with-deadline-approaching-march-11-2025/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -874,378 +874,378 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
+          <t>Mastercard Foundation Scholars Program at the University of Rwanda 2026/2027 (Fully-funded)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
+          <t>https://opportunitydesk.org/2026/10/01/mastercard-foundation-scholars-program-at-the-university-of-rwanda-2026-2027/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Master’s Opportunity at the University of Cambridge 2027 with Funding of Up to GBP 70,000</t>
+          <t>Lester B. Pearson International Student Scholarships 2027</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 89 days</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-opportunity-at-the-university-of-cambridge-2027-with-funding-of-up-to-gbp-70000</t>
+          <t>https://opportunitydesk.org/2026/08/22/lester-b-pearson-international-student-scholarships-2027/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>University of Sydney Scholarship for International Students to Pursue Bachelor’s and Master’s Studies with Funding of Up to AUD 60,000</t>
+          <t>SHE-CAN Scholar Program 2026-2027 (Funded)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 38 days</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-sydney-scholarship-for-international-students-to-pursue-bachelors-and-masters-studies-with-funding-of-up-to-aud-60000</t>
+          <t>https://opportunitydesk.org/2026/07/28/she-can-scholar-program-2026-2027/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Funded UNSW Scholarship in Australia for Undergraduate and Master’s Studies</t>
+          <t>Girls On Campus She Leads Scholarship 2026 (up to $1,500)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 21 days</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-unsw-scholarship-australia-undergraduate-masters-studies</t>
+          <t>https://opportunitydesk.org/2026/07/27/girls-on-campus-she-leads-scholarship-2026/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Master’s Scholarship at Peking University 2027 for International Students</t>
+          <t>50 Scholarships, Grants and Global Opportunities With Deadline Fast Approaching  – February 24, 2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 52 days</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-scholarship-at-peking-university-international-students</t>
+          <t>https://opportunitydesk.org/2026/02/24/50-scholarships-grants-and-global-opportunities-with-deadline-fast-approaching-february-24-2026/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Partially Funded Master’s Scholarship in Australia Worth AUD 20,000 for International Students</t>
+          <t>12 Global Scholarships Currently Open – December 18,2025</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 52 days</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/partially-funded-masters-scholarship-in-australia-worth-aud-20000</t>
+          <t>https://opportunitydesk.org/2025/12/18/12-global-scholarships-currently-open-december-12025/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s in Canada at the University of Waterloo in Artificial Intelligence and Cybersecurity for International Students</t>
+          <t>40 Grants, Scholarships, Awards, Fellowships, Prizes and Internships Closing Before January 2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-in-canada-at-the-university-of-waterloo-in-artificial-intelligence-and-cybersecurity-for-international-students</t>
+          <t>https://opportunitydesk.org/2025/11/22/40-grants-scholarships-awards-fellowships-prizes-and-internships-closing-before-january-2026/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Al Akhawayn University Scholarship for International Students 2027 to Pursue a Master’s Degree in Morocco</t>
+          <t>NL Scholarship 2026/2027 to Study in The Netherlands (up to €5,000)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 22 days</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/al-akhawayn-university-scholarship-for-international-students-pursue-masters-degree-in-morocco</t>
+          <t>https://opportunitydesk.org/2025/11/08/nl-scholarship-2026-2027/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>Sterling Bank/Miva Open University Scholarship 2025</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 11 days</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>https://opportunitydesk.org/2025/06/19/sterling-bank-miva-open-university-scholarship-2025/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Kolding School of Design Scholarship 2027 for a Master’s in Design in Denmark</t>
+          <t>Mastercard Foundation Scholars Program at Pan-Atlantic University 2025-2026 for Nigerians</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/kolding-school-of-design-scholarship-for-a-masters-in-design-in-denmark-bwlon</t>
+          <t>https://opportunitydesk.org/2025/05/27/mastercard-foundation-scholars-program-at-pan-atlantic-university-2025-2026/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>IT University of Copenhagen Scholarship 2027 for Master’s Study in Denmark</t>
+          <t>10 Scholarship Opportunities for Graduate and Postgraduate Studies Currently Open – March 23, 2025</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/it-university-of-copenhagen-scholarship-2027-for-masters-study-in-denmark</t>
+          <t>https://opportunitydesk.org/2025/03/23/10-scholarship-opportunities-for-graduate-and-postgraduate-studies-currently-open-march-23-2025/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Erasmus Mundus CYBERSURE Scholarship 2027 for a Master’s in Cybersecurity with a EUR 1,400 Monthly Stipend</t>
+          <t>22 Scholarship Opportunities for Postgraduate and Undergraduate Students Closing Soon – December 27, 2024</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/erasmus-mundus-cybersure-scholarship-a-masters-in-cybersecurity-with-monthly-stipend</t>
+          <t>https://opportunitydesk.org/2024/12/27/22-scholarship-opportunities-for-postgraduate-and-undergraduate-students-closing-soon-december-27-2024/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>VLIRUOS ICP Connect Study Scholarship 2025 (Fully-funded)</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>https://opportunitydesk.org/2024/10/31/vliruos-icp-connect-study-scholarship-2025/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>LUT University Master’s Scholarships in Finland with Discounts and Funding of up to €10,000</t>
+          <t>20 Global Opportunities for Postgraduate &amp; Undergraduate Students Currently Open – October 15, 2024</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/lut-university-scholarships-international-students-finland</t>
+          <t>https://opportunitydesk.org/2024/10/15/20-global-opportunities-for-postgraduate-undergraduate-students-currently-open-october-15-2024/</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>University of Jyväskylä Bachelor’s and Master’s Scholarships with Discounts of up to €6,000 in 2027</t>
+          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1272,19 +1272,19 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-jyv%C3%A4skyl%C3%A4-bachelors-and-masters-scholarships-with-discounts-of-up-to-6000-in-2027</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
+          <t>Fully Funded Master’s Opportunity at the University of Cambridge 2027 with Funding of Up to GBP 70,000</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1294,51 +1294,51 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Application closes in 89 days</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-opportunity-at-the-university-of-cambridge-2027-with-funding-of-up-to-gbp-70000</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
+          <t>University of Sydney Scholarship for International Students to Pursue Bachelor’s and Master’s Studies with Funding of Up to AUD 60,000</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 53 days</t>
+          <t>Application closes in 38 days</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-sydney-scholarship-for-international-students-to-pursue-bachelors-and-masters-studies-with-funding-of-up-to-aud-60000</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
+          <t>Funded UNSW Scholarship in Australia for Undergraduate and Master’s Studies</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1348,78 +1348,78 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 16 days</t>
+          <t>Application closes in 21 days</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
+          <t>https://www.for9a.com/en/opportunity/funded-unsw-scholarship-australia-undergraduate-masters-studies</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship in New Zealand 2027 at the University of Canterbury for International Students with Funding of up to NZD 32,650</t>
+          <t>Fully Funded Master’s Scholarship at Peking University 2027 for International Students</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 6 days</t>
+          <t>Application closes in 52 days</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-new-zealand-the-university-of-canterbury-for-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-scholarship-at-peking-university-international-students</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
+          <t>Partially Funded Master’s Scholarship in Australia Worth AUD 20,000 for International Students</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 37 days</t>
+          <t>Application closes in 52 days</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
+          <t>https://www.for9a.com/en/opportunity/partially-funded-masters-scholarship-in-australia-worth-aud-20000</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
+          <t>Funded Master’s in Canada at the University of Waterloo in Artificial Intelligence and Cybersecurity for International Students</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1434,78 +1434,78 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-in-canada-at-the-university-of-waterloo-in-artificial-intelligence-and-cybersecurity-for-international-students</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>Al Akhawayn University Scholarship for International Students 2027 to Pursue a Master’s Degree in Morocco</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 11 days</t>
+          <t>Application closes in 22 days</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>https://www.for9a.com/en/opportunity/al-akhawayn-university-scholarship-for-international-students-pursue-masters-degree-in-morocco</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Application closes in 11 days</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>Kolding School of Design Scholarship 2027 for a Master’s in Design in Denmark</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1515,51 +1515,51 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>https://www.for9a.com/en/opportunity/kolding-school-of-design-scholarship-for-a-masters-in-design-in-denmark-bwlon</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded GEMS PhD Scholarship 2026 at Monash University Malaysia with a Monthly Stipend</t>
+          <t>IT University of Copenhagen Scholarship 2027 for Master’s Study in Denmark</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 6 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-gems-phd-scholarship-2026-at-monash-university-malaysia-with-a-monthly-stipend</t>
+          <t>https://www.for9a.com/en/opportunity/it-university-of-copenhagen-scholarship-2027-for-masters-study-in-denmark</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
+          <t>Erasmus Mundus CYBERSURE Scholarship 2027 for a Master’s in Cybersecurity with a EUR 1,400 Monthly Stipend</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1569,24 +1569,24 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
+          <t>https://www.for9a.com/en/opportunity/erasmus-mundus-cybersure-scholarship-a-masters-in-cybersecurity-with-monthly-stipend</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -1596,24 +1596,24 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
+          <t>LUT University Master’s Scholarships in Finland with Discounts and Funding of up to €10,000</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -1623,24 +1623,24 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
+          <t>https://www.for9a.com/en/opportunity/lut-university-scholarships-international-students-finland</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
+          <t>University of Jyväskylä Bachelor’s and Master’s Scholarships with Discounts of up to €6,000 in 2027</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -1650,46 +1650,46 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-jyv%C3%A4skyl%C3%A4-bachelors-and-masters-scholarships-with-discounts-of-up-to-6000-in-2027</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
+          <t>University of Global Health Equity Master of Science in Health Professions Education Program (MSc-HPE) 2027</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
+          <t>https://opportunitydesk.org/2026/10/07/university-of-global-health-equity-master-of-science-in-health-professions-education-program-2027/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation Scholars Program at the University of Rwanda 2026/2027 (Fully-funded)</t>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -1704,19 +1704,19 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/mastercard-foundation-scholars-program-at-the-university-of-rwanda-2026-2027/</t>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Lester B. Pearson International Student Scholarships 2027</t>
+          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -1731,19 +1731,19 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/22/lester-b-pearson-international-student-scholarships-2027/</t>
+          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SHE-CAN Scholar Program 2026-2027 (Funded)</t>
+          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -1758,19 +1758,19 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/she-can-scholar-program-2026-2027/</t>
+          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Girls On Campus She Leads Scholarship 2026 (up to $1,500)</t>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -1785,19 +1785,19 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/27/girls-on-campus-she-leads-scholarship-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>50 Scholarships, Grants and Global Opportunities With Deadline Fast Approaching  – February 24, 2026</t>
+          <t>Gates Cambridge Scholarships 2027-2028 (Fully-funded)</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -1812,19 +1812,19 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/02/24/50-scholarships-grants-and-global-opportunities-with-deadline-fast-approaching-february-24-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/15/gates-cambridge-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12 Global Scholarships Currently Open – December 18,2025</t>
+          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -1839,19 +1839,19 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/12/18/12-global-scholarships-currently-open-december-12025/</t>
+          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>40 Grants, Scholarships, Awards, Fellowships, Prizes and Internships Closing Before January 2026</t>
+          <t>Commonwealth Master’s Scholarships 2027/2028 (Fully-funded)</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -1866,19 +1866,19 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/11/22/40-grants-scholarships-awards-fellowships-prizes-and-internships-closing-before-january-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/09/commonwealth-masters-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>NL Scholarship 2026/2027 to Study in The Netherlands (up to €5,000)</t>
+          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -1893,19 +1893,19 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/11/08/nl-scholarship-2026-2027/</t>
+          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Sterling Bank/Miva Open University Scholarship 2025</t>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -1920,19 +1920,19 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/06/19/sterling-bank-miva-open-university-scholarship-2025/</t>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation Scholars Program at Pan-Atlantic University 2025-2026 for Nigerians</t>
+          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -1947,19 +1947,19 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/05/27/mastercard-foundation-scholars-program-at-pan-atlantic-university-2025-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10 Scholarship Opportunities for Graduate and Postgraduate Studies Currently Open – March 23, 2025</t>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -1974,19 +1974,19 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/03/23/10-scholarship-opportunities-for-graduate-and-postgraduate-studies-currently-open-march-23-2025/</t>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>22 Scholarship Opportunities for Postgraduate and Undergraduate Students Closing Soon – December 27, 2024</t>
+          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -2001,19 +2001,19 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2024/12/27/22-scholarship-opportunities-for-postgraduate-and-undergraduate-students-closing-soon-december-27-2024/</t>
+          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>VLIRUOS ICP Connect Study Scholarship 2025 (Fully-funded)</t>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2028,19 +2028,19 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2024/10/31/vliruos-icp-connect-study-scholarship-2025/</t>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>20 Global Opportunities for Postgraduate &amp; Undergraduate Students Currently Open – October 15, 2024</t>
+          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2024/10/15/20-global-opportunities-for-postgraduate-undergraduate-students-currently-open-october-15-2024/</t>
+          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>University of Global Health Equity Master of Science in Health Professions Education Program (MSc-HPE) 2027</t>
+          <t>Glendon Chase McCormick Scholarship 2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/07/university-of-global-health-equity-master-of-science-in-health-professions-education-program-2027/</t>
+          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
+          <t>Johns Hopkins SAIS Public Service Scholars – Scholarship Program 2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
+          <t>https://opportunitydesk.org/2026/06/13/johns-hopkins-sais-public-service-scholars-scholarship-program-2026/</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
+          <t>Johns Hopkins SAIS Public Service Fellows – Scholarship Program 2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
+          <t>https://opportunitydesk.org/2026/06/13/johns-hopkins-sais-public-service-fellows-scholarship-program-2026/</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
+          <t>Professor Tagirin A. Fregene Scholarship Fund for Masters in Medical Physics 2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/06/10/professor-tagirin-a-fregene-scholarship-fund-2026/</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
+          <t>Rhodes Scholarships 2027 for Study at the University of Oxford (Fully-funded)</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
+          <t>https://opportunitydesk.org/2026/06/01/rhodes-scholarships-2027/</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Gates Cambridge Scholarships 2027-2028 (Fully-funded)</t>
+          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/15/gates-cambridge-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
+          <t>66 Grants, Study Abroad, Trainings and Professional Development Opportunities Currently Open – May 9, 2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
+          <t>https://opportunitydesk.org/2026/05/09/66-grants-study-abroad-trainings-and-professional-development-opportunities-currently-open-saturday-may-9-2026/</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Commonwealth Master’s Scholarships 2027/2028 (Fully-funded)</t>
+          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/commonwealth-masters-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
+          <t>IHE Delft Sahel, Middle East and Horn of Africa Scholarships 2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
+          <t>https://opportunitydesk.org/2026/04/24/ihe-delft-sahel-middle-east-and-horn-of-africa-scholarships-2026/</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+          <t>20 Fully Sponsored, Study Abroad, Mentorship and Other Global Opportunities Currently Open – April 6, 2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/04/06/20-fully-sponsored-study-abroad-mentorship-and-other-global-opportunities-currently-open-april-6-2026/</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
+          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
+          <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+          <t>50 Scholarships, Grants and Global Opportunities With Deadline Fast Approaching  – February 24, 2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+          <t>https://opportunitydesk.org/2026/02/24/50-scholarships-grants-and-global-opportunities-with-deadline-fast-approaching-february-24-2026/</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
+          <t>15 Global Opportunities for Graduate and Postgraduate Studies Currently Open – February 1, 2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -2406,412 +2406,412 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/02/01/15-global-opportunities-for-graduate-and-postgraduate-studies-currently-open-february-1-2026/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
+          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>Application closes in 53 days</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Glendon Chase McCormick Scholarship 2026</t>
+          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>Application closes in 16 days</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Johns Hopkins SAIS Public Service Scholars – Scholarship Program 2026</t>
+          <t>Funded PhD Scholarship in New Zealand 2027 at the University of Canterbury for International Students with Funding of up to NZD 32,650</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>Application closes in 6 days</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/13/johns-hopkins-sais-public-service-scholars-scholarship-program-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-new-zealand-the-university-of-canterbury-for-international-students</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Johns Hopkins SAIS Public Service Fellows – Scholarship Program 2026</t>
+          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>Application closes in 37 days</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/13/johns-hopkins-sais-public-service-fellows-scholarship-program-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Professor Tagirin A. Fregene Scholarship Fund for Masters in Medical Physics 2026</t>
+          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/10/professor-tagirin-a-fregene-scholarship-fund-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Rhodes Scholarships 2027 for Study at the University of Oxford (Fully-funded)</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>Application closes in 11 days</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/01/rhodes-scholarships-2027/</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
+          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>66 Grants, Study Abroad, Trainings and Professional Development Opportunities Currently Open – May 9, 2026</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/09/66-grants-study-abroad-trainings-and-professional-development-opportunities-currently-open-saturday-may-9-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
+          <t>Fully Funded GEMS PhD Scholarship 2026 at Monash University Malaysia with a Monthly Stipend</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>Application closes in 6 days</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-gems-phd-scholarship-2026-at-monash-university-malaysia-with-a-monthly-stipend</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>IHE Delft Sahel, Middle East and Horn of Africa Scholarships 2026</t>
+          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/04/24/ihe-delft-sahel-middle-east-and-horn-of-africa-scholarships-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>20 Fully Sponsored, Study Abroad, Mentorship and Other Global Opportunities Currently Open – April 6, 2026</t>
+          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/04/06/20-fully-sponsored-study-abroad-mentorship-and-other-global-opportunities-currently-open-april-6-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
+          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>50 Scholarships, Grants and Global Opportunities With Deadline Fast Approaching  – February 24, 2026</t>
+          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/02/24/50-scholarships-grants-and-global-opportunities-with-deadline-fast-approaching-february-24-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>15 Global Opportunities for Graduate and Postgraduate Studies Currently Open – February 1, 2026</t>
+          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/02/01/15-global-opportunities-for-graduate-and-postgraduate-studies-currently-open-february-1-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
         </is>
       </c>
     </row>

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -874,378 +874,378 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
+          <t>Mastercard Foundation Scholars Program at the University of Rwanda 2026/2027 (Fully-funded)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
+          <t>https://opportunitydesk.org/2026/10/01/mastercard-foundation-scholars-program-at-the-university-of-rwanda-2026-2027/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Master’s Opportunity at the University of Cambridge 2027 with Funding of Up to GBP 70,000</t>
+          <t>Lester B. Pearson International Student Scholarships 2027</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 89 days</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-opportunity-at-the-university-of-cambridge-2027-with-funding-of-up-to-gbp-70000</t>
+          <t>https://opportunitydesk.org/2026/08/22/lester-b-pearson-international-student-scholarships-2027/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>University of Sydney Scholarship for International Students to Pursue Bachelor’s and Master’s Studies with Funding of Up to AUD 60,000</t>
+          <t>SHE-CAN Scholar Program 2026-2027 (Funded)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 38 days</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-sydney-scholarship-for-international-students-to-pursue-bachelors-and-masters-studies-with-funding-of-up-to-aud-60000</t>
+          <t>https://opportunitydesk.org/2026/07/28/she-can-scholar-program-2026-2027/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Funded UNSW Scholarship in Australia for Undergraduate and Master’s Studies</t>
+          <t>Girls On Campus She Leads Scholarship 2026 (up to $1,500)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 21 days</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-unsw-scholarship-australia-undergraduate-masters-studies</t>
+          <t>https://opportunitydesk.org/2026/07/27/girls-on-campus-she-leads-scholarship-2026/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Master’s Scholarship at Peking University 2027 for International Students</t>
+          <t>50 Scholarships, Grants and Global Opportunities With Deadline Fast Approaching  – February 24, 2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 52 days</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-scholarship-at-peking-university-international-students</t>
+          <t>https://opportunitydesk.org/2026/02/24/50-scholarships-grants-and-global-opportunities-with-deadline-fast-approaching-february-24-2026/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Partially Funded Master’s Scholarship in Australia Worth AUD 20,000 for International Students</t>
+          <t>12 Global Scholarships Currently Open – December 18,2025</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 52 days</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/partially-funded-masters-scholarship-in-australia-worth-aud-20000</t>
+          <t>https://opportunitydesk.org/2025/12/18/12-global-scholarships-currently-open-december-12025/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s in Canada at the University of Waterloo in Artificial Intelligence and Cybersecurity for International Students</t>
+          <t>40 Grants, Scholarships, Awards, Fellowships, Prizes and Internships Closing Before January 2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-in-canada-at-the-university-of-waterloo-in-artificial-intelligence-and-cybersecurity-for-international-students</t>
+          <t>https://opportunitydesk.org/2025/11/22/40-grants-scholarships-awards-fellowships-prizes-and-internships-closing-before-january-2026/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Al Akhawayn University Scholarship for International Students 2027 to Pursue a Master’s Degree in Morocco</t>
+          <t>NL Scholarship 2026/2027 to Study in The Netherlands (up to €5,000)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 22 days</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/al-akhawayn-university-scholarship-for-international-students-pursue-masters-degree-in-morocco</t>
+          <t>https://opportunitydesk.org/2025/11/08/nl-scholarship-2026-2027/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>Sterling Bank/Miva Open University Scholarship 2025</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 11 days</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>https://opportunitydesk.org/2025/06/19/sterling-bank-miva-open-university-scholarship-2025/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Kolding School of Design Scholarship 2027 for a Master’s in Design in Denmark</t>
+          <t>Mastercard Foundation Scholars Program at Pan-Atlantic University 2025-2026 for Nigerians</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/kolding-school-of-design-scholarship-for-a-masters-in-design-in-denmark-bwlon</t>
+          <t>https://opportunitydesk.org/2025/05/27/mastercard-foundation-scholars-program-at-pan-atlantic-university-2025-2026/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>IT University of Copenhagen Scholarship 2027 for Master’s Study in Denmark</t>
+          <t>10 Scholarship Opportunities for Graduate and Postgraduate Studies Currently Open – March 23, 2025</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/it-university-of-copenhagen-scholarship-2027-for-masters-study-in-denmark</t>
+          <t>https://opportunitydesk.org/2025/03/23/10-scholarship-opportunities-for-graduate-and-postgraduate-studies-currently-open-march-23-2025/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Erasmus Mundus CYBERSURE Scholarship 2027 for a Master’s in Cybersecurity with a EUR 1,400 Monthly Stipend</t>
+          <t>22 Scholarship Opportunities for Postgraduate and Undergraduate Students Closing Soon – December 27, 2024</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/erasmus-mundus-cybersure-scholarship-a-masters-in-cybersecurity-with-monthly-stipend</t>
+          <t>https://opportunitydesk.org/2024/12/27/22-scholarship-opportunities-for-postgraduate-and-undergraduate-students-closing-soon-december-27-2024/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>VLIRUOS ICP Connect Study Scholarship 2025 (Fully-funded)</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>https://opportunitydesk.org/2024/10/31/vliruos-icp-connect-study-scholarship-2025/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>LUT University Master’s Scholarships in Finland with Discounts and Funding of up to €10,000</t>
+          <t>20 Global Opportunities for Postgraduate &amp; Undergraduate Students Currently Open – October 15, 2024</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/lut-university-scholarships-international-students-finland</t>
+          <t>https://opportunitydesk.org/2024/10/15/20-global-opportunities-for-postgraduate-undergraduate-students-currently-open-october-15-2024/</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>University of Jyväskylä Bachelor’s and Master’s Scholarships with Discounts of up to €6,000 in 2027</t>
+          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1272,19 +1272,19 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-jyv%C3%A4skyl%C3%A4-bachelors-and-masters-scholarships-with-discounts-of-up-to-6000-in-2027</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
+          <t>Fully Funded Master’s Opportunity at the University of Cambridge 2027 with Funding of Up to GBP 70,000</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1294,51 +1294,51 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Application closes in 89 days</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-opportunity-at-the-university-of-cambridge-2027-with-funding-of-up-to-gbp-70000</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
+          <t>Fully Funded Master’s Scholarship at Peking University 2027 for International Students</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 53 days</t>
+          <t>Application closes in 52 days</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-scholarship-at-peking-university-international-students</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
+          <t>Partially Funded Master’s Scholarship in Australia Worth AUD 20,000 for International Students</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1348,137 +1348,137 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 16 days</t>
+          <t>Application closes in 52 days</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
+          <t>https://www.for9a.com/en/opportunity/partially-funded-masters-scholarship-in-australia-worth-aud-20000</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship in New Zealand 2027 at the University of Canterbury for International Students with Funding of up to NZD 32,650</t>
+          <t>Funded Master’s in Canada at the University of Waterloo in Artificial Intelligence and Cybersecurity for International Students</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 6 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-new-zealand-the-university-of-canterbury-for-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-in-canada-at-the-university-of-waterloo-in-artificial-intelligence-and-cybersecurity-for-international-students</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
+          <t>Al Akhawayn University Scholarship for International Students 2027 to Pursue a Master’s Degree in Morocco</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 37 days</t>
+          <t>Application closes in 22 days</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
+          <t>https://www.for9a.com/en/opportunity/al-akhawayn-university-scholarship-for-international-students-pursue-masters-degree-in-morocco</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Application closes in 11 days</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>Kolding School of Design Scholarship 2027 for a Master’s in Design in Denmark</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 11 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>https://www.for9a.com/en/opportunity/kolding-school-of-design-scholarship-for-a-masters-in-design-in-denmark-bwlon</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
+          <t>IT University of Copenhagen Scholarship 2027 for Master’s Study in Denmark</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1488,24 +1488,24 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
+          <t>https://www.for9a.com/en/opportunity/it-university-of-copenhagen-scholarship-2027-for-masters-study-in-denmark</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>Erasmus Mundus CYBERSURE Scholarship 2027 for a Master’s in Cybersecurity with a EUR 1,400 Monthly Stipend</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1515,19 +1515,19 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>https://www.for9a.com/en/opportunity/erasmus-mundus-cybersure-scholarship-a-masters-in-cybersecurity-with-monthly-stipend</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded GEMS PhD Scholarship 2026 at Monash University Malaysia with a Monthly Stipend</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1537,29 +1537,29 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 6 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-gems-phd-scholarship-2026-at-monash-university-malaysia-with-a-monthly-stipend</t>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
+          <t>LUT University Master’s Scholarships in Finland with Discounts and Funding of up to €10,000</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1569,115 +1569,1330 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
+          <t>https://www.for9a.com/en/opportunity/lut-university-scholarships-international-students-finland</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
+          <t>University of Global Health Equity Master of Science in Health Professions Education Program (MSc-HPE) 2027</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
+          <t>https://opportunitydesk.org/2026/10/07/university-of-global-health-equity-master-of-science-in-health-professions-education-program-2027/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
+          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
+          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Gates Cambridge Scholarships 2027-2028 (Fully-funded)</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/09/15/gates-cambridge-scholarships-2027-2028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Commonwealth Master’s Scholarships 2027/2028 (Fully-funded)</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/09/09/commonwealth-masters-scholarships-2027-2028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Glendon Chase McCormick Scholarship 2026</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Johns Hopkins SAIS Public Service Scholars – Scholarship Program 2026</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/06/13/johns-hopkins-sais-public-service-scholars-scholarship-program-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Johns Hopkins SAIS Public Service Fellows – Scholarship Program 2026</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/06/13/johns-hopkins-sais-public-service-fellows-scholarship-program-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Professor Tagirin A. Fregene Scholarship Fund for Masters in Medical Physics 2026</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/06/10/professor-tagirin-a-fregene-scholarship-fund-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Rhodes Scholarships 2027 for Study at the University of Oxford (Fully-funded)</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/06/01/rhodes-scholarships-2027/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>66 Grants, Study Abroad, Trainings and Professional Development Opportunities Currently Open – May 9, 2026</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/05/09/66-grants-study-abroad-trainings-and-professional-development-opportunities-currently-open-saturday-may-9-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>IHE Delft Sahel, Middle East and Horn of Africa Scholarships 2026</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/04/24/ihe-delft-sahel-middle-east-and-horn-of-africa-scholarships-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>20 Fully Sponsored, Study Abroad, Mentorship and Other Global Opportunities Currently Open – April 6, 2026</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/04/06/20-fully-sponsored-study-abroad-mentorship-and-other-global-opportunities-currently-open-april-6-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>15 Global Opportunities for Graduate and Postgraduate Studies Currently Open – February 1, 2026</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/02/01/15-global-opportunities-for-graduate-and-postgraduate-studies-currently-open-february-1-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
           <t>phd</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Application closes in 53 days</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Application closes in 16 days</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Funded PhD Scholarship in New Zealand 2027 at the University of Canterbury for International Students with Funding of up to NZD 32,650</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Application closes in 6 days</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-new-zealand-the-university-of-canterbury-for-international-students</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Application closes in 37 days</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Fully Funded GEMS PhD Scholarship 2026 at Monash University Malaysia with a Monthly Stipend</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Application closes in 6 days</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-gems-phd-scholarship-2026-at-monash-university-malaysia-with-a-monthly-stipend</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>AHRC Doctoral Landscape Award at the University of Sheffield 2027/2028</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/10/01/ahrc-doctoral-landscape-award-2027-2028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Commonwealth PhD Scholarships 2027/2028 (Fully-Funded)</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/09/09/commonwealth-phd-scholarships-2027-2028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Mastercard Foundation Doctoral Scholarships 2026-2027 at the University of Toronto</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/05/11/mastercard-foundation-doctoral-scholarships-2026-2027-at-the-university-of-toronto/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>UNU-IIGH Global Health PhD Fellowship Programme 2026</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/03/03/unu-iigh-global-health-phd-fellowship-programme-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>14 Scholarships, Grants and Global Opportunities Open this Valentine Season – February 10, 2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/02/11/14-scholarships-grants-and-global-opportunities-open-this-valentine-season-february-10-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>85 Scholarships, Contests, Grants and other Global Opportunities Currently Open – January 25, 2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/01/25/85-scholarships-contests-grants-and-other-global-opportunities-currently-open-january-25-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Commonwealth PhD Scholarships 2026/2027 (Fully-funded)</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2025/09/03/commonwealth-phd-scholarships-2026-2027/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>23 Scholarships and Opportunities for Postgraduate Studies and Students Currently Open –  August 10, 2025</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2025/08/10/__trashed-6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Cambridge Africa Changemakers Scholarship 2025 for PhD students (Fully-funded)</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2025/06/18/cambridge-africa-changemakers-scholarship-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Call for Applications: CLARITY-Africa PhD Scholarship 2025 (Fully-funded)</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2025/03/28/clarity-africa-phd-scholarship-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>20 Scholarship Opportunities for Graduate and Postgraduate Studies With  Deadline Fast Approaching- March 11, 2025</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2025/03/11/20-scholarship-opportunities-for-graduates-and-postgraduates-with-deadline-approaching-march-11-2025/</t>
         </is>
       </c>
     </row>

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1311,22 +1311,22 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Master’s Scholarship at Peking University 2027 for International Students</t>
+          <t>University of Sydney Scholarship for International Students to Pursue Bachelor’s and Master’s Studies with Funding of Up to AUD 60,000</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 52 days</t>
+          <t>Application closes in 38 days</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-scholarship-at-peking-university-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-sydney-scholarship-for-international-students-to-pursue-bachelors-and-masters-studies-with-funding-of-up-to-aud-60000</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Partially Funded Master’s Scholarship in Australia Worth AUD 20,000 for International Students</t>
+          <t>Funded UNSW Scholarship in Australia for Undergraduate and Master’s Studies</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 52 days</t>
+          <t>Application closes in 21 days</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/partially-funded-masters-scholarship-in-australia-worth-aud-20000</t>
+          <t>https://www.for9a.com/en/opportunity/funded-unsw-scholarship-australia-undergraduate-masters-studies</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s in Canada at the University of Waterloo in Artificial Intelligence and Cybersecurity for International Students</t>
+          <t>Fully Funded Master’s Scholarship at Peking University 2027 for International Students</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Application closes in 52 days</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-in-canada-at-the-university-of-waterloo-in-artificial-intelligence-and-cybersecurity-for-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-scholarship-at-peking-university-international-students</t>
         </is>
       </c>
     </row>
@@ -1392,22 +1392,22 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Al Akhawayn University Scholarship for International Students 2027 to Pursue a Master’s Degree in Morocco</t>
+          <t>Partially Funded Master’s Scholarship in Australia Worth AUD 20,000 for International Students</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 22 days</t>
+          <t>Application closes in 52 days</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/al-akhawayn-university-scholarship-for-international-students-pursue-masters-degree-in-morocco</t>
+          <t>https://www.for9a.com/en/opportunity/partially-funded-masters-scholarship-in-australia-worth-aud-20000</t>
         </is>
       </c>
     </row>
@@ -1419,22 +1419,22 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>Funded Master’s in Canada at the University of Waterloo in Artificial Intelligence and Cybersecurity for International Students</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 11 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-in-canada-at-the-university-of-waterloo-in-artificial-intelligence-and-cybersecurity-for-international-students</t>
         </is>
       </c>
     </row>
@@ -1446,22 +1446,22 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Kolding School of Design Scholarship 2027 for a Master’s in Design in Denmark</t>
+          <t>Al Akhawayn University Scholarship for International Students 2027 to Pursue a Master’s Degree in Morocco</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Application closes in 22 days</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/kolding-school-of-design-scholarship-for-a-masters-in-design-in-denmark-bwlon</t>
+          <t>https://www.for9a.com/en/opportunity/al-akhawayn-university-scholarship-for-international-students-pursue-masters-degree-in-morocco</t>
         </is>
       </c>
     </row>
@@ -1473,22 +1473,22 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>IT University of Copenhagen Scholarship 2027 for Master’s Study in Denmark</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Application closes in 11 days</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/it-university-of-copenhagen-scholarship-2027-for-masters-study-in-denmark</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Erasmus Mundus CYBERSURE Scholarship 2027 for a Master’s in Cybersecurity with a EUR 1,400 Monthly Stipend</t>
+          <t>Kolding School of Design Scholarship 2027 for a Master’s in Design in Denmark</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/erasmus-mundus-cybersure-scholarship-a-masters-in-cybersecurity-with-monthly-stipend</t>
+          <t>https://www.for9a.com/en/opportunity/kolding-school-of-design-scholarship-for-a-masters-in-design-in-denmark-bwlon</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>IT University of Copenhagen Scholarship 2027 for Master’s Study in Denmark</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>https://www.for9a.com/en/opportunity/it-university-of-copenhagen-scholarship-2027-for-masters-study-in-denmark</t>
         </is>
       </c>
     </row>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>LUT University Master’s Scholarships in Finland with Discounts and Funding of up to €10,000</t>
+          <t>Erasmus Mundus CYBERSURE Scholarship 2027 for a Master’s in Cybersecurity with a EUR 1,400 Monthly Stipend</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/lut-university-scholarships-international-students-finland</t>
+          <t>https://www.for9a.com/en/opportunity/erasmus-mundus-cybersure-scholarship-a-masters-in-cybersecurity-with-monthly-stipend</t>
         </is>
       </c>
     </row>
@@ -1581,22 +1581,22 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>University of Global Health Equity Master of Science in Health Professions Education Program (MSc-HPE) 2027</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/07/university-of-global-health-equity-master-of-science-in-health-professions-education-program-2027/</t>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
@@ -1608,22 +1608,22 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
+          <t>LUT University Master’s Scholarships in Finland with Discounts and Funding of up to €10,000</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/lut-university-scholarships-international-students-finland</t>
         </is>
       </c>
     </row>
@@ -1635,22 +1635,22 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
+          <t>University of Jyväskylä Bachelor’s and Master’s Scholarships with Discounts of up to €6,000 in 2027</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-jyv%C3%A4skyl%C3%A4-bachelors-and-masters-scholarships-with-discounts-of-up-to-6000-in-2027</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
+          <t>University of Global Health Equity Master of Science in Health Professions Education Program (MSc-HPE) 2027</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/10/07/university-of-global-health-equity-master-of-science-in-health-professions-education-program-2027/</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Gates Cambridge Scholarships 2027-2028 (Fully-funded)</t>
+          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/15/gates-cambridge-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
+          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
+          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Commonwealth Master’s Scholarships 2027/2028 (Fully-funded)</t>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/commonwealth-masters-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
+          <t>Gates Cambridge Scholarships 2027-2028 (Fully-funded)</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
+          <t>https://opportunitydesk.org/2026/09/15/gates-cambridge-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
+          <t>Commonwealth Master’s Scholarships 2027/2028 (Fully-funded)</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/09/commonwealth-masters-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Glendon Chase McCormick Scholarship 2026</t>
+          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Johns Hopkins SAIS Public Service Scholars – Scholarship Program 2026</t>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/13/johns-hopkins-sais-public-service-scholars-scholarship-program-2026/</t>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Johns Hopkins SAIS Public Service Fellows – Scholarship Program 2026</t>
+          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/13/johns-hopkins-sais-public-service-fellows-scholarship-program-2026/</t>
+          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Professor Tagirin A. Fregene Scholarship Fund for Masters in Medical Physics 2026</t>
+          <t>Glendon Chase McCormick Scholarship 2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/10/professor-tagirin-a-fregene-scholarship-fund-2026/</t>
+          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Rhodes Scholarships 2027 for Study at the University of Oxford (Fully-funded)</t>
+          <t>Johns Hopkins SAIS Public Service Scholars – Scholarship Program 2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/01/rhodes-scholarships-2027/</t>
+          <t>https://opportunitydesk.org/2026/06/13/johns-hopkins-sais-public-service-scholars-scholarship-program-2026/</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
+          <t>Johns Hopkins SAIS Public Service Fellows – Scholarship Program 2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
+          <t>https://opportunitydesk.org/2026/06/13/johns-hopkins-sais-public-service-fellows-scholarship-program-2026/</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>66 Grants, Study Abroad, Trainings and Professional Development Opportunities Currently Open – May 9, 2026</t>
+          <t>Professor Tagirin A. Fregene Scholarship Fund for Masters in Medical Physics 2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/09/66-grants-study-abroad-trainings-and-professional-development-opportunities-currently-open-saturday-may-9-2026/</t>
+          <t>https://opportunitydesk.org/2026/06/10/professor-tagirin-a-fregene-scholarship-fund-2026/</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
+          <t>Rhodes Scholarships 2027 for Study at the University of Oxford (Fully-funded)</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
+          <t>https://opportunitydesk.org/2026/06/01/rhodes-scholarships-2027/</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>IHE Delft Sahel, Middle East and Horn of Africa Scholarships 2026</t>
+          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/04/24/ihe-delft-sahel-middle-east-and-horn-of-africa-scholarships-2026/</t>
+          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>20 Fully Sponsored, Study Abroad, Mentorship and Other Global Opportunities Currently Open – April 6, 2026</t>
+          <t>66 Grants, Study Abroad, Trainings and Professional Development Opportunities Currently Open – May 9, 2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/04/06/20-fully-sponsored-study-abroad-mentorship-and-other-global-opportunities-currently-open-april-6-2026/</t>
+          <t>https://opportunitydesk.org/2026/05/09/66-grants-study-abroad-trainings-and-professional-development-opportunities-currently-open-saturday-may-9-2026/</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
+          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
+          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15 Global Opportunities for Graduate and Postgraduate Studies Currently Open – February 1, 2026</t>
+          <t>IHE Delft Sahel, Middle East and Horn of Africa Scholarships 2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -2298,115 +2298,115 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/02/01/15-global-opportunities-for-graduate-and-postgraduate-studies-currently-open-february-1-2026/</t>
+          <t>https://opportunitydesk.org/2026/04/24/ihe-delft-sahel-middle-east-and-horn-of-africa-scholarships-2026/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
+          <t>20 Fully Sponsored, Study Abroad, Mentorship and Other Global Opportunities Currently Open – April 6, 2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 53 days</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
+          <t>https://opportunitydesk.org/2026/04/06/20-fully-sponsored-study-abroad-mentorship-and-other-global-opportunities-currently-open-april-6-2026/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
+          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 16 days</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
+          <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship in New Zealand 2027 at the University of Canterbury for International Students with Funding of up to NZD 32,650</t>
+          <t>50 Scholarships, Grants and Global Opportunities With Deadline Fast Approaching  – February 24, 2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 6 days</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-new-zealand-the-university-of-canterbury-for-international-students</t>
+          <t>https://opportunitydesk.org/2026/02/24/50-scholarships-grants-and-global-opportunities-with-deadline-fast-approaching-february-24-2026/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
+          <t>15 Global Opportunities for Graduate and Postgraduate Studies Currently Open – February 1, 2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 37 days</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
+          <t>https://opportunitydesk.org/2026/02/01/15-global-opportunities-for-graduate-and-postgraduate-studies-currently-open-february-1-2026/</t>
         </is>
       </c>
     </row>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
+          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
         </is>
       </c>
     </row>
@@ -2445,22 +2445,22 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
+          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Application closes in 53 days</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
         </is>
       </c>
     </row>
@@ -2472,22 +2472,22 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded GEMS PhD Scholarship 2026 at Monash University Malaysia with a Monthly Stipend</t>
+          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 6 days</t>
+          <t>Application closes in 16 days</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-gems-phd-scholarship-2026-at-monash-university-malaysia-with-a-monthly-stipend</t>
+          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
         </is>
       </c>
     </row>
@@ -2499,22 +2499,22 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
+          <t>Funded PhD Scholarship in New Zealand 2027 at the University of Canterbury for International Students with Funding of up to NZD 32,650</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Application closes in 6 days</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
+          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-new-zealand-the-university-of-canterbury-for-international-students</t>
         </is>
       </c>
     </row>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
+          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Application closes in 37 days</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
+          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
         </is>
       </c>
     </row>
@@ -2580,22 +2580,22 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Application closes in 11 days</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
@@ -2607,22 +2607,22 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>AHRC Doctoral Landscape Award at the University of Sheffield 2027/2028</t>
+          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/ahrc-doctoral-landscape-award-2027-2028/</t>
+          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
         </is>
       </c>
     </row>
@@ -2634,22 +2634,22 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Commonwealth PhD Scholarships 2027/2028 (Fully-Funded)</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/commonwealth-phd-scholarships-2027-2028/</t>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
@@ -2661,22 +2661,22 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation Doctoral Scholarships 2026-2027 at the University of Toronto</t>
+          <t>Fully Funded GEMS PhD Scholarship 2026 at Monash University Malaysia with a Monthly Stipend</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>Application closes in 6 days</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/11/mastercard-foundation-doctoral-scholarships-2026-2027-at-the-university-of-toronto/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-gems-phd-scholarship-2026-at-monash-university-malaysia-with-a-monthly-stipend</t>
         </is>
       </c>
     </row>
@@ -2688,22 +2688,22 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>UNU-IIGH Global Health PhD Fellowship Programme 2026</t>
+          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/03/03/unu-iigh-global-health-phd-fellowship-programme-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
         </is>
       </c>
     </row>
@@ -2715,22 +2715,22 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>14 Scholarships, Grants and Global Opportunities Open this Valentine Season – February 10, 2026</t>
+          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/02/11/14-scholarships-grants-and-global-opportunities-open-this-valentine-season-february-10-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -2742,22 +2742,22 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>85 Scholarships, Contests, Grants and other Global Opportunities Currently Open – January 25, 2026</t>
+          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/01/25/85-scholarships-contests-grants-and-other-global-opportunities-currently-open-january-25-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -2769,22 +2769,22 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Commonwealth PhD Scholarships 2026/2027 (Fully-funded)</t>
+          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/09/03/commonwealth-phd-scholarships-2026-2027/</t>
+          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
         </is>
       </c>
     </row>
@@ -2796,22 +2796,22 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>23 Scholarships and Opportunities for Postgraduate Studies and Students Currently Open –  August 10, 2025</t>
+          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/08/10/__trashed-6/</t>
+          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Cambridge Africa Changemakers Scholarship 2025 for PhD students (Fully-funded)</t>
+          <t>AHRC Doctoral Landscape Award at the University of Sheffield 2027/2028</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/06/18/cambridge-africa-changemakers-scholarship-2025/</t>
+          <t>https://opportunitydesk.org/2026/10/01/ahrc-doctoral-landscape-award-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Call for Applications: CLARITY-Africa PhD Scholarship 2025 (Fully-funded)</t>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/03/28/clarity-africa-phd-scholarship-2025/</t>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
         </is>
       </c>
     </row>
@@ -2877,20 +2877,587 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Gates Cambridge Scholarships 2027-2028 (Fully-funded)</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/09/15/gates-cambridge-scholarships-2027-2028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Commonwealth PhD Scholarships 2027/2028 (Fully-Funded)</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/09/09/commonwealth-phd-scholarships-2027-2028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Glendon Chase McCormick Scholarship 2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Mastercard Foundation Doctoral Scholarships 2026-2027 at the University of Toronto</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/05/11/mastercard-foundation-doctoral-scholarships-2026-2027-at-the-university-of-toronto/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>UNU-IIGH Global Health PhD Fellowship Programme 2026</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/03/03/unu-iigh-global-health-phd-fellowship-programme-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>14 Scholarships, Grants and Global Opportunities Open this Valentine Season – February 10, 2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/02/11/14-scholarships-grants-and-global-opportunities-open-this-valentine-season-february-10-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>15 Global Opportunities for Graduate and Postgraduate Studies Currently Open – February 1, 2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/02/01/15-global-opportunities-for-graduate-and-postgraduate-studies-currently-open-february-1-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>85 Scholarships, Contests, Grants and other Global Opportunities Currently Open – January 25, 2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/01/25/85-scholarships-contests-grants-and-other-global-opportunities-currently-open-january-25-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>40 Grants, Scholarships, Awards, Fellowships, Prizes and Internships Closing Before January 2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2025/11/22/40-grants-scholarships-awards-fellowships-prizes-and-internships-closing-before-january-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Commonwealth PhD Scholarships 2026/2027 (Fully-funded)</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2025/09/03/commonwealth-phd-scholarships-2026-2027/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>23 Scholarships and Opportunities for Postgraduate Studies and Students Currently Open –  August 10, 2025</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2025/08/10/__trashed-6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Cambridge Africa Changemakers Scholarship 2025 for PhD students (Fully-funded)</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2025/06/18/cambridge-africa-changemakers-scholarship-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Call for Applications: CLARITY-Africa PhD Scholarship 2025 (Fully-funded)</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2025/03/28/clarity-africa-phd-scholarship-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>10 Scholarship Opportunities for Graduate and Postgraduate Studies Currently Open – March 23, 2025</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2025/03/23/10-scholarship-opportunities-for-graduate-and-postgraduate-studies-currently-open-march-23-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>20 Scholarship Opportunities for Graduate and Postgraduate Studies With  Deadline Fast Approaching- March 11, 2025</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Check Official Website</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Check Official Website</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>https://opportunitydesk.org/2025/03/11/20-scholarship-opportunities-for-graduates-and-postgraduates-with-deadline-approaching-march-11-2025/</t>
         </is>

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E112"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -906,7 +906,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Lester B. Pearson International Student Scholarships 2027</t>
+          <t>SHE-CAN Scholar Program 2026-2027 (Funded)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/22/lester-b-pearson-international-student-scholarships-2027/</t>
+          <t>https://opportunitydesk.org/2026/07/28/she-can-scholar-program-2026-2027/</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SHE-CAN Scholar Program 2026-2027 (Funded)</t>
+          <t>Girls On Campus She Leads Scholarship 2026 (up to $1,500)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/she-can-scholar-program-2026-2027/</t>
+          <t>https://opportunitydesk.org/2026/07/27/girls-on-campus-she-leads-scholarship-2026/</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Girls On Campus She Leads Scholarship 2026 (up to $1,500)</t>
+          <t>50 Scholarships, Grants and Global Opportunities With Deadline Fast Approaching  – February 24, 2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/27/girls-on-campus-she-leads-scholarship-2026/</t>
+          <t>https://opportunitydesk.org/2026/02/24/50-scholarships-grants-and-global-opportunities-with-deadline-fast-approaching-february-24-2026/</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>50 Scholarships, Grants and Global Opportunities With Deadline Fast Approaching  – February 24, 2026</t>
+          <t>12 Global Scholarships Currently Open – December 18,2025</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/02/24/50-scholarships-grants-and-global-opportunities-with-deadline-fast-approaching-february-24-2026/</t>
+          <t>https://opportunitydesk.org/2025/12/18/12-global-scholarships-currently-open-december-12025/</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>12 Global Scholarships Currently Open – December 18,2025</t>
+          <t>40 Grants, Scholarships, Awards, Fellowships, Prizes and Internships Closing Before January 2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/12/18/12-global-scholarships-currently-open-december-12025/</t>
+          <t>https://opportunitydesk.org/2025/11/22/40-grants-scholarships-awards-fellowships-prizes-and-internships-closing-before-january-2026/</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>40 Grants, Scholarships, Awards, Fellowships, Prizes and Internships Closing Before January 2026</t>
+          <t>NL Scholarship 2026/2027 to Study in The Netherlands (up to €5,000)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/11/22/40-grants-scholarships-awards-fellowships-prizes-and-internships-closing-before-january-2026/</t>
+          <t>https://opportunitydesk.org/2025/11/08/nl-scholarship-2026-2027/</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>NL Scholarship 2026/2027 to Study in The Netherlands (up to €5,000)</t>
+          <t>Sterling Bank/Miva Open University Scholarship 2025</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/11/08/nl-scholarship-2026-2027/</t>
+          <t>https://opportunitydesk.org/2025/06/19/sterling-bank-miva-open-university-scholarship-2025/</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Sterling Bank/Miva Open University Scholarship 2025</t>
+          <t>Mastercard Foundation Scholars Program at Pan-Atlantic University 2025-2026 for Nigerians</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/06/19/sterling-bank-miva-open-university-scholarship-2025/</t>
+          <t>https://opportunitydesk.org/2025/05/27/mastercard-foundation-scholars-program-at-pan-atlantic-university-2025-2026/</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation Scholars Program at Pan-Atlantic University 2025-2026 for Nigerians</t>
+          <t>10 Scholarship Opportunities for Graduate and Postgraduate Studies Currently Open – March 23, 2025</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/05/27/mastercard-foundation-scholars-program-at-pan-atlantic-university-2025-2026/</t>
+          <t>https://opportunitydesk.org/2025/03/23/10-scholarship-opportunities-for-graduate-and-postgraduate-studies-currently-open-march-23-2025/</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>10 Scholarship Opportunities for Graduate and Postgraduate Studies Currently Open – March 23, 2025</t>
+          <t>22 Scholarship Opportunities for Postgraduate and Undergraduate Students Closing Soon – December 27, 2024</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/03/23/10-scholarship-opportunities-for-graduate-and-postgraduate-studies-currently-open-march-23-2025/</t>
+          <t>https://opportunitydesk.org/2024/12/27/22-scholarship-opportunities-for-postgraduate-and-undergraduate-students-closing-soon-december-27-2024/</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>22 Scholarship Opportunities for Postgraduate and Undergraduate Students Closing Soon – December 27, 2024</t>
+          <t>VLIRUOS ICP Connect Study Scholarship 2025 (Fully-funded)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2024/12/27/22-scholarship-opportunities-for-postgraduate-and-undergraduate-students-closing-soon-december-27-2024/</t>
+          <t>https://opportunitydesk.org/2024/10/31/vliruos-icp-connect-study-scholarship-2025/</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>VLIRUOS ICP Connect Study Scholarship 2025 (Fully-funded)</t>
+          <t>20 Global Opportunities for Postgraduate &amp; Undergraduate Students Currently Open – October 15, 2024</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1218,34 +1218,34 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2024/10/31/vliruos-icp-connect-study-scholarship-2025/</t>
+          <t>https://opportunitydesk.org/2024/10/15/20-global-opportunities-for-postgraduate-undergraduate-students-currently-open-october-15-2024/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>20 Global Opportunities for Postgraduate &amp; Undergraduate Students Currently Open – October 15, 2024</t>
+          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2024/10/15/20-global-opportunities-for-postgraduate-undergraduate-students-currently-open-october-15-2024/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
+          <t>Fully Funded Master’s Opportunity at the University of Cambridge 2027 with Funding of Up to GBP 70,000</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Application closes in 89 days</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-opportunity-at-the-university-of-cambridge-2027-with-funding-of-up-to-gbp-70000</t>
         </is>
       </c>
     </row>
@@ -1284,22 +1284,22 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Master’s Opportunity at the University of Cambridge 2027 with Funding of Up to GBP 70,000</t>
+          <t>University of Sydney Scholarship for International Students to Pursue Bachelor’s and Master’s Studies with Funding of Up to AUD 60,000</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 89 days</t>
+          <t>Application closes in 38 days</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-opportunity-at-the-university-of-cambridge-2027-with-funding-of-up-to-gbp-70000</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-sydney-scholarship-for-international-students-to-pursue-bachelors-and-masters-studies-with-funding-of-up-to-aud-60000</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>University of Sydney Scholarship for International Students to Pursue Bachelor’s and Master’s Studies with Funding of Up to AUD 60,000</t>
+          <t>Funded UNSW Scholarship in Australia for Undergraduate and Master’s Studies</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1321,12 +1321,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 38 days</t>
+          <t>Application closes in 21 days</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-sydney-scholarship-for-international-students-to-pursue-bachelors-and-masters-studies-with-funding-of-up-to-aud-60000</t>
+          <t>https://www.for9a.com/en/opportunity/funded-unsw-scholarship-australia-undergraduate-masters-studies</t>
         </is>
       </c>
     </row>
@@ -1338,22 +1338,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Funded UNSW Scholarship in Australia for Undergraduate and Master’s Studies</t>
+          <t>Fully Funded Master’s Scholarship at Peking University 2027 for International Students</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 21 days</t>
+          <t>Application closes in 52 days</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-unsw-scholarship-australia-undergraduate-masters-studies</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-scholarship-at-peking-university-international-students</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Master’s Scholarship at Peking University 2027 for International Students</t>
+          <t>Partially Funded Master’s Scholarship in Australia Worth AUD 20,000 for International Students</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-scholarship-at-peking-university-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/partially-funded-masters-scholarship-in-australia-worth-aud-20000</t>
         </is>
       </c>
     </row>
@@ -1392,22 +1392,22 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Partially Funded Master’s Scholarship in Australia Worth AUD 20,000 for International Students</t>
+          <t>Funded Master’s in Canada at the University of Waterloo in Artificial Intelligence and Cybersecurity for International Students</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 52 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/partially-funded-masters-scholarship-in-australia-worth-aud-20000</t>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-in-canada-at-the-university-of-waterloo-in-artificial-intelligence-and-cybersecurity-for-international-students</t>
         </is>
       </c>
     </row>
@@ -1419,22 +1419,22 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s in Canada at the University of Waterloo in Artificial Intelligence and Cybersecurity for International Students</t>
+          <t>Al Akhawayn University Scholarship for International Students 2027 to Pursue a Master’s Degree in Morocco</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Application closes in 22 days</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-in-canada-at-the-university-of-waterloo-in-artificial-intelligence-and-cybersecurity-for-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/al-akhawayn-university-scholarship-for-international-students-pursue-masters-degree-in-morocco</t>
         </is>
       </c>
     </row>
@@ -1446,22 +1446,22 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Al Akhawayn University Scholarship for International Students 2027 to Pursue a Master’s Degree in Morocco</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 22 days</t>
+          <t>Application closes in 11 days</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/al-akhawayn-university-scholarship-for-international-students-pursue-masters-degree-in-morocco</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
@@ -1473,22 +1473,22 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>Kolding School of Design Scholarship 2027 for a Master’s in Design in Denmark</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 11 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>https://www.for9a.com/en/opportunity/kolding-school-of-design-scholarship-for-a-masters-in-design-in-denmark-bwlon</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Kolding School of Design Scholarship 2027 for a Master’s in Design in Denmark</t>
+          <t>IT University of Copenhagen Scholarship 2027 for Master’s Study in Denmark</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/kolding-school-of-design-scholarship-for-a-masters-in-design-in-denmark-bwlon</t>
+          <t>https://www.for9a.com/en/opportunity/it-university-of-copenhagen-scholarship-2027-for-masters-study-in-denmark</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>IT University of Copenhagen Scholarship 2027 for Master’s Study in Denmark</t>
+          <t>Erasmus Mundus CYBERSURE Scholarship 2027 for a Master’s in Cybersecurity with a EUR 1,400 Monthly Stipend</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/it-university-of-copenhagen-scholarship-2027-for-masters-study-in-denmark</t>
+          <t>https://www.for9a.com/en/opportunity/erasmus-mundus-cybersure-scholarship-a-masters-in-cybersecurity-with-monthly-stipend</t>
         </is>
       </c>
     </row>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Erasmus Mundus CYBERSURE Scholarship 2027 for a Master’s in Cybersecurity with a EUR 1,400 Monthly Stipend</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/erasmus-mundus-cybersure-scholarship-a-masters-in-cybersecurity-with-monthly-stipend</t>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>LUT University Master’s Scholarships in Finland with Discounts and Funding of up to €10,000</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>https://www.for9a.com/en/opportunity/lut-university-scholarships-international-students-finland</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>LUT University Master’s Scholarships in Finland with Discounts and Funding of up to €10,000</t>
+          <t>University of Jyväskylä Bachelor’s and Master’s Scholarships with Discounts of up to €6,000 in 2027</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/lut-university-scholarships-international-students-finland</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-jyv%C3%A4skyl%C3%A4-bachelors-and-masters-scholarships-with-discounts-of-up-to-6000-in-2027</t>
         </is>
       </c>
     </row>
@@ -1635,22 +1635,22 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>University of Jyväskylä Bachelor’s and Master’s Scholarships with Discounts of up to €6,000 in 2027</t>
+          <t>University of Global Health Equity Master of Science in Health Professions Education Program (MSc-HPE) 2027</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-jyv%C3%A4skyl%C3%A4-bachelors-and-masters-scholarships-with-discounts-of-up-to-6000-in-2027</t>
+          <t>https://opportunitydesk.org/2026/10/07/university-of-global-health-equity-master-of-science-in-health-professions-education-program-2027/</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>University of Global Health Equity Master of Science in Health Professions Education Program (MSc-HPE) 2027</t>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/07/university-of-global-health-equity-master-of-science-in-health-professions-education-program-2027/</t>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
+          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
+          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
+          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
+          <t>Gates Cambridge Scholarships 2027-2028 (Fully-funded)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/15/gates-cambridge-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Gates Cambridge Scholarships 2027-2028 (Fully-funded)</t>
+          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/15/gates-cambridge-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
+          <t>Commonwealth Master’s Scholarships 2027/2028 (Fully-funded)</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
+          <t>https://opportunitydesk.org/2026/09/09/commonwealth-masters-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Commonwealth Master’s Scholarships 2027/2028 (Fully-funded)</t>
+          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/commonwealth-masters-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
+          <t>Glendon Chase McCormick Scholarship 2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
+          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Glendon Chase McCormick Scholarship 2026</t>
+          <t>Johns Hopkins SAIS Public Service Scholars – Scholarship Program 2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
+          <t>https://opportunitydesk.org/2026/06/13/johns-hopkins-sais-public-service-scholars-scholarship-program-2026/</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Johns Hopkins SAIS Public Service Scholars – Scholarship Program 2026</t>
+          <t>Johns Hopkins SAIS Public Service Fellows – Scholarship Program 2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/13/johns-hopkins-sais-public-service-scholars-scholarship-program-2026/</t>
+          <t>https://opportunitydesk.org/2026/06/13/johns-hopkins-sais-public-service-fellows-scholarship-program-2026/</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Johns Hopkins SAIS Public Service Fellows – Scholarship Program 2026</t>
+          <t>Professor Tagirin A. Fregene Scholarship Fund for Masters in Medical Physics 2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/13/johns-hopkins-sais-public-service-fellows-scholarship-program-2026/</t>
+          <t>https://opportunitydesk.org/2026/06/10/professor-tagirin-a-fregene-scholarship-fund-2026/</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Professor Tagirin A. Fregene Scholarship Fund for Masters in Medical Physics 2026</t>
+          <t>Rhodes Scholarships 2027 for Study at the University of Oxford (Fully-funded)</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/10/professor-tagirin-a-fregene-scholarship-fund-2026/</t>
+          <t>https://opportunitydesk.org/2026/06/01/rhodes-scholarships-2027/</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Rhodes Scholarships 2027 for Study at the University of Oxford (Fully-funded)</t>
+          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/01/rhodes-scholarships-2027/</t>
+          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
+          <t>66 Grants, Study Abroad, Trainings and Professional Development Opportunities Currently Open – May 9, 2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
+          <t>https://opportunitydesk.org/2026/05/09/66-grants-study-abroad-trainings-and-professional-development-opportunities-currently-open-saturday-may-9-2026/</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>66 Grants, Study Abroad, Trainings and Professional Development Opportunities Currently Open – May 9, 2026</t>
+          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/09/66-grants-study-abroad-trainings-and-professional-development-opportunities-currently-open-saturday-may-9-2026/</t>
+          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
+          <t>IHE Delft Sahel, Middle East and Horn of Africa Scholarships 2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
+          <t>https://opportunitydesk.org/2026/04/24/ihe-delft-sahel-middle-east-and-horn-of-africa-scholarships-2026/</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>IHE Delft Sahel, Middle East and Horn of Africa Scholarships 2026</t>
+          <t>20 Fully Sponsored, Study Abroad, Mentorship and Other Global Opportunities Currently Open – April 6, 2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/04/24/ihe-delft-sahel-middle-east-and-horn-of-africa-scholarships-2026/</t>
+          <t>https://opportunitydesk.org/2026/04/06/20-fully-sponsored-study-abroad-mentorship-and-other-global-opportunities-currently-open-april-6-2026/</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>20 Fully Sponsored, Study Abroad, Mentorship and Other Global Opportunities Currently Open – April 6, 2026</t>
+          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/04/06/20-fully-sponsored-study-abroad-mentorship-and-other-global-opportunities-currently-open-april-6-2026/</t>
+          <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
+          <t>50 Scholarships, Grants and Global Opportunities With Deadline Fast Approaching  – February 24, 2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
+          <t>https://opportunitydesk.org/2026/02/24/50-scholarships-grants-and-global-opportunities-with-deadline-fast-approaching-february-24-2026/</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>50 Scholarships, Grants and Global Opportunities With Deadline Fast Approaching  – February 24, 2026</t>
+          <t>15 Global Opportunities for Graduate and Postgraduate Studies Currently Open – February 1, 2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -2379,34 +2379,34 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/02/24/50-scholarships-grants-and-global-opportunities-with-deadline-fast-approaching-february-24-2026/</t>
+          <t>https://opportunitydesk.org/2026/02/01/15-global-opportunities-for-graduate-and-postgraduate-studies-currently-open-february-1-2026/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15 Global Opportunities for Graduate and Postgraduate Studies Currently Open – February 1, 2026</t>
+          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/02/01/15-global-opportunities-for-graduate-and-postgraduate-studies-currently-open-february-1-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
         </is>
       </c>
     </row>
@@ -2418,22 +2418,22 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
+          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Application closes in 53 days</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
         </is>
       </c>
     </row>
@@ -2445,22 +2445,22 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
+          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 53 days</t>
+          <t>Application closes in 16 days</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
+          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
         </is>
       </c>
     </row>
@@ -2472,22 +2472,22 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
+          <t>Funded PhD Scholarship in New Zealand 2027 at the University of Canterbury for International Students with Funding of up to NZD 32,650</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 16 days</t>
+          <t>Application closes in 6 days</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
+          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-new-zealand-the-university-of-canterbury-for-international-students</t>
         </is>
       </c>
     </row>
@@ -2499,22 +2499,22 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship in New Zealand 2027 at the University of Canterbury for International Students with Funding of up to NZD 32,650</t>
+          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 6 days</t>
+          <t>Application closes in 37 days</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-new-zealand-the-university-of-canterbury-for-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
         </is>
       </c>
     </row>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
+          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 37 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
         </is>
       </c>
     </row>
@@ -2553,22 +2553,22 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Application closes in 11 days</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
@@ -2580,22 +2580,22 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 11 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
         </is>
       </c>
     </row>
@@ -2607,12 +2607,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>Fully Funded GEMS PhD Scholarship 2026 at Monash University Malaysia with a Monthly Stipend</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Application closes in 6 days</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-gems-phd-scholarship-2026-at-monash-university-malaysia-with-a-monthly-stipend</t>
         </is>
       </c>
     </row>
@@ -2661,22 +2661,22 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded GEMS PhD Scholarship 2026 at Monash University Malaysia with a Monthly Stipend</t>
+          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 6 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-gems-phd-scholarship-2026-at-monash-university-malaysia-with-a-monthly-stipend</t>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
         </is>
       </c>
     </row>
@@ -2688,12 +2688,12 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
+          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
+          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
+          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
+          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
+          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
+          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2769,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
+          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
+          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
         </is>
       </c>
     </row>
@@ -2796,22 +2796,22 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
+          <t>AHRC Doctoral Landscape Award at the University of Sheffield 2027/2028</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
+          <t>https://opportunitydesk.org/2026/10/01/ahrc-doctoral-landscape-award-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>AHRC Doctoral Landscape Award at the University of Sheffield 2027/2028</t>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/ahrc-doctoral-landscape-award-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
+          <t>Gates Cambridge Scholarships 2027-2028 (Fully-funded)</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/15/gates-cambridge-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Gates Cambridge Scholarships 2027-2028 (Fully-funded)</t>
+          <t>Commonwealth PhD Scholarships 2027/2028 (Fully-Funded)</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/15/gates-cambridge-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/09/commonwealth-phd-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Commonwealth PhD Scholarships 2027/2028 (Fully-Funded)</t>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/commonwealth-phd-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+          <t>Glendon Chase McCormick Scholarship 2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Glendon Chase McCormick Scholarship 2026</t>
+          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
+          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
+          <t>Mastercard Foundation Doctoral Scholarships 2026-2027 at the University of Toronto</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
+          <t>https://opportunitydesk.org/2026/05/11/mastercard-foundation-doctoral-scholarships-2026-2027-at-the-university-of-toronto/</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation Doctoral Scholarships 2026-2027 at the University of Toronto</t>
+          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/11/mastercard-foundation-doctoral-scholarships-2026-2027-at-the-university-of-toronto/</t>
+          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
+          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
+          <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
+          <t>UNU-IIGH Global Health PhD Fellowship Programme 2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
+          <t>https://opportunitydesk.org/2026/03/03/unu-iigh-global-health-phd-fellowship-programme-2026/</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>UNU-IIGH Global Health PhD Fellowship Programme 2026</t>
+          <t>14 Scholarships, Grants and Global Opportunities Open this Valentine Season – February 10, 2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/03/03/unu-iigh-global-health-phd-fellowship-programme-2026/</t>
+          <t>https://opportunitydesk.org/2026/02/11/14-scholarships-grants-and-global-opportunities-open-this-valentine-season-february-10-2026/</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>14 Scholarships, Grants and Global Opportunities Open this Valentine Season – February 10, 2026</t>
+          <t>15 Global Opportunities for Graduate and Postgraduate Studies Currently Open – February 1, 2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/02/11/14-scholarships-grants-and-global-opportunities-open-this-valentine-season-february-10-2026/</t>
+          <t>https://opportunitydesk.org/2026/02/01/15-global-opportunities-for-graduate-and-postgraduate-studies-currently-open-february-1-2026/</t>
         </is>
       </c>
     </row>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>15 Global Opportunities for Graduate and Postgraduate Studies Currently Open – February 1, 2026</t>
+          <t>85 Scholarships, Contests, Grants and other Global Opportunities Currently Open – January 25, 2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/02/01/15-global-opportunities-for-graduate-and-postgraduate-studies-currently-open-february-1-2026/</t>
+          <t>https://opportunitydesk.org/2026/01/25/85-scholarships-contests-grants-and-other-global-opportunities-currently-open-january-25-2026/</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>85 Scholarships, Contests, Grants and other Global Opportunities Currently Open – January 25, 2026</t>
+          <t>40 Grants, Scholarships, Awards, Fellowships, Prizes and Internships Closing Before January 2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/01/25/85-scholarships-contests-grants-and-other-global-opportunities-currently-open-january-25-2026/</t>
+          <t>https://opportunitydesk.org/2025/11/22/40-grants-scholarships-awards-fellowships-prizes-and-internships-closing-before-january-2026/</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>40 Grants, Scholarships, Awards, Fellowships, Prizes and Internships Closing Before January 2026</t>
+          <t>Commonwealth PhD Scholarships 2026/2027 (Fully-funded)</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/11/22/40-grants-scholarships-awards-fellowships-prizes-and-internships-closing-before-january-2026/</t>
+          <t>https://opportunitydesk.org/2025/09/03/commonwealth-phd-scholarships-2026-2027/</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Commonwealth PhD Scholarships 2026/2027 (Fully-funded)</t>
+          <t>23 Scholarships and Opportunities for Postgraduate Studies and Students Currently Open –  August 10, 2025</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/09/03/commonwealth-phd-scholarships-2026-2027/</t>
+          <t>https://opportunitydesk.org/2025/08/10/__trashed-6/</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>23 Scholarships and Opportunities for Postgraduate Studies and Students Currently Open –  August 10, 2025</t>
+          <t>Cambridge Africa Changemakers Scholarship 2025 for PhD students (Fully-funded)</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/08/10/__trashed-6/</t>
+          <t>https://opportunitydesk.org/2025/06/18/cambridge-africa-changemakers-scholarship-2025/</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Cambridge Africa Changemakers Scholarship 2025 for PhD students (Fully-funded)</t>
+          <t>Call for Applications: CLARITY-Africa PhD Scholarship 2025 (Fully-funded)</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/06/18/cambridge-africa-changemakers-scholarship-2025/</t>
+          <t>https://opportunitydesk.org/2025/03/28/clarity-africa-phd-scholarship-2025/</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Call for Applications: CLARITY-Africa PhD Scholarship 2025 (Fully-funded)</t>
+          <t>10 Scholarship Opportunities for Graduate and Postgraduate Studies Currently Open – March 23, 2025</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/03/28/clarity-africa-phd-scholarship-2025/</t>
+          <t>https://opportunitydesk.org/2025/03/23/10-scholarship-opportunities-for-graduate-and-postgraduate-studies-currently-open-march-23-2025/</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>10 Scholarship Opportunities for Graduate and Postgraduate Studies Currently Open – March 23, 2025</t>
+          <t>20 Scholarship Opportunities for Graduate and Postgraduate Studies With  Deadline Fast Approaching- March 11, 2025</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -3431,33 +3431,6 @@
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2025/03/23/10-scholarship-opportunities-for-graduate-and-postgraduate-studies-currently-open-march-23-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>20 Scholarship Opportunities for Graduate and Postgraduate Studies With  Deadline Fast Approaching- March 11, 2025</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>Check Official Website</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>https://opportunitydesk.org/2025/03/11/20-scholarship-opportunities-for-graduates-and-postgraduates-with-deadline-approaching-march-11-2025/</t>
         </is>

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -484,7 +484,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 38 days</t>
+          <t>Application closes in 37 days</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 21 days</t>
+          <t>Application closes in 20 days</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 53 days</t>
+          <t>Application closes in 52 days</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 23 days</t>
+          <t>Application closes in 22 days</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 98 days</t>
+          <t>Application closes in 97 days</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 53 days</t>
+          <t>Application closes in 52 days</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 38 days</t>
+          <t>Application closes in 37 days</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 89 days</t>
+          <t>Application closes in 88 days</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 38 days</t>
+          <t>Application closes in 37 days</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 21 days</t>
+          <t>Application closes in 20 days</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 52 days</t>
+          <t>Application closes in 51 days</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 52 days</t>
+          <t>Application closes in 51 days</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 22 days</t>
+          <t>Application closes in 21 days</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 11 days</t>
+          <t>Application closes in 10 days</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 53 days</t>
+          <t>Application closes in 52 days</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 16 days</t>
+          <t>Application closes in 15 days</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 6 days</t>
+          <t>Application closes in 5 days</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 37 days</t>
+          <t>Application closes in 36 days</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 11 days</t>
+          <t>Application closes in 10 days</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 6 days</t>
+          <t>Application closes in 5 days</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation Doctoral Scholarships 2026-2027 at the University of Toronto</t>
+          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/11/mastercard-foundation-doctoral-scholarships-2026-2027-at-the-university-of-toronto/</t>
+          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
+          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
+          <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
+          <t>UNU-IIGH Global Health PhD Fellowship Programme 2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
+          <t>https://opportunitydesk.org/2026/03/03/unu-iigh-global-health-phd-fellowship-programme-2026/</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>UNU-IIGH Global Health PhD Fellowship Programme 2026</t>
+          <t>14 Scholarships, Grants and Global Opportunities Open this Valentine Season – February 10, 2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/03/03/unu-iigh-global-health-phd-fellowship-programme-2026/</t>
+          <t>https://opportunitydesk.org/2026/02/11/14-scholarships-grants-and-global-opportunities-open-this-valentine-season-february-10-2026/</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>14 Scholarships, Grants and Global Opportunities Open this Valentine Season – February 10, 2026</t>
+          <t>15 Global Opportunities for Graduate and Postgraduate Studies Currently Open – February 1, 2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/02/11/14-scholarships-grants-and-global-opportunities-open-this-valentine-season-february-10-2026/</t>
+          <t>https://opportunitydesk.org/2026/02/01/15-global-opportunities-for-graduate-and-postgraduate-studies-currently-open-february-1-2026/</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>15 Global Opportunities for Graduate and Postgraduate Studies Currently Open – February 1, 2026</t>
+          <t>85 Scholarships, Contests, Grants and other Global Opportunities Currently Open – January 25, 2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/02/01/15-global-opportunities-for-graduate-and-postgraduate-studies-currently-open-february-1-2026/</t>
+          <t>https://opportunitydesk.org/2026/01/25/85-scholarships-contests-grants-and-other-global-opportunities-currently-open-january-25-2026/</t>
         </is>
       </c>
     </row>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>85 Scholarships, Contests, Grants and other Global Opportunities Currently Open – January 25, 2026</t>
+          <t>40 Grants, Scholarships, Awards, Fellowships, Prizes and Internships Closing Before January 2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/01/25/85-scholarships-contests-grants-and-other-global-opportunities-currently-open-january-25-2026/</t>
+          <t>https://opportunitydesk.org/2025/11/22/40-grants-scholarships-awards-fellowships-prizes-and-internships-closing-before-january-2026/</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>40 Grants, Scholarships, Awards, Fellowships, Prizes and Internships Closing Before January 2026</t>
+          <t>Commonwealth PhD Scholarships 2026/2027 (Fully-funded)</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/11/22/40-grants-scholarships-awards-fellowships-prizes-and-internships-closing-before-january-2026/</t>
+          <t>https://opportunitydesk.org/2025/09/03/commonwealth-phd-scholarships-2026-2027/</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Commonwealth PhD Scholarships 2026/2027 (Fully-funded)</t>
+          <t>23 Scholarships and Opportunities for Postgraduate Studies and Students Currently Open –  August 10, 2025</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/09/03/commonwealth-phd-scholarships-2026-2027/</t>
+          <t>https://opportunitydesk.org/2025/08/10/__trashed-6/</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>23 Scholarships and Opportunities for Postgraduate Studies and Students Currently Open –  August 10, 2025</t>
+          <t>Cambridge Africa Changemakers Scholarship 2025 for PhD students (Fully-funded)</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/08/10/__trashed-6/</t>
+          <t>https://opportunitydesk.org/2025/06/18/cambridge-africa-changemakers-scholarship-2025/</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Cambridge Africa Changemakers Scholarship 2025 for PhD students (Fully-funded)</t>
+          <t>Call for Applications: CLARITY-Africa PhD Scholarship 2025 (Fully-funded)</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/06/18/cambridge-africa-changemakers-scholarship-2025/</t>
+          <t>https://opportunitydesk.org/2025/03/28/clarity-africa-phd-scholarship-2025/</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Call for Applications: CLARITY-Africa PhD Scholarship 2025 (Fully-funded)</t>
+          <t>10 Scholarship Opportunities for Graduate and Postgraduate Studies Currently Open – March 23, 2025</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/03/28/clarity-africa-phd-scholarship-2025/</t>
+          <t>https://opportunitydesk.org/2025/03/23/10-scholarship-opportunities-for-graduate-and-postgraduate-studies-currently-open-march-23-2025/</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>10 Scholarship Opportunities for Graduate and Postgraduate Studies Currently Open – March 23, 2025</t>
+          <t>20 Scholarship Opportunities for Graduate and Postgraduate Studies With  Deadline Fast Approaching- March 11, 2025</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -3404,33 +3404,6 @@
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2025/03/23/10-scholarship-opportunities-for-graduate-and-postgraduate-studies-currently-open-march-23-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>20 Scholarship Opportunities for Graduate and Postgraduate Studies With  Deadline Fast Approaching- March 11, 2025</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>Check Official Website</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>https://opportunitydesk.org/2025/03/11/20-scholarship-opportunities-for-graduates-and-postgraduates-with-deadline-approaching-march-11-2025/</t>
         </is>

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -987,7 +987,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>12 Global Scholarships Currently Open – December 18,2025</t>
+          <t>Türkiye Scholarships 2026 for International Students</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1002,223 +1002,223 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/12/18/12-global-scholarships-currently-open-december-12025/</t>
+          <t>https://opportunitydesk.org/2026/01/09/turkiye-scholarships-2026/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>40 Grants, Scholarships, Awards, Fellowships, Prizes and Internships Closing Before January 2026</t>
+          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/11/22/40-grants-scholarships-awards-fellowships-prizes-and-internships-closing-before-january-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>NL Scholarship 2026/2027 to Study in The Netherlands (up to €5,000)</t>
+          <t>Fully Funded Master’s Opportunity at the University of Cambridge 2027 with Funding of Up to GBP 70,000</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>Application closes in 88 days</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/11/08/nl-scholarship-2026-2027/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-opportunity-at-the-university-of-cambridge-2027-with-funding-of-up-to-gbp-70000</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Sterling Bank/Miva Open University Scholarship 2025</t>
+          <t>University of Sydney Scholarship for International Students to Pursue Bachelor’s and Master’s Studies with Funding of Up to AUD 60,000</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>Application closes in 37 days</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/06/19/sterling-bank-miva-open-university-scholarship-2025/</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-sydney-scholarship-for-international-students-to-pursue-bachelors-and-masters-studies-with-funding-of-up-to-aud-60000</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation Scholars Program at Pan-Atlantic University 2025-2026 for Nigerians</t>
+          <t>Funded UNSW Scholarship in Australia for Undergraduate and Master’s Studies</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>Application closes in 20 days</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/05/27/mastercard-foundation-scholars-program-at-pan-atlantic-university-2025-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/funded-unsw-scholarship-australia-undergraduate-masters-studies</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>10 Scholarship Opportunities for Graduate and Postgraduate Studies Currently Open – March 23, 2025</t>
+          <t>Fully Funded Master’s Scholarship at Peking University 2027 for International Students</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>Application closes in 51 days</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2025/03/23/10-scholarship-opportunities-for-graduate-and-postgraduate-studies-currently-open-march-23-2025/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-scholarship-at-peking-university-international-students</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>22 Scholarship Opportunities for Postgraduate and Undergraduate Students Closing Soon – December 27, 2024</t>
+          <t>Partially Funded Master’s Scholarship in Australia Worth AUD 20,000 for International Students</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>Application closes in 51 days</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2024/12/27/22-scholarship-opportunities-for-postgraduate-and-undergraduate-students-closing-soon-december-27-2024/</t>
+          <t>https://www.for9a.com/en/opportunity/partially-funded-masters-scholarship-in-australia-worth-aud-20000</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>VLIRUOS ICP Connect Study Scholarship 2025 (Fully-funded)</t>
+          <t>Funded Master’s in Canada at the University of Waterloo in Artificial Intelligence and Cybersecurity for International Students</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2024/10/31/vliruos-icp-connect-study-scholarship-2025/</t>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-in-canada-at-the-university-of-waterloo-in-artificial-intelligence-and-cybersecurity-for-international-students</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>20 Global Opportunities for Postgraduate &amp; Undergraduate Students Currently Open – October 15, 2024</t>
+          <t>Al Akhawayn University Scholarship for International Students 2027 to Pursue a Master’s Degree in Morocco</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>Application closes in 21 days</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2024/10/15/20-global-opportunities-for-postgraduate-undergraduate-students-currently-open-october-15-2024/</t>
+          <t>https://www.for9a.com/en/opportunity/al-akhawayn-university-scholarship-for-international-students-pursue-masters-degree-in-morocco</t>
         </is>
       </c>
     </row>
@@ -1230,22 +1230,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Application closes in 10 days</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
@@ -1257,22 +1257,22 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Master’s Opportunity at the University of Cambridge 2027 with Funding of Up to GBP 70,000</t>
+          <t>Kolding School of Design Scholarship 2027 for a Master’s in Design in Denmark</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 88 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-opportunity-at-the-university-of-cambridge-2027-with-funding-of-up-to-gbp-70000</t>
+          <t>https://www.for9a.com/en/opportunity/kolding-school-of-design-scholarship-for-a-masters-in-design-in-denmark-bwlon</t>
         </is>
       </c>
     </row>
@@ -1284,22 +1284,22 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>University of Sydney Scholarship for International Students to Pursue Bachelor’s and Master’s Studies with Funding of Up to AUD 60,000</t>
+          <t>IT University of Copenhagen Scholarship 2027 for Master’s Study in Denmark</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 37 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-sydney-scholarship-for-international-students-to-pursue-bachelors-and-masters-studies-with-funding-of-up-to-aud-60000</t>
+          <t>https://www.for9a.com/en/opportunity/it-university-of-copenhagen-scholarship-2027-for-masters-study-in-denmark</t>
         </is>
       </c>
     </row>
@@ -1311,22 +1311,22 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Funded UNSW Scholarship in Australia for Undergraduate and Master’s Studies</t>
+          <t>Erasmus Mundus CYBERSURE Scholarship 2027 for a Master’s in Cybersecurity with a EUR 1,400 Monthly Stipend</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 20 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-unsw-scholarship-australia-undergraduate-masters-studies</t>
+          <t>https://www.for9a.com/en/opportunity/erasmus-mundus-cybersure-scholarship-a-masters-in-cybersecurity-with-monthly-stipend</t>
         </is>
       </c>
     </row>
@@ -1338,22 +1338,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Master’s Scholarship at Peking University 2027 for International Students</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 51 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-scholarship-at-peking-university-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Partially Funded Master’s Scholarship in Australia Worth AUD 20,000 for International Students</t>
+          <t>LUT University Master’s Scholarships in Finland with Discounts and Funding of up to €10,000</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 51 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/partially-funded-masters-scholarship-in-australia-worth-aud-20000</t>
+          <t>https://www.for9a.com/en/opportunity/lut-university-scholarships-international-students-finland</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s in Canada at the University of Waterloo in Artificial Intelligence and Cybersecurity for International Students</t>
+          <t>University of Jyväskylä Bachelor’s and Master’s Scholarships with Discounts of up to €6,000 in 2027</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-in-canada-at-the-university-of-waterloo-in-artificial-intelligence-and-cybersecurity-for-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-jyv%C3%A4skyl%C3%A4-bachelors-and-masters-scholarships-with-discounts-of-up-to-6000-in-2027</t>
         </is>
       </c>
     </row>
@@ -1419,22 +1419,22 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Al Akhawayn University Scholarship for International Students 2027 to Pursue a Master’s Degree in Morocco</t>
+          <t>University of Global Health Equity Master of Science in Health Professions Education Program (MSc-HPE) 2027</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 21 days</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/al-akhawayn-university-scholarship-for-international-students-pursue-masters-degree-in-morocco</t>
+          <t>https://opportunitydesk.org/2026/10/07/university-of-global-health-equity-master-of-science-in-health-professions-education-program-2027/</t>
         </is>
       </c>
     </row>
@@ -1446,22 +1446,22 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 10 days</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
         </is>
       </c>
     </row>
@@ -1473,22 +1473,22 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Kolding School of Design Scholarship 2027 for a Master’s in Design in Denmark</t>
+          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/kolding-school-of-design-scholarship-for-a-masters-in-design-in-denmark-bwlon</t>
+          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
         </is>
       </c>
     </row>
@@ -1500,22 +1500,22 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>IT University of Copenhagen Scholarship 2027 for Master’s Study in Denmark</t>
+          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/it-university-of-copenhagen-scholarship-2027-for-masters-study-in-denmark</t>
+          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1527,22 +1527,22 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Erasmus Mundus CYBERSURE Scholarship 2027 for a Master’s in Cybersecurity with a EUR 1,400 Monthly Stipend</t>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/erasmus-mundus-cybersure-scholarship-a-masters-in-cybersecurity-with-monthly-stipend</t>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
         </is>
       </c>
     </row>
@@ -1554,22 +1554,22 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>Gates Cambridge Scholarships 2027-2028 (Fully-funded)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>https://opportunitydesk.org/2026/09/15/gates-cambridge-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1581,22 +1581,22 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>LUT University Master’s Scholarships in Finland with Discounts and Funding of up to €10,000</t>
+          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/lut-university-scholarships-international-students-finland</t>
+          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
         </is>
       </c>
     </row>
@@ -1608,22 +1608,22 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>University of Jyväskylä Bachelor’s and Master’s Scholarships with Discounts of up to €6,000 in 2027</t>
+          <t>Commonwealth Master’s Scholarships 2027/2028 (Fully-funded)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-jyv%C3%A4skyl%C3%A4-bachelors-and-masters-scholarships-with-discounts-of-up-to-6000-in-2027</t>
+          <t>https://opportunitydesk.org/2026/09/09/commonwealth-masters-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>University of Global Health Equity Master of Science in Health Professions Education Program (MSc-HPE) 2027</t>
+          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/07/university-of-global-health-equity-master-of-science-in-health-professions-education-program-2027/</t>
+          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
+          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
+          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
+          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Gates Cambridge Scholarships 2027-2028 (Fully-funded)</t>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/15/gates-cambridge-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
+          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
+          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Commonwealth Master’s Scholarships 2027/2028 (Fully-funded)</t>
+          <t>Glendon Chase McCormick Scholarship 2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/commonwealth-masters-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
+          <t>Johns Hopkins SAIS Public Service Scholars – Scholarship Program 2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
+          <t>https://opportunitydesk.org/2026/06/13/johns-hopkins-sais-public-service-scholars-scholarship-program-2026/</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+          <t>Johns Hopkins SAIS Public Service Fellows – Scholarship Program 2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/06/13/johns-hopkins-sais-public-service-fellows-scholarship-program-2026/</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
+          <t>Professor Tagirin A. Fregene Scholarship Fund for Masters in Medical Physics 2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
+          <t>https://opportunitydesk.org/2026/06/10/professor-tagirin-a-fregene-scholarship-fund-2026/</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+          <t>Rhodes Scholarships 2027 for Study at the University of Oxford (Fully-funded)</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+          <t>https://opportunitydesk.org/2026/06/01/rhodes-scholarships-2027/</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
+          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+          <t>66 Grants, Study Abroad, Trainings and Professional Development Opportunities Currently Open – May 9, 2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+          <t>https://opportunitydesk.org/2026/05/09/66-grants-study-abroad-trainings-and-professional-development-opportunities-currently-open-saturday-may-9-2026/</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
+          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
+          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Glendon Chase McCormick Scholarship 2026</t>
+          <t>IHE Delft Sahel, Middle East and Horn of Africa Scholarships 2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
+          <t>https://opportunitydesk.org/2026/04/24/ihe-delft-sahel-middle-east-and-horn-of-africa-scholarships-2026/</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Johns Hopkins SAIS Public Service Scholars – Scholarship Program 2026</t>
+          <t>20 Fully Sponsored, Study Abroad, Mentorship and Other Global Opportunities Currently Open – April 6, 2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/13/johns-hopkins-sais-public-service-scholars-scholarship-program-2026/</t>
+          <t>https://opportunitydesk.org/2026/04/06/20-fully-sponsored-study-abroad-mentorship-and-other-global-opportunities-currently-open-april-6-2026/</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Johns Hopkins SAIS Public Service Fellows – Scholarship Program 2026</t>
+          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/13/johns-hopkins-sais-public-service-fellows-scholarship-program-2026/</t>
+          <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Professor Tagirin A. Fregene Scholarship Fund for Masters in Medical Physics 2026</t>
+          <t>50 Scholarships, Grants and Global Opportunities With Deadline Fast Approaching  – February 24, 2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/10/professor-tagirin-a-fregene-scholarship-fund-2026/</t>
+          <t>https://opportunitydesk.org/2026/02/24/50-scholarships-grants-and-global-opportunities-with-deadline-fast-approaching-february-24-2026/</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Rhodes Scholarships 2027 for Study at the University of Oxford (Fully-funded)</t>
+          <t>15 Global Opportunities for Graduate and Postgraduate Studies Currently Open – February 1, 2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2163,223 +2163,223 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/01/rhodes-scholarships-2027/</t>
+          <t>https://opportunitydesk.org/2026/02/01/15-global-opportunities-for-graduate-and-postgraduate-studies-currently-open-february-1-2026/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
+          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>66 Grants, Study Abroad, Trainings and Professional Development Opportunities Currently Open – May 9, 2026</t>
+          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>Application closes in 52 days</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/09/66-grants-study-abroad-trainings-and-professional-development-opportunities-currently-open-saturday-may-9-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
+          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>Application closes in 15 days</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>IHE Delft Sahel, Middle East and Horn of Africa Scholarships 2026</t>
+          <t>Funded PhD Scholarship in New Zealand 2027 at the University of Canterbury for International Students with Funding of up to NZD 32,650</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>Application closes in 5 days</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/04/24/ihe-delft-sahel-middle-east-and-horn-of-africa-scholarships-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-new-zealand-the-university-of-canterbury-for-international-students</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>20 Fully Sponsored, Study Abroad, Mentorship and Other Global Opportunities Currently Open – April 6, 2026</t>
+          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>Application closes in 36 days</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/04/06/20-fully-sponsored-study-abroad-mentorship-and-other-global-opportunities-currently-open-april-6-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
+          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>50 Scholarships, Grants and Global Opportunities With Deadline Fast Approaching  – February 24, 2026</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>Application closes in 10 days</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/02/24/50-scholarships-grants-and-global-opportunities-with-deadline-fast-approaching-february-24-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>15 Global Opportunities for Graduate and Postgraduate Studies Currently Open – February 1, 2026</t>
+          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/02/01/15-global-opportunities-for-graduate-and-postgraduate-studies-currently-open-february-1-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
         </is>
       </c>
     </row>
@@ -2391,12 +2391,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
@@ -2418,22 +2418,22 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
+          <t>Fully Funded GEMS PhD Scholarship 2026 at Monash University Malaysia with a Monthly Stipend</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 52 days</t>
+          <t>Application closes in 5 days</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-gems-phd-scholarship-2026-at-monash-university-malaysia-with-a-monthly-stipend</t>
         </is>
       </c>
     </row>
@@ -2445,22 +2445,22 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
+          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 15 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
         </is>
       </c>
     </row>
@@ -2472,22 +2472,22 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship in New Zealand 2027 at the University of Canterbury for International Students with Funding of up to NZD 32,650</t>
+          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 5 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-new-zealand-the-university-of-canterbury-for-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -2499,22 +2499,22 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
+          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 36 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
+          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
+          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
+          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
         </is>
       </c>
     </row>
@@ -2553,22 +2553,22 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 10 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
         </is>
       </c>
     </row>
@@ -2580,22 +2580,22 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
+          <t>AHRC Doctoral Landscape Award at the University of Sheffield 2027/2028</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
+          <t>https://opportunitydesk.org/2026/10/01/ahrc-doctoral-landscape-award-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2607,22 +2607,22 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
         </is>
       </c>
     </row>
@@ -2634,22 +2634,22 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded GEMS PhD Scholarship 2026 at Monash University Malaysia with a Monthly Stipend</t>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 5 days</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-gems-phd-scholarship-2026-at-monash-university-malaysia-with-a-monthly-stipend</t>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
         </is>
       </c>
     </row>
@@ -2661,22 +2661,22 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
+          <t>Gates Cambridge Scholarships 2027-2028 (Fully-funded)</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
+          <t>https://opportunitydesk.org/2026/09/15/gates-cambridge-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2688,22 +2688,22 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
+          <t>Commonwealth PhD Scholarships 2027/2028 (Fully-Funded)</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
+          <t>https://opportunitydesk.org/2026/09/09/commonwealth-phd-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2715,22 +2715,22 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2742,22 +2742,22 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
         </is>
       </c>
     </row>
@@ -2769,22 +2769,22 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check Official Website</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>AHRC Doctoral Landscape Award at the University of Sheffield 2027/2028</t>
+          <t>Glendon Chase McCormick Scholarship 2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/ahrc-doctoral-landscape-award-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
+          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
+          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
+          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
+          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Gates Cambridge Scholarships 2027-2028 (Fully-funded)</t>
+          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/15/gates-cambridge-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Commonwealth PhD Scholarships 2027/2028 (Fully-Funded)</t>
+          <t>15 Global Opportunities for Graduate and Postgraduate Studies Currently Open – February 1, 2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/commonwealth-phd-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/02/01/15-global-opportunities-for-graduate-and-postgraduate-studies-currently-open-february-1-2026/</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+          <t>85 Scholarships, Contests, Grants and other Global Opportunities Currently Open – January 25, 2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/01/25/85-scholarships-contests-grants-and-other-global-opportunities-currently-open-january-25-2026/</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+          <t>MESCAL Project PhD in Marine Science 2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+          <t>https://opportunitydesk.org/2026/03/02/mescal-project-phd-in-marine-science-2026/</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+          <t>KAS Scholarship Program 2026 for Master’s Degree or Doctorate Degree in Germany</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+          <t>https://opportunitydesk.org/2026/02/04/kas-scholarship-program-2027/</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Glendon Chase McCormick Scholarship 2026</t>
+          <t>Call for Nominations: Fonseca Leadership Program in Africa 2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
+          <t>https://opportunitydesk.org/2026/01/26/fonseca-leadership-program-in-africa-2026/</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
+          <t>Ghent University Doctoral Scholarships for Candidates from the Global South 2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
+          <t>https://opportunitydesk.org/2026/01/20/ghent-university-doctoral-scholarships-for-candidates-from-the-global-south-2026/</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
+          <t>Ute and György Széll International Scholarship 2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
+          <t>https://opportunitydesk.org/2026/01/13/ute-and-gyorgy-szell-international-scholarship-2026/</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
+          <t>Hans Böckler Foundation Dieter Schumacher PhD Scholarship Program 2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
+          <t>https://opportunitydesk.org/2026/01/13/hans-bockler-foundation-dieter-schumacher-phd-scholarship-program-2026/</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>UNU-IIGH Global Health PhD Fellowship Programme 2026</t>
+          <t>Maple Leaf Centre for Action on Food Security Scholarship 2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/03/03/unu-iigh-global-health-phd-fellowship-programme-2026/</t>
+          <t>https://opportunitydesk.org/2026/01/12/maple-leaf-centre-for-action-on-food-security-scholarship-2026/</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>14 Scholarships, Grants and Global Opportunities Open this Valentine Season – February 10, 2026</t>
+          <t>Türkiye Scholarships 2026 for International Students</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/02/11/14-scholarships-grants-and-global-opportunities-open-this-valentine-season-february-10-2026/</t>
+          <t>https://opportunitydesk.org/2026/01/09/turkiye-scholarships-2026/</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>15 Global Opportunities for Graduate and Postgraduate Studies Currently Open – February 1, 2026</t>
+          <t>James McCune Smith Scholarships 2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/02/01/15-global-opportunities-for-graduate-and-postgraduate-studies-currently-open-february-1-2026/</t>
+          <t>https://opportunitydesk.org/2026/01/08/james-mccune-smith-scholarships-2026/</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>85 Scholarships, Contests, Grants and other Global Opportunities Currently Open – January 25, 2026</t>
+          <t>ARUA Early-career Research Fellowships 2026 (Stipend available)</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -3216,196 +3216,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/01/25/85-scholarships-contests-grants-and-other-global-opportunities-currently-open-january-25-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>40 Grants, Scholarships, Awards, Fellowships, Prizes and Internships Closing Before January 2026</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>Check Official Website</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2025/11/22/40-grants-scholarships-awards-fellowships-prizes-and-internships-closing-before-january-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>Commonwealth PhD Scholarships 2026/2027 (Fully-funded)</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>Check Official Website</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2025/09/03/commonwealth-phd-scholarships-2026-2027/</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>23 Scholarships and Opportunities for Postgraduate Studies and Students Currently Open –  August 10, 2025</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>Check Official Website</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2025/08/10/__trashed-6/</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>Cambridge Africa Changemakers Scholarship 2025 for PhD students (Fully-funded)</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>Check Official Website</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2025/06/18/cambridge-africa-changemakers-scholarship-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>Call for Applications: CLARITY-Africa PhD Scholarship 2025 (Fully-funded)</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>Check Official Website</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2025/03/28/clarity-africa-phd-scholarship-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>10 Scholarship Opportunities for Graduate and Postgraduate Studies Currently Open – March 23, 2025</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>Check Official Website</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2025/03/23/10-scholarship-opportunities-for-graduate-and-postgraduate-studies-currently-open-march-23-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>20 Scholarship Opportunities for Graduate and Postgraduate Studies With  Deadline Fast Approaching- March 11, 2025</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>Check Official Website</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2025/03/11/20-scholarship-opportunities-for-graduates-and-postgraduates-with-deadline-approaching-march-11-2025/</t>
+          <t>https://opportunitydesk.org/2026/01/01/arua-early-career-research-fellowships-2026/</t>
         </is>
       </c>
     </row>

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -889,7 +889,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Check Official Website</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 37 days</t>
+          <t>Application closes in 36 days</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 20 days</t>
+          <t>Application closes in 19 days</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 52 days</t>
+          <t>Application closes in 51 days</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 22 days</t>
+          <t>Application closes in 21 days</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 97 days</t>
+          <t>Application closes in 96 days</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 52 days</t>
+          <t>Application closes in 51 days</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 37 days</t>
+          <t>Application closes in 36 days</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 88 days</t>
+          <t>Application closes in 87 days</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 37 days</t>
+          <t>Application closes in 36 days</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 20 days</t>
+          <t>Application closes in 19 days</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 51 days</t>
+          <t>Application closes in 50 days</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 51 days</t>
+          <t>Application closes in 50 days</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 21 days</t>
+          <t>Application closes in 20 days</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 10 days</t>
+          <t>Application closes in 9 days</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 52 days</t>
+          <t>Application closes in 51 days</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 15 days</t>
+          <t>Application closes in 14 days</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 5 days</t>
+          <t>Application closes in 4 days</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 36 days</t>
+          <t>Application closes in 35 days</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 10 days</t>
+          <t>Application closes in 9 days</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 5 days</t>
+          <t>Application closes in 4 days</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -673,7 +673,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Always Open</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Always Open</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Always Open</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Always Open</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -982,27 +982,27 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Türkiye Scholarships 2026 for International Students</t>
+          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/01/09/turkiye-scholarships-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
+          <t>Fully Funded Master’s Opportunity at the University of Cambridge 2027 with Funding of Up to GBP 70,000</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Application closes in 87 days</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-opportunity-at-the-university-of-cambridge-2027-with-funding-of-up-to-gbp-70000</t>
         </is>
       </c>
     </row>
@@ -1041,22 +1041,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Master’s Opportunity at the University of Cambridge 2027 with Funding of Up to GBP 70,000</t>
+          <t>University of Sydney Scholarship for International Students to Pursue Bachelor’s and Master’s Studies with Funding of Up to AUD 60,000</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 87 days</t>
+          <t>Application closes in 36 days</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-opportunity-at-the-university-of-cambridge-2027-with-funding-of-up-to-gbp-70000</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-sydney-scholarship-for-international-students-to-pursue-bachelors-and-masters-studies-with-funding-of-up-to-aud-60000</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>University of Sydney Scholarship for International Students to Pursue Bachelor’s and Master’s Studies with Funding of Up to AUD 60,000</t>
+          <t>Funded UNSW Scholarship in Australia for Undergraduate and Master’s Studies</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 36 days</t>
+          <t>Application closes in 19 days</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-sydney-scholarship-for-international-students-to-pursue-bachelors-and-masters-studies-with-funding-of-up-to-aud-60000</t>
+          <t>https://www.for9a.com/en/opportunity/funded-unsw-scholarship-australia-undergraduate-masters-studies</t>
         </is>
       </c>
     </row>
@@ -1095,22 +1095,22 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Funded UNSW Scholarship in Australia for Undergraduate and Master’s Studies</t>
+          <t>Fully Funded Master’s Scholarship at Peking University 2027 for International Students</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 19 days</t>
+          <t>Application closes in 50 days</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-unsw-scholarship-australia-undergraduate-masters-studies</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-scholarship-at-peking-university-international-students</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Master’s Scholarship at Peking University 2027 for International Students</t>
+          <t>Partially Funded Master’s Scholarship in Australia Worth AUD 20,000 for International Students</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-scholarship-at-peking-university-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/partially-funded-masters-scholarship-in-australia-worth-aud-20000</t>
         </is>
       </c>
     </row>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Partially Funded Master’s Scholarship in Australia Worth AUD 20,000 for International Students</t>
+          <t>Funded Master’s in Canada at the University of Waterloo in Artificial Intelligence and Cybersecurity for International Students</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 50 days</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/partially-funded-masters-scholarship-in-australia-worth-aud-20000</t>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-in-canada-at-the-university-of-waterloo-in-artificial-intelligence-and-cybersecurity-for-international-students</t>
         </is>
       </c>
     </row>
@@ -1176,22 +1176,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s in Canada at the University of Waterloo in Artificial Intelligence and Cybersecurity for International Students</t>
+          <t>Al Akhawayn University Scholarship for International Students 2027 to Pursue a Master’s Degree in Morocco</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Application closes in 20 days</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-in-canada-at-the-university-of-waterloo-in-artificial-intelligence-and-cybersecurity-for-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/al-akhawayn-university-scholarship-for-international-students-pursue-masters-degree-in-morocco</t>
         </is>
       </c>
     </row>
@@ -1203,22 +1203,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Al Akhawayn University Scholarship for International Students 2027 to Pursue a Master’s Degree in Morocco</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 20 days</t>
+          <t>Application closes in 9 days</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/al-akhawayn-university-scholarship-for-international-students-pursue-masters-degree-in-morocco</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
@@ -1230,22 +1230,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>Kolding School of Design Scholarship 2027 for a Master’s in Design in Denmark</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 9 days</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>https://www.for9a.com/en/opportunity/kolding-school-of-design-scholarship-for-a-masters-in-design-in-denmark-bwlon</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Kolding School of Design Scholarship 2027 for a Master’s in Design in Denmark</t>
+          <t>IT University of Copenhagen Scholarship 2027 for Master’s Study in Denmark</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/kolding-school-of-design-scholarship-for-a-masters-in-design-in-denmark-bwlon</t>
+          <t>https://www.for9a.com/en/opportunity/it-university-of-copenhagen-scholarship-2027-for-masters-study-in-denmark</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>IT University of Copenhagen Scholarship 2027 for Master’s Study in Denmark</t>
+          <t>Erasmus Mundus CYBERSURE Scholarship 2027 for a Master’s in Cybersecurity with a EUR 1,400 Monthly Stipend</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/it-university-of-copenhagen-scholarship-2027-for-masters-study-in-denmark</t>
+          <t>https://www.for9a.com/en/opportunity/erasmus-mundus-cybersure-scholarship-a-masters-in-cybersecurity-with-monthly-stipend</t>
         </is>
       </c>
     </row>
@@ -1311,22 +1311,22 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Erasmus Mundus CYBERSURE Scholarship 2027 for a Master’s in Cybersecurity with a EUR 1,400 Monthly Stipend</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>Always Open</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/erasmus-mundus-cybersure-scholarship-a-masters-in-cybersecurity-with-monthly-stipend</t>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
@@ -1338,22 +1338,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>LUT University Master’s Scholarships in Finland with Discounts and Funding of up to €10,000</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Always Open</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>https://www.for9a.com/en/opportunity/lut-university-scholarships-international-students-finland</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>LUT University Master’s Scholarships in Finland with Discounts and Funding of up to €10,000</t>
+          <t>University of Jyväskylä Bachelor’s and Master’s Scholarships with Discounts of up to €6,000 in 2027</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1375,12 +1375,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/lut-university-scholarships-international-students-finland</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-jyv%C3%A4skyl%C3%A4-bachelors-and-masters-scholarships-with-discounts-of-up-to-6000-in-2027</t>
         </is>
       </c>
     </row>
@@ -1392,22 +1392,22 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>University of Jyväskylä Bachelor’s and Master’s Scholarships with Discounts of up to €6,000 in 2027</t>
+          <t>University of Global Health Equity Master of Science in Health Professions Education Program (MSc-HPE) 2027</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-jyv%C3%A4skyl%C3%A4-bachelors-and-masters-scholarships-with-discounts-of-up-to-6000-in-2027</t>
+          <t>https://opportunitydesk.org/2026/10/07/university-of-global-health-equity-master-of-science-in-health-professions-education-program-2027/</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>University of Global Health Equity Master of Science in Health Professions Education Program (MSc-HPE) 2027</t>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/07/university-of-global-health-equity-master-of-science-in-health-professions-education-program-2027/</t>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
+          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
+          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
+          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
+          <t>Gates Cambridge Scholarships 2027-2028 (Fully-funded)</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/15/gates-cambridge-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Gates Cambridge Scholarships 2027-2028 (Fully-funded)</t>
+          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/15/gates-cambridge-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
+          <t>Commonwealth Master’s Scholarships 2027/2028 (Fully-funded)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
+          <t>https://opportunitydesk.org/2026/09/09/commonwealth-masters-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Commonwealth Master’s Scholarships 2027/2028 (Fully-funded)</t>
+          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/commonwealth-masters-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
+          <t>Glendon Chase McCormick Scholarship 2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -1812,358 +1812,358 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
+          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Glendon Chase McCormick Scholarship 2026</t>
+          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Johns Hopkins SAIS Public Service Scholars – Scholarship Program 2026</t>
+          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Application closes in 51 days</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/13/johns-hopkins-sais-public-service-scholars-scholarship-program-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Johns Hopkins SAIS Public Service Fellows – Scholarship Program 2026</t>
+          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Application closes in 14 days</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/13/johns-hopkins-sais-public-service-fellows-scholarship-program-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Professor Tagirin A. Fregene Scholarship Fund for Masters in Medical Physics 2026</t>
+          <t>Funded PhD Scholarship in New Zealand 2027 at the University of Canterbury for International Students with Funding of up to NZD 32,650</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Application closes in 4 days</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/10/professor-tagirin-a-fregene-scholarship-fund-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-new-zealand-the-university-of-canterbury-for-international-students</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Rhodes Scholarships 2027 for Study at the University of Oxford (Fully-funded)</t>
+          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Application closes in 35 days</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/01/rhodes-scholarships-2027/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
+          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>66 Grants, Study Abroad, Trainings and Professional Development Opportunities Currently Open – May 9, 2026</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Application closes in 9 days</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/09/66-grants-study-abroad-trainings-and-professional-development-opportunities-currently-open-saturday-may-9-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
+          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Always Open</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>IHE Delft Sahel, Middle East and Horn of Africa Scholarships 2026</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Always Open</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/04/24/ihe-delft-sahel-middle-east-and-horn-of-africa-scholarships-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>20 Fully Sponsored, Study Abroad, Mentorship and Other Global Opportunities Currently Open – April 6, 2026</t>
+          <t>Fully Funded GEMS PhD Scholarship 2026 at Monash University Malaysia with a Monthly Stipend</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Application closes in 4 days</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/04/06/20-fully-sponsored-study-abroad-mentorship-and-other-global-opportunities-currently-open-april-6-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-gems-phd-scholarship-2026-at-monash-university-malaysia-with-a-monthly-stipend</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
+          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>50 Scholarships, Grants and Global Opportunities With Deadline Fast Approaching  – February 24, 2026</t>
+          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/02/24/50-scholarships-grants-and-global-opportunities-with-deadline-fast-approaching-february-24-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>15 Global Opportunities for Graduate and Postgraduate Studies Currently Open – February 1, 2026</t>
+          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/02/01/15-global-opportunities-for-graduate-and-postgraduate-studies-currently-open-february-1-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -2175,12 +2175,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
+          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
+          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
         </is>
       </c>
     </row>
@@ -2202,22 +2202,22 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
+          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 51 days</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
+          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
         </is>
       </c>
     </row>
@@ -2229,22 +2229,22 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
+          <t>AHRC Doctoral Landscape Award at the University of Sheffield 2027/2028</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 14 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
+          <t>https://opportunitydesk.org/2026/10/01/ahrc-doctoral-landscape-award-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2256,22 +2256,22 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship in New Zealand 2027 at the University of Canterbury for International Students with Funding of up to NZD 32,650</t>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 4 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-new-zealand-the-university-of-canterbury-for-international-students</t>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
         </is>
       </c>
     </row>
@@ -2283,22 +2283,22 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 35 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
         </is>
       </c>
     </row>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
+          <t>Gates Cambridge Scholarships 2027-2028 (Fully-funded)</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
+          <t>https://opportunitydesk.org/2026/09/15/gates-cambridge-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2337,22 +2337,22 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>Commonwealth PhD Scholarships 2027/2028 (Fully-Funded)</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 9 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>https://opportunitydesk.org/2026/09/09/commonwealth-phd-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2364,22 +2364,22 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Always Open</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2391,22 +2391,22 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Always Open</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
         </is>
       </c>
     </row>
@@ -2418,22 +2418,22 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded GEMS PhD Scholarship 2026 at Monash University Malaysia with a Monthly Stipend</t>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 4 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-gems-phd-scholarship-2026-at-monash-university-malaysia-with-a-monthly-stipend</t>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
         </is>
       </c>
     </row>
@@ -2445,22 +2445,22 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
+          <t>Glendon Chase McCormick Scholarship 2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
+          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
         </is>
       </c>
     </row>
@@ -2472,22 +2472,22 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
+          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
+          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
         </is>
       </c>
     </row>
@@ -2499,22 +2499,22 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
+          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
+          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
         </is>
       </c>
     </row>
@@ -2526,697 +2526,22 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
+          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>Open Now</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>AHRC Doctoral Landscape Award at the University of Sheffield 2027/2028</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/10/01/ahrc-doctoral-landscape-award-2027-2028/</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>Gates Cambridge Scholarships 2027-2028 (Fully-funded)</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/09/15/gates-cambridge-scholarships-2027-2028/</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>Commonwealth PhD Scholarships 2027/2028 (Fully-Funded)</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/09/09/commonwealth-phd-scholarships-2027-2028/</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>Glendon Chase McCormick Scholarship 2026</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
           <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>15 Global Opportunities for Graduate and Postgraduate Studies Currently Open – February 1, 2026</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/02/01/15-global-opportunities-for-graduate-and-postgraduate-studies-currently-open-february-1-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>85 Scholarships, Contests, Grants and other Global Opportunities Currently Open – January 25, 2026</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/01/25/85-scholarships-contests-grants-and-other-global-opportunities-currently-open-january-25-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>MESCAL Project PhD in Marine Science 2026</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/03/02/mescal-project-phd-in-marine-science-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>KAS Scholarship Program 2026 for Master’s Degree or Doctorate Degree in Germany</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/02/04/kas-scholarship-program-2027/</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>Call for Nominations: Fonseca Leadership Program in Africa 2026</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/01/26/fonseca-leadership-program-in-africa-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>Ghent University Doctoral Scholarships for Candidates from the Global South 2026</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/01/20/ghent-university-doctoral-scholarships-for-candidates-from-the-global-south-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>Ute and György Széll International Scholarship 2026</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/01/13/ute-and-gyorgy-szell-international-scholarship-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>Hans Böckler Foundation Dieter Schumacher PhD Scholarship Program 2026</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/01/13/hans-bockler-foundation-dieter-schumacher-phd-scholarship-program-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>Maple Leaf Centre for Action on Food Security Scholarship 2026</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/01/12/maple-leaf-centre-for-action-on-food-security-scholarship-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>Türkiye Scholarships 2026 for International Students</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/01/09/turkiye-scholarships-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>James McCune Smith Scholarships 2026</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/01/08/james-mccune-smith-scholarships-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>ARUA Early-career Research Fellowships 2026 (Stipend available)</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/01/01/arua-early-career-research-fellowships-2026/</t>
         </is>
       </c>
     </row>

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 36 days</t>
+          <t>Application closes in 35 days</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 19 days</t>
+          <t>Application closes in 18 days</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 51 days</t>
+          <t>Application closes in 50 days</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 21 days</t>
+          <t>Application closes in 20 days</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 96 days</t>
+          <t>Application closes in 95 days</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 51 days</t>
+          <t>Application closes in 50 days</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 36 days</t>
+          <t>Application closes in 35 days</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 87 days</t>
+          <t>Application closes in 86 days</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 36 days</t>
+          <t>Application closes in 35 days</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 19 days</t>
+          <t>Application closes in 18 days</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 50 days</t>
+          <t>Application closes in 49 days</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 50 days</t>
+          <t>Application closes in 49 days</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 20 days</t>
+          <t>Application closes in 19 days</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 9 days</t>
+          <t>Application closes in 8 days</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 51 days</t>
+          <t>Application closes in 50 days</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 14 days</t>
+          <t>Application closes in 13 days</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 4 days</t>
+          <t>Application closes in 3 days</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 35 days</t>
+          <t>Application closes in 34 days</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 9 days</t>
+          <t>Application closes in 8 days</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 4 days</t>
+          <t>Application closes in 3 days</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 35 days</t>
+          <t>Application closes in 34 days</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 18 days</t>
+          <t>Application closes in 17 days</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 50 days</t>
+          <t>Application closes in 49 days</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 20 days</t>
+          <t>Application closes in 19 days</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 95 days</t>
+          <t>Application closes in 94 days</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 50 days</t>
+          <t>Application closes in 49 days</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 35 days</t>
+          <t>Application closes in 34 days</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 86 days</t>
+          <t>Application closes in 85 days</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 35 days</t>
+          <t>Application closes in 34 days</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 18 days</t>
+          <t>Application closes in 17 days</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 49 days</t>
+          <t>Application closes in 48 days</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 49 days</t>
+          <t>Application closes in 48 days</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 19 days</t>
+          <t>Application closes in 18 days</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 8 days</t>
+          <t>Application closes in 7 days</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 50 days</t>
+          <t>Application closes in 49 days</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 13 days</t>
+          <t>Application closes in 12 days</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 3 days</t>
+          <t>Application closes in 2 days</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 34 days</t>
+          <t>Application closes in 33 days</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 8 days</t>
+          <t>Application closes in 7 days</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 3 days</t>
+          <t>Application closes in 2 days</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -484,7 +484,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 34 days</t>
+          <t>Application closes in 33 days</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 17 days</t>
+          <t>Application closes in 16 days</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 49 days</t>
+          <t>Application closes in 48 days</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 19 days</t>
+          <t>Application closes in 18 days</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 94 days</t>
+          <t>Application closes in 93 days</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 49 days</t>
+          <t>Application closes in 48 days</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 34 days</t>
+          <t>Application closes in 33 days</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 85 days</t>
+          <t>Application closes in 84 days</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 34 days</t>
+          <t>Application closes in 33 days</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 17 days</t>
+          <t>Application closes in 16 days</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 48 days</t>
+          <t>Application closes in 47 days</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 48 days</t>
+          <t>Application closes in 47 days</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 18 days</t>
+          <t>Application closes in 17 days</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 7 days</t>
+          <t>Application closes in 6 days</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Gates Cambridge Scholarships 2027-2028 (Fully-funded)</t>
+          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/15/gates-cambridge-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
+          <t>Commonwealth Master’s Scholarships 2027/2028 (Fully-funded)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
+          <t>https://opportunitydesk.org/2026/09/09/commonwealth-masters-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Commonwealth Master’s Scholarships 2027/2028 (Fully-funded)</t>
+          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/commonwealth-masters-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
+          <t>Glendon Chase McCormick Scholarship 2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -1785,34 +1785,34 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
+          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Glendon Chase McCormick Scholarship 2026</t>
+          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
         </is>
       </c>
     </row>
@@ -1824,22 +1824,22 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
+          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Application closes in 48 days</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
         </is>
       </c>
     </row>
@@ -1851,22 +1851,22 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
+          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 49 days</t>
+          <t>Application closes in 11 days</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
+          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
         </is>
       </c>
     </row>
@@ -1878,22 +1878,22 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
+          <t>Funded PhD Scholarship in New Zealand 2027 at the University of Canterbury for International Students with Funding of up to NZD 32,650</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 12 days</t>
+          <t>Application closes in 1 day</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
+          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-new-zealand-the-university-of-canterbury-for-international-students</t>
         </is>
       </c>
     </row>
@@ -1905,22 +1905,22 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship in New Zealand 2027 at the University of Canterbury for International Students with Funding of up to NZD 32,650</t>
+          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 2 days</t>
+          <t>Application closes in 32 days</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-new-zealand-the-university-of-canterbury-for-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
         </is>
       </c>
     </row>
@@ -1932,22 +1932,22 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
+          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 33 days</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
         </is>
       </c>
     </row>
@@ -1959,22 +1959,22 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Application closes in 6 days</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
@@ -1986,22 +1986,22 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 7 days</t>
+          <t>Always Open</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
         </is>
       </c>
     </row>
@@ -2013,12 +2013,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>Fully Funded GEMS PhD Scholarship 2026 at Monash University Malaysia with a Monthly Stipend</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Always Open</t>
+          <t>Application closes in 1 day</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-gems-phd-scholarship-2026-at-monash-university-malaysia-with-a-monthly-stipend</t>
         </is>
       </c>
     </row>
@@ -2067,22 +2067,22 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded GEMS PhD Scholarship 2026 at Monash University Malaysia with a Monthly Stipend</t>
+          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 2 days</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-gems-phd-scholarship-2026-at-monash-university-malaysia-with-a-monthly-stipend</t>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
         </is>
       </c>
     </row>
@@ -2094,22 +2094,22 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
+          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
+          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
+          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
+          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
+          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
+          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
+          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
+          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
         </is>
       </c>
     </row>
@@ -2202,22 +2202,22 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
+          <t>AHRC Doctoral Landscape Award at the University of Sheffield 2027/2028</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
+          <t>https://opportunitydesk.org/2026/10/01/ahrc-doctoral-landscape-award-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>AHRC Doctoral Landscape Award at the University of Sheffield 2027/2028</t>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/ahrc-doctoral-landscape-award-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
+          <t>Commonwealth PhD Scholarships 2027/2028 (Fully-Funded)</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/09/commonwealth-phd-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Gates Cambridge Scholarships 2027-2028 (Fully-funded)</t>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/15/gates-cambridge-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Commonwealth PhD Scholarships 2027/2028 (Fully-Funded)</t>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/commonwealth-phd-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+          <t>Glendon Chase McCormick Scholarship 2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Glendon Chase McCormick Scholarship 2026</t>
+          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
+          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
+          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -2486,60 +2486,6 @@
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
         </is>

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -474,22 +474,22 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>University of Sydney Scholarship for International Students to Pursue Bachelor’s and Master’s Studies with Funding of Up to AUD 60,000</t>
+          <t>University of Oregon Scholarship 2027 for Undergraduate and Master’s Students with Funding of Up to US$5,000</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 33 days</t>
+          <t>Application closes in 31 days</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-sydney-scholarship-for-international-students-to-pursue-bachelors-and-masters-studies-with-funding-of-up-to-aud-60000</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-study-abroad-scholarship</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Funded UNSW Scholarship in Australia for Undergraduate and Master’s Studies</t>
+          <t>University of Sydney Scholarship for International Students to Pursue Bachelor’s and Master’s Studies with Funding of Up to AUD 60,000</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -511,12 +511,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 16 days</t>
+          <t>Application closes in 32 days</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-unsw-scholarship-australia-undergraduate-masters-studies</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-sydney-scholarship-for-international-students-to-pursue-bachelors-and-masters-studies-with-funding-of-up-to-aud-60000</t>
         </is>
       </c>
     </row>
@@ -528,22 +528,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Undergraduate Scholarship in China 2027 with Funding of Up to RMB 187,000 per Year</t>
+          <t>Funded UNSW Scholarship in Australia for Undergraduate and Master’s Studies</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 48 days</t>
+          <t>Application closes in 15 days</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/undergraduate-scholarship-in-china-2027-with-funding-of-up-to-rmb-187000-per-year</t>
+          <t>https://www.for9a.com/en/opportunity/funded-unsw-scholarship-australia-undergraduate-masters-studies</t>
         </is>
       </c>
     </row>
@@ -555,22 +555,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Undergraduate Scholarship in Artificial Intelligence in the UAE for 2027 with Up to 100% Funding</t>
+          <t>Undergraduate Scholarship in China 2027 with Funding of Up to RMB 187,000 per Year</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 18 days</t>
+          <t>Application closes in 47 days</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/undergraduate-scholarship-in-artificial-intelligence-in-the-uae-for-2027-with-up-to-100-funding</t>
+          <t>https://www.for9a.com/en/opportunity/undergraduate-scholarship-in-china-2027-with-funding-of-up-to-rmb-187000-per-year</t>
         </is>
       </c>
     </row>
@@ -582,22 +582,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Funded Undergraduate Scholarship at American University in the U.S. Covering Tuition, Housing, and Meals</t>
+          <t>Undergraduate Scholarship in Artificial Intelligence in the UAE for 2027 with Up to 100% Funding</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 93 days</t>
+          <t>Application closes in 17 days</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-undergraduate-scholarship-american-university-the-us-covering-tuition-housing-meals</t>
+          <t>https://www.for9a.com/en/opportunity/undergraduate-scholarship-in-artificial-intelligence-in-the-uae-for-2027-with-up-to-100-funding</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Bachelor’s Scholarship at Vanderbilt University in the USA for International Students 2027</t>
+          <t>Funded Undergraduate Scholarship at American University in the U.S. Covering Tuition, Housing, and Meals</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -619,12 +619,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 48 days</t>
+          <t>Application closes in 92 days</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/bachelors-scholarship-vanderbilt-university-the-usa-for-international</t>
+          <t>https://www.for9a.com/en/opportunity/funded-undergraduate-scholarship-american-university-the-us-covering-tuition-housing-meals</t>
         </is>
       </c>
     </row>
@@ -636,22 +636,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>University of Reading Scholarship 2027 for International Students Worth £5,000</t>
+          <t>Bachelor’s Scholarship at Vanderbilt University in the USA for International Students 2027</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 33 days</t>
+          <t>Application closes in 47 days</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-reading-scholarship-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/bachelors-scholarship-vanderbilt-university-the-usa-for-international</t>
         </is>
       </c>
     </row>
@@ -663,22 +663,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Scholarship in New Zealand for International Students Worth NZD 10,000</t>
+          <t>University of Reading Scholarship 2027 for International Students Worth £5,000</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Always Open</t>
+          <t>Application closes in 32 days</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/scholarship-in-new-zealand-for-international-students-worth-nzd-10000</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-reading-scholarship-international-students</t>
         </is>
       </c>
     </row>
@@ -690,22 +690,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>University of Jyväskylä Bachelor’s and Master’s Scholarships with Discounts of up to €6,000 in 2027</t>
+          <t>Scholarship in New Zealand for International Students Worth NZD 10,000</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>Always Open</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-jyv%C3%A4skyl%C3%A4-bachelors-and-masters-scholarships-with-discounts-of-up-to-6000-in-2027</t>
+          <t>https://www.for9a.com/en/opportunity/scholarship-in-new-zealand-for-international-students-worth-nzd-10000</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Partially Funded Bachelor’s and Master’s Scholarships at the University of Turku in Finland</t>
+          <t>University of Jyväskylä Bachelor’s and Master’s Scholarships with Discounts of up to €6,000 in 2027</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/partially-funded-bachelors-and-masters-scholarships-at-the-university-of-turku-in-finland</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-jyv%C3%A4skyl%C3%A4-bachelors-and-masters-scholarships-with-discounts-of-up-to-6000-in-2027</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>University of Eastern Finland Bachelor’s and Master’s Scholarships for International Students</t>
+          <t>Partially Funded Bachelor’s and Master’s Scholarships at the University of Turku in Finland</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-eastern-finland-bachelors-and-masters-scholarships-for-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/partially-funded-bachelors-and-masters-scholarships-at-the-university-of-turku-in-finland</t>
         </is>
       </c>
     </row>
@@ -771,22 +771,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
+          <t>University of Eastern Finland Bachelor’s and Master’s Scholarships for International Students</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-eastern-finland-bachelors-and-masters-scholarships-for-international-students</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>KAS Scholarships in Germany 2026 for Master’s, PhD, and International Students</t>
+          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/kas-scholarships-in-germany-2026-for-masters-phd-and-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Najran University Undergraduate Scholarships in Saudi Arabia for International Students</t>
+          <t>KAS Scholarships in Germany 2026 for Master’s, PhD, and International Students</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/najran-university-scholarships-in-saudi-arabia-for-international-students-2026</t>
+          <t>https://www.for9a.com/en/opportunity/kas-scholarships-in-germany-2026-for-masters-phd-and-international-students</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Prince Sultan University Undergraduate Scholarships in Saudi Arabia with Partial Funding</t>
+          <t>Najran University Undergraduate Scholarships in Saudi Arabia for International Students</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/prince-sultan-university-undergraduate-scholarships-in-saudi-arabia-with-partial-funding</t>
+          <t>https://www.for9a.com/en/opportunity/najran-university-scholarships-in-saudi-arabia-for-international-students-2026</t>
         </is>
       </c>
     </row>
@@ -987,22 +987,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
+          <t>University of Oregon Scholarship 2027 for Undergraduate and Master’s Students with Funding of Up to US$5,000</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Application closes in 31 days</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-study-abroad-scholarship</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Master’s Opportunity at the University of Cambridge 2027 with Funding of Up to GBP 70,000</t>
+          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 84 days</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-opportunity-at-the-university-of-cambridge-2027-with-funding-of-up-to-gbp-70000</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
         </is>
       </c>
     </row>
@@ -1041,22 +1041,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>University of Sydney Scholarship for International Students to Pursue Bachelor’s and Master’s Studies with Funding of Up to AUD 60,000</t>
+          <t>Fully Funded Master’s Opportunity at the University of Cambridge 2027 with Funding of Up to GBP 70,000</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 33 days</t>
+          <t>Application closes in 83 days</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-sydney-scholarship-for-international-students-to-pursue-bachelors-and-masters-studies-with-funding-of-up-to-aud-60000</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-opportunity-at-the-university-of-cambridge-2027-with-funding-of-up-to-gbp-70000</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Funded UNSW Scholarship in Australia for Undergraduate and Master’s Studies</t>
+          <t>University of Sydney Scholarship for International Students to Pursue Bachelor’s and Master’s Studies with Funding of Up to AUD 60,000</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 16 days</t>
+          <t>Application closes in 32 days</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-unsw-scholarship-australia-undergraduate-masters-studies</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-sydney-scholarship-for-international-students-to-pursue-bachelors-and-masters-studies-with-funding-of-up-to-aud-60000</t>
         </is>
       </c>
     </row>
@@ -1095,22 +1095,22 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Master’s Scholarship at Peking University 2027 for International Students</t>
+          <t>Funded UNSW Scholarship in Australia for Undergraduate and Master’s Studies</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 47 days</t>
+          <t>Application closes in 15 days</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-scholarship-at-peking-university-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/funded-unsw-scholarship-australia-undergraduate-masters-studies</t>
         </is>
       </c>
     </row>
@@ -1122,22 +1122,22 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Partially Funded Master’s Scholarship in Australia Worth AUD 20,000 for International Students</t>
+          <t>Fully Funded Master’s Scholarship at Peking University 2027 for International Students</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 47 days</t>
+          <t>Application closes in 46 days</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/partially-funded-masters-scholarship-in-australia-worth-aud-20000</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-scholarship-at-peking-university-international-students</t>
         </is>
       </c>
     </row>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s in Canada at the University of Waterloo in Artificial Intelligence and Cybersecurity for International Students</t>
+          <t>Partially Funded Master’s Scholarship in Australia Worth AUD 20,000 for International Students</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Application closes in 46 days</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-in-canada-at-the-university-of-waterloo-in-artificial-intelligence-and-cybersecurity-for-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/partially-funded-masters-scholarship-in-australia-worth-aud-20000</t>
         </is>
       </c>
     </row>
@@ -1176,22 +1176,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Al Akhawayn University Scholarship for International Students 2027 to Pursue a Master’s Degree in Morocco</t>
+          <t>Funded Master’s in Canada at the University of Waterloo in Artificial Intelligence and Cybersecurity for International Students</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 17 days</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/al-akhawayn-university-scholarship-for-international-students-pursue-masters-degree-in-morocco</t>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-in-canada-at-the-university-of-waterloo-in-artificial-intelligence-and-cybersecurity-for-international-students</t>
         </is>
       </c>
     </row>
@@ -1203,22 +1203,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>Al Akhawayn University Scholarship for International Students 2027 to Pursue a Master’s Degree in Morocco</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 6 days</t>
+          <t>Application closes in 16 days</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>https://www.for9a.com/en/opportunity/al-akhawayn-university-scholarship-for-international-students-pursue-masters-degree-in-morocco</t>
         </is>
       </c>
     </row>
@@ -1230,22 +1230,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Kolding School of Design Scholarship 2027 for a Master’s in Design in Denmark</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>Application closes in 5 days</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/kolding-school-of-design-scholarship-for-a-masters-in-design-in-denmark-bwlon</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>IT University of Copenhagen Scholarship 2027 for Master’s Study in Denmark</t>
+          <t>Kolding School of Design Scholarship 2027 for a Master’s in Design in Denmark</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/it-university-of-copenhagen-scholarship-2027-for-masters-study-in-denmark</t>
+          <t>https://www.for9a.com/en/opportunity/kolding-school-of-design-scholarship-for-a-masters-in-design-in-denmark-bwlon</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Erasmus Mundus CYBERSURE Scholarship 2027 for a Master’s in Cybersecurity with a EUR 1,400 Monthly Stipend</t>
+          <t>IT University of Copenhagen Scholarship 2027 for Master’s Study in Denmark</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/erasmus-mundus-cybersure-scholarship-a-masters-in-cybersecurity-with-monthly-stipend</t>
+          <t>https://www.for9a.com/en/opportunity/it-university-of-copenhagen-scholarship-2027-for-masters-study-in-denmark</t>
         </is>
       </c>
     </row>
@@ -1311,22 +1311,22 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>Erasmus Mundus CYBERSURE Scholarship 2027 for a Master’s in Cybersecurity with a EUR 1,400 Monthly Stipend</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Always Open</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>https://www.for9a.com/en/opportunity/erasmus-mundus-cybersure-scholarship-a-masters-in-cybersecurity-with-monthly-stipend</t>
         </is>
       </c>
     </row>
@@ -1338,22 +1338,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>LUT University Master’s Scholarships in Finland with Discounts and Funding of up to €10,000</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Always Open</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/lut-university-scholarships-international-students-finland</t>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>University of Jyväskylä Bachelor’s and Master’s Scholarships with Discounts of up to €6,000 in 2027</t>
+          <t>LUT University Master’s Scholarships in Finland with Discounts and Funding of up to €10,000</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1375,12 +1375,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-jyv%C3%A4skyl%C3%A4-bachelors-and-masters-scholarships-with-discounts-of-up-to-6000-in-2027</t>
+          <t>https://www.for9a.com/en/opportunity/lut-university-scholarships-international-students-finland</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>University of Global Health Equity Master of Science in Health Professions Education Program (MSc-HPE) 2027</t>
+          <t>France Excellence Eiffel Scholarship Program 2026-2027</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/07/university-of-global-health-equity-master-of-science-in-health-professions-education-program-2027/</t>
+          <t>https://opportunitydesk.org/2026/10/14/france-excellence-eiffel-scholarship-program-2026-2027/</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
+          <t>University of Global Health Equity Master of Science in Health Professions Education Program (MSc-HPE) 2027</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
+          <t>https://opportunitydesk.org/2026/10/07/university-of-global-health-equity-master-of-science-in-health-professions-education-program-2027/</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
+          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
+          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Commonwealth Master’s Scholarships 2027/2028 (Fully-funded)</t>
+          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/commonwealth-masters-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
+          <t>Commonwealth Master’s Scholarships 2027/2028 (Fully-funded)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
+          <t>https://opportunitydesk.org/2026/09/09/commonwealth-masters-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Glendon Chase McCormick Scholarship 2026</t>
+          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
+          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 48 days</t>
+          <t>Application closes in 47 days</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 11 days</t>
+          <t>Application closes in 10 days</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -1878,22 +1878,22 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship in New Zealand 2027 at the University of Canterbury for International Students with Funding of up to NZD 32,650</t>
+          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 1 day</t>
+          <t>Application closes in 31 days</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-new-zealand-the-university-of-canterbury-for-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
         </is>
       </c>
     </row>
@@ -1905,22 +1905,22 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
+          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 32 days</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
         </is>
       </c>
     </row>
@@ -1932,22 +1932,22 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Application closes in 5 days</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
@@ -1959,22 +1959,22 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 6 days</t>
+          <t>Always Open</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
         </is>
       </c>
     </row>
@@ -1986,12 +1986,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
@@ -2013,22 +2013,22 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Always Open</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
         </is>
       </c>
     </row>
@@ -2040,22 +2040,22 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded GEMS PhD Scholarship 2026 at Monash University Malaysia with a Monthly Stipend</t>
+          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 1 day</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-gems-phd-scholarship-2026-at-monash-university-malaysia-with-a-monthly-stipend</t>
+          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -2067,12 +2067,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
+          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
+          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
+          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
+          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
+          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
+          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
         </is>
       </c>
     </row>
@@ -2148,22 +2148,22 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
+          <t>France Excellence Eiffel Scholarship Program 2026-2027</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
+          <t>https://opportunitydesk.org/2026/10/14/france-excellence-eiffel-scholarship-program-2026-2027/</t>
         </is>
       </c>
     </row>
@@ -2175,22 +2175,22 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
+          <t>AHRC Doctoral Landscape Award at the University of Sheffield 2027/2028</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
+          <t>https://opportunitydesk.org/2026/10/01/ahrc-doctoral-landscape-award-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>AHRC Doctoral Landscape Award at the University of Sheffield 2027/2028</t>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/ahrc-doctoral-landscape-award-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
+          <t>Commonwealth PhD Scholarships 2027/2028 (Fully-Funded)</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/09/commonwealth-phd-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Commonwealth PhD Scholarships 2027/2028 (Fully-Funded)</t>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/commonwealth-phd-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+          <t>Glendon Chase McCormick Scholarship 2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Glendon Chase McCormick Scholarship 2026</t>
+          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
+          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
+          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
+          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
+          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -2459,33 +2459,6 @@
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
         </is>

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -484,7 +484,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 31 days</t>
+          <t>Application closes in 30 days</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 32 days</t>
+          <t>Application closes in 31 days</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 15 days</t>
+          <t>Application closes in 14 days</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 47 days</t>
+          <t>Application closes in 46 days</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 17 days</t>
+          <t>Application closes in 16 days</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 92 days</t>
+          <t>Application closes in 91 days</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 47 days</t>
+          <t>Application closes in 46 days</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 32 days</t>
+          <t>Application closes in 31 days</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -987,22 +987,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>University of Oregon Scholarship 2027 for Undergraduate and Master’s Students with Funding of Up to US$5,000</t>
+          <t>Fully Funded PhD Fellowship at New York University 2026 in Artificial Intelligence and Computer Science</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 31 days</t>
+          <t>Application closes in 57 days</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-study-abroad-scholarship</t>
+          <t>https://www.for9a.com/en/opportunity/nyuad-global-phd-student-fellowship-for-computer-science-2026</t>
         </is>
       </c>
     </row>
@@ -1014,22 +1014,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
+          <t>University of Oregon Scholarship 2027 for Undergraduate and Master’s Students with Funding of Up to US$5,000</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Application closes in 30 days</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-study-abroad-scholarship</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Master’s Opportunity at the University of Cambridge 2027 with Funding of Up to GBP 70,000</t>
+          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 83 days</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-opportunity-at-the-university-of-cambridge-2027-with-funding-of-up-to-gbp-70000</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
         </is>
       </c>
     </row>
@@ -1068,22 +1068,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>University of Sydney Scholarship for International Students to Pursue Bachelor’s and Master’s Studies with Funding of Up to AUD 60,000</t>
+          <t>Fully Funded Master’s Opportunity at the University of Cambridge 2027 with Funding of Up to GBP 70,000</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 32 days</t>
+          <t>Application closes in 82 days</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-sydney-scholarship-for-international-students-to-pursue-bachelors-and-masters-studies-with-funding-of-up-to-aud-60000</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-opportunity-at-the-university-of-cambridge-2027-with-funding-of-up-to-gbp-70000</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Funded UNSW Scholarship in Australia for Undergraduate and Master’s Studies</t>
+          <t>University of Sydney Scholarship for International Students to Pursue Bachelor’s and Master’s Studies with Funding of Up to AUD 60,000</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 15 days</t>
+          <t>Application closes in 31 days</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-unsw-scholarship-australia-undergraduate-masters-studies</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-sydney-scholarship-for-international-students-to-pursue-bachelors-and-masters-studies-with-funding-of-up-to-aud-60000</t>
         </is>
       </c>
     </row>
@@ -1122,22 +1122,22 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Master’s Scholarship at Peking University 2027 for International Students</t>
+          <t>Funded UNSW Scholarship in Australia for Undergraduate and Master’s Studies</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 46 days</t>
+          <t>Application closes in 14 days</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-scholarship-at-peking-university-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/funded-unsw-scholarship-australia-undergraduate-masters-studies</t>
         </is>
       </c>
     </row>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Partially Funded Master’s Scholarship in Australia Worth AUD 20,000 for International Students</t>
+          <t>Fully Funded Master’s Scholarship at Peking University 2027 for International Students</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 46 days</t>
+          <t>Application closes in 45 days</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/partially-funded-masters-scholarship-in-australia-worth-aud-20000</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-scholarship-at-peking-university-international-students</t>
         </is>
       </c>
     </row>
@@ -1176,22 +1176,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s in Canada at the University of Waterloo in Artificial Intelligence and Cybersecurity for International Students</t>
+          <t>Partially Funded Master’s Scholarship in Australia Worth AUD 20,000 for International Students</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Application closes in 45 days</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-in-canada-at-the-university-of-waterloo-in-artificial-intelligence-and-cybersecurity-for-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/partially-funded-masters-scholarship-in-australia-worth-aud-20000</t>
         </is>
       </c>
     </row>
@@ -1203,22 +1203,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Al Akhawayn University Scholarship for International Students 2027 to Pursue a Master’s Degree in Morocco</t>
+          <t>Funded Master’s in Canada at the University of Waterloo in Artificial Intelligence and Cybersecurity for International Students</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 16 days</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/al-akhawayn-university-scholarship-for-international-students-pursue-masters-degree-in-morocco</t>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-in-canada-at-the-university-of-waterloo-in-artificial-intelligence-and-cybersecurity-for-international-students</t>
         </is>
       </c>
     </row>
@@ -1230,22 +1230,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>Al Akhawayn University Scholarship for International Students 2027 to Pursue a Master’s Degree in Morocco</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 5 days</t>
+          <t>Application closes in 15 days</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>https://www.for9a.com/en/opportunity/al-akhawayn-university-scholarship-for-international-students-pursue-masters-degree-in-morocco</t>
         </is>
       </c>
     </row>
@@ -1257,22 +1257,22 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Kolding School of Design Scholarship 2027 for a Master’s in Design in Denmark</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>Application closes in 4 days</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/kolding-school-of-design-scholarship-for-a-masters-in-design-in-denmark-bwlon</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>IT University of Copenhagen Scholarship 2027 for Master’s Study in Denmark</t>
+          <t>Kolding School of Design Scholarship 2027 for a Master’s in Design in Denmark</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/it-university-of-copenhagen-scholarship-2027-for-masters-study-in-denmark</t>
+          <t>https://www.for9a.com/en/opportunity/kolding-school-of-design-scholarship-for-a-masters-in-design-in-denmark-bwlon</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Erasmus Mundus CYBERSURE Scholarship 2027 for a Master’s in Cybersecurity with a EUR 1,400 Monthly Stipend</t>
+          <t>IT University of Copenhagen Scholarship 2027 for Master’s Study in Denmark</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/erasmus-mundus-cybersure-scholarship-a-masters-in-cybersecurity-with-monthly-stipend</t>
+          <t>https://www.for9a.com/en/opportunity/it-university-of-copenhagen-scholarship-2027-for-masters-study-in-denmark</t>
         </is>
       </c>
     </row>
@@ -1338,22 +1338,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>Erasmus Mundus CYBERSURE Scholarship 2027 for a Master’s in Cybersecurity with a EUR 1,400 Monthly Stipend</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Always Open</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>https://www.for9a.com/en/opportunity/erasmus-mundus-cybersure-scholarship-a-masters-in-cybersecurity-with-monthly-stipend</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>LUT University Master’s Scholarships in Finland with Discounts and Funding of up to €10,000</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Always Open</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/lut-university-scholarships-international-students-finland</t>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>France Excellence Eiffel Scholarship Program 2026-2027</t>
+          <t>Toronto Metropolitan University Global Migration Institute Scholarships 2027-2028</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/14/france-excellence-eiffel-scholarship-program-2026-2027/</t>
+          <t>https://opportunitydesk.org/2026/10/15/tmu-global-migration-institute-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>University of Global Health Equity Master of Science in Health Professions Education Program (MSc-HPE) 2027</t>
+          <t>France Excellence Eiffel Scholarship Program 2026-2027</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/07/university-of-global-health-equity-master-of-science-in-health-professions-education-program-2027/</t>
+          <t>https://opportunitydesk.org/2026/10/14/france-excellence-eiffel-scholarship-program-2026-2027/</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
+          <t>University of Global Health Equity Master of Science in Health Professions Education Program (MSc-HPE) 2027</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
+          <t>https://opportunitydesk.org/2026/10/07/university-of-global-health-equity-master-of-science-in-health-professions-education-program-2027/</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
+          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
+          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Commonwealth Master’s Scholarships 2027/2028 (Fully-funded)</t>
+          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/commonwealth-masters-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
+          <t>Commonwealth Master’s Scholarships 2027/2028 (Fully-funded)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
+          <t>https://opportunitydesk.org/2026/09/09/commonwealth-masters-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -1785,34 +1785,34 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
+          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
+          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
         </is>
       </c>
     </row>
@@ -1824,22 +1824,22 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
+          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 47 days</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
         </is>
       </c>
     </row>
@@ -1851,22 +1851,22 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
+          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 10 days</t>
+          <t>Application closes in 46 days</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
         </is>
       </c>
     </row>
@@ -1878,22 +1878,22 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
+          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 31 days</t>
+          <t>Application closes in 9 days</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
+          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
         </is>
       </c>
     </row>
@@ -1905,22 +1905,22 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
+          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Application closes in 30 days</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
         </is>
       </c>
     </row>
@@ -1932,22 +1932,22 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 5 days</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
         </is>
       </c>
     </row>
@@ -1959,22 +1959,22 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Always Open</t>
+          <t>Application closes in 4 days</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
@@ -1986,12 +1986,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
         </is>
       </c>
     </row>
@@ -2013,22 +2013,22 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>Always Open</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
@@ -2040,22 +2040,22 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
+          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
+          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
+          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
+          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
+          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
+          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
+          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
         </is>
       </c>
     </row>
@@ -2148,22 +2148,22 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>France Excellence Eiffel Scholarship Program 2026-2027</t>
+          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/14/france-excellence-eiffel-scholarship-program-2026-2027/</t>
+          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
         </is>
       </c>
     </row>
@@ -2175,22 +2175,22 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>AHRC Doctoral Landscape Award at the University of Sheffield 2027/2028</t>
+          <t>KAS Scholarships in Germany 2026 for Master’s, PhD, and International Students</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/ahrc-doctoral-landscape-award-2027-2028/</t>
+          <t>https://www.for9a.com/en/opportunity/kas-scholarships-in-germany-2026-for-masters-phd-and-international-students</t>
         </is>
       </c>
     </row>
@@ -2202,22 +2202,22 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
+          <t>Fully Funded Scholarship in Azerbaijan for 2026-2027</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-scholarship-in-azerbaijan-for-2026-2027</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
+          <t>Toronto Metropolitan University Global Migration Institute Scholarships 2027-2028</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
+          <t>https://opportunitydesk.org/2026/10/15/tmu-global-migration-institute-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Commonwealth PhD Scholarships 2027/2028 (Fully-Funded)</t>
+          <t>France Excellence Eiffel Scholarship Program 2026-2027</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/commonwealth-phd-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/10/14/france-excellence-eiffel-scholarship-program-2026-2027/</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+          <t>AHRC Doctoral Landscape Award at the University of Sheffield 2027/2028</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/10/01/ahrc-doctoral-landscape-award-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Glendon Chase McCormick Scholarship 2026</t>
+          <t>Commonwealth PhD Scholarships 2027/2028 (Fully-Funded)</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/09/commonwealth-phd-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
         </is>
       </c>
     </row>
@@ -2445,20 +2445,128 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Glendon Chase McCormick Scholarship 2026</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
         </is>

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 30 days</t>
+          <t>Application closes in 29 days</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 31 days</t>
+          <t>Application closes in 30 days</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 14 days</t>
+          <t>Application closes in 13 days</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 46 days</t>
+          <t>Application closes in 45 days</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 16 days</t>
+          <t>Application closes in 15 days</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 91 days</t>
+          <t>Application closes in 90 days</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 46 days</t>
+          <t>Application closes in 45 days</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 31 days</t>
+          <t>Application closes in 30 days</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 57 days</t>
+          <t>Application closes in 56 days</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 30 days</t>
+          <t>Application closes in 29 days</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 82 days</t>
+          <t>Application closes in 81 days</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 31 days</t>
+          <t>Application closes in 30 days</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 14 days</t>
+          <t>Application closes in 13 days</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 45 days</t>
+          <t>Application closes in 44 days</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 45 days</t>
+          <t>Application closes in 44 days</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 15 days</t>
+          <t>Application closes in 14 days</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 4 days</t>
+          <t>Application closes in 3 days</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 46 days</t>
+          <t>Application closes in 45 days</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 9 days</t>
+          <t>Application closes in 8 days</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 30 days</t>
+          <t>Application closes in 29 days</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 4 days</t>
+          <t>Application closes in 3 days</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 29 days</t>
+          <t>Application closes in 28 days</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 30 days</t>
+          <t>Application closes in 29 days</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 13 days</t>
+          <t>Application closes in 12 days</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 45 days</t>
+          <t>Application closes in 44 days</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 15 days</t>
+          <t>Application closes in 14 days</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 90 days</t>
+          <t>Application closes in 89 days</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 45 days</t>
+          <t>Application closes in 44 days</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 30 days</t>
+          <t>Application closes in 29 days</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 56 days</t>
+          <t>Application closes in 55 days</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 29 days</t>
+          <t>Application closes in 28 days</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 81 days</t>
+          <t>Application closes in 80 days</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 30 days</t>
+          <t>Application closes in 29 days</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 13 days</t>
+          <t>Application closes in 12 days</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 44 days</t>
+          <t>Application closes in 43 days</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 44 days</t>
+          <t>Application closes in 43 days</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 14 days</t>
+          <t>Application closes in 13 days</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 3 days</t>
+          <t>Application closes in 2 days</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 45 days</t>
+          <t>Application closes in 44 days</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 8 days</t>
+          <t>Application closes in 7 days</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 29 days</t>
+          <t>Application closes in 28 days</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 3 days</t>
+          <t>Application closes in 2 days</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 28 days</t>
+          <t>Application closes in 27 days</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 29 days</t>
+          <t>Application closes in 28 days</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 12 days</t>
+          <t>Application closes in 11 days</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 44 days</t>
+          <t>Application closes in 43 days</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 14 days</t>
+          <t>Application closes in 13 days</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 89 days</t>
+          <t>Application closes in 88 days</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 44 days</t>
+          <t>Application closes in 43 days</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 29 days</t>
+          <t>Application closes in 28 days</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 55 days</t>
+          <t>Application closes in 54 days</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 28 days</t>
+          <t>Application closes in 27 days</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 80 days</t>
+          <t>Application closes in 79 days</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 29 days</t>
+          <t>Application closes in 28 days</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 12 days</t>
+          <t>Application closes in 11 days</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 43 days</t>
+          <t>Application closes in 42 days</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 43 days</t>
+          <t>Application closes in 42 days</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 13 days</t>
+          <t>Application closes in 12 days</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 2 days</t>
+          <t>Application closes in 1 day</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 44 days</t>
+          <t>Application closes in 43 days</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 7 days</t>
+          <t>Application closes in 6 days</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 28 days</t>
+          <t>Application closes in 27 days</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 2 days</t>
+          <t>Application closes in 1 day</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Commonwealth Master’s Scholarships 2027/2028 (Fully-funded)</t>
+          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/commonwealth-masters-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -1785,34 +1785,34 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
+          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
         </is>
       </c>
     </row>
@@ -1824,22 +1824,22 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
+          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Application closes in 43 days</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
         </is>
       </c>
     </row>
@@ -1851,22 +1851,22 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
+          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 43 days</t>
+          <t>Application closes in 6 days</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
+          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
         </is>
       </c>
     </row>
@@ -1878,22 +1878,22 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
+          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 6 days</t>
+          <t>Application closes in 27 days</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
         </is>
       </c>
     </row>
@@ -1905,22 +1905,22 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
+          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 27 days</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
         </is>
       </c>
     </row>
@@ -1932,22 +1932,22 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Application closes in 1 day</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
@@ -1959,22 +1959,22 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 1 day</t>
+          <t>Always Open</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
         </is>
       </c>
     </row>
@@ -1986,12 +1986,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
@@ -2013,22 +2013,22 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Always Open</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
         </is>
       </c>
     </row>
@@ -2040,22 +2040,22 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
+          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
+          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
+          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
+          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
+          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
+          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
+          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
+          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
+          <t>KAS Scholarships in Germany 2026 for Master’s, PhD, and International Students</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
+          <t>https://www.for9a.com/en/opportunity/kas-scholarships-in-germany-2026-for-masters-phd-and-international-students</t>
         </is>
       </c>
     </row>
@@ -2175,12 +2175,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>KAS Scholarships in Germany 2026 for Master’s, PhD, and International Students</t>
+          <t>Fully Funded Scholarship in Azerbaijan for 2026-2027</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/kas-scholarships-in-germany-2026-for-masters-phd-and-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-scholarship-in-azerbaijan-for-2026-2027</t>
         </is>
       </c>
     </row>
@@ -2202,22 +2202,22 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Scholarship in Azerbaijan for 2026-2027</t>
+          <t>Toronto Metropolitan University Global Migration Institute Scholarships 2027-2028</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-scholarship-in-azerbaijan-for-2026-2027</t>
+          <t>https://opportunitydesk.org/2026/10/15/tmu-global-migration-institute-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Toronto Metropolitan University Global Migration Institute Scholarships 2027-2028</t>
+          <t>France Excellence Eiffel Scholarship Program 2026-2027</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/15/tmu-global-migration-institute-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/10/14/france-excellence-eiffel-scholarship-program-2026-2027/</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>France Excellence Eiffel Scholarship Program 2026-2027</t>
+          <t>AHRC Doctoral Landscape Award at the University of Sheffield 2027/2028</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/14/france-excellence-eiffel-scholarship-program-2026-2027/</t>
+          <t>https://opportunitydesk.org/2026/10/01/ahrc-doctoral-landscape-award-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>AHRC Doctoral Landscape Award at the University of Sheffield 2027/2028</t>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/ahrc-doctoral-landscape-award-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Commonwealth PhD Scholarships 2027/2028 (Fully-Funded)</t>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/commonwealth-phd-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+          <t>Glendon Chase McCormick Scholarship 2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Glendon Chase McCormick Scholarship 2026</t>
+          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
+          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
+          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -2513,60 +2513,6 @@
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
         </is>

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Toronto Metropolitan University Global Migration Institute Scholarships 2027-2028</t>
+          <t>Swedish Institute (SI) Scholarship for Global Professionals 2027 (Fully-funded)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/15/tmu-global-migration-institute-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/10/22/si-scholarship-for-global-professionals-2027/</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>France Excellence Eiffel Scholarship Program 2026-2027</t>
+          <t>Toronto Metropolitan University Global Migration Institute Scholarships 2027-2028</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/14/france-excellence-eiffel-scholarship-program-2026-2027/</t>
+          <t>https://opportunitydesk.org/2026/10/15/tmu-global-migration-institute-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>University of Global Health Equity Master of Science in Health Professions Education Program (MSc-HPE) 2027</t>
+          <t>France Excellence Eiffel Scholarship Program 2026-2027</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/07/university-of-global-health-equity-master-of-science-in-health-professions-education-program-2027/</t>
+          <t>https://opportunitydesk.org/2026/10/14/france-excellence-eiffel-scholarship-program-2026-2027/</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
+          <t>University of Global Health Equity Master of Science in Health Professions Education Program (MSc-HPE) 2027</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
+          <t>https://opportunitydesk.org/2026/10/07/university-of-global-health-equity-master-of-science-in-health-professions-education-program-2027/</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
+          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
+          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
+          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
+          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -1785,34 +1785,34 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
+          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
+          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
         </is>
       </c>
     </row>
@@ -1824,22 +1824,22 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
+          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 43 days</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
         </is>
       </c>
     </row>
@@ -1851,22 +1851,22 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
+          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 6 days</t>
+          <t>Application closes in 43 days</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
         </is>
       </c>
     </row>
@@ -1878,22 +1878,22 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
+          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 27 days</t>
+          <t>Application closes in 6 days</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
+          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
         </is>
       </c>
     </row>
@@ -1905,22 +1905,22 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
+          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Application closes in 27 days</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
         </is>
       </c>
     </row>
@@ -1932,22 +1932,22 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 1 day</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
         </is>
       </c>
     </row>
@@ -1959,22 +1959,22 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Always Open</t>
+          <t>Application closes in 1 day</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
@@ -1986,12 +1986,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
         </is>
       </c>
     </row>
@@ -2013,22 +2013,22 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>Always Open</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
@@ -2040,22 +2040,22 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
+          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
+          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
+          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
+          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
+          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
+          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
+          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>KAS Scholarships in Germany 2026 for Master’s, PhD, and International Students</t>
+          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/kas-scholarships-in-germany-2026-for-masters-phd-and-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
         </is>
       </c>
     </row>
@@ -2175,12 +2175,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Scholarship in Azerbaijan for 2026-2027</t>
+          <t>KAS Scholarships in Germany 2026 for Master’s, PhD, and International Students</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-scholarship-in-azerbaijan-for-2026-2027</t>
+          <t>https://www.for9a.com/en/opportunity/kas-scholarships-in-germany-2026-for-masters-phd-and-international-students</t>
         </is>
       </c>
     </row>
@@ -2202,22 +2202,22 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Toronto Metropolitan University Global Migration Institute Scholarships 2027-2028</t>
+          <t>Fully Funded Scholarship in Azerbaijan for 2026-2027</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/15/tmu-global-migration-institute-scholarships-2027-2028/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-scholarship-in-azerbaijan-for-2026-2027</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>France Excellence Eiffel Scholarship Program 2026-2027</t>
+          <t>Toronto Metropolitan University Global Migration Institute Scholarships 2027-2028</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/14/france-excellence-eiffel-scholarship-program-2026-2027/</t>
+          <t>https://opportunitydesk.org/2026/10/15/tmu-global-migration-institute-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>AHRC Doctoral Landscape Award at the University of Sheffield 2027/2028</t>
+          <t>France Excellence Eiffel Scholarship Program 2026-2027</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/ahrc-doctoral-landscape-award-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/10/14/france-excellence-eiffel-scholarship-program-2026-2027/</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
+          <t>AHRC Doctoral Landscape Award at the University of Sheffield 2027/2028</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
+          <t>https://opportunitydesk.org/2026/10/01/ahrc-doctoral-landscape-award-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Glendon Chase McCormick Scholarship 2026</t>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
+          <t>Glendon Chase McCormick Scholarship 2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
+          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
+          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
+          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
         </is>
       </c>
     </row>
@@ -2499,20 +2499,47 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
+          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
         </is>

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>University of Global Health Equity Master of Science in Health Professions Education Program (MSc-HPE) 2027</t>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/07/university-of-global-health-equity-master-of-science-in-health-professions-education-program-2027/</t>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
+          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
+          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
+          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
+          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
+          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
+          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -1785,34 +1785,34 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
+          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
         </is>
       </c>
     </row>
@@ -1824,22 +1824,22 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
+          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Application closes in 43 days</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
         </is>
       </c>
     </row>
@@ -1851,22 +1851,22 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
+          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 43 days</t>
+          <t>Application closes in 6 days</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
+          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
         </is>
       </c>
     </row>
@@ -1878,22 +1878,22 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
+          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 6 days</t>
+          <t>Application closes in 27 days</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
         </is>
       </c>
     </row>
@@ -1905,22 +1905,22 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
+          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 27 days</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
         </is>
       </c>
     </row>
@@ -1932,22 +1932,22 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Application closes in 1 day</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
@@ -1959,22 +1959,22 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 1 day</t>
+          <t>Always Open</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
         </is>
       </c>
     </row>
@@ -1986,12 +1986,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
@@ -2013,22 +2013,22 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Always Open</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
         </is>
       </c>
     </row>
@@ -2040,22 +2040,22 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
+          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
+          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
+          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
+          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
+          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
+          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
+          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
+          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
+          <t>KAS Scholarships in Germany 2026 for Master’s, PhD, and International Students</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
+          <t>https://www.for9a.com/en/opportunity/kas-scholarships-in-germany-2026-for-masters-phd-and-international-students</t>
         </is>
       </c>
     </row>
@@ -2175,12 +2175,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>KAS Scholarships in Germany 2026 for Master’s, PhD, and International Students</t>
+          <t>Fully Funded Scholarship in Azerbaijan for 2026-2027</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/kas-scholarships-in-germany-2026-for-masters-phd-and-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-scholarship-in-azerbaijan-for-2026-2027</t>
         </is>
       </c>
     </row>
@@ -2202,22 +2202,22 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Scholarship in Azerbaijan for 2026-2027</t>
+          <t>Toronto Metropolitan University Global Migration Institute Scholarships 2027-2028</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-scholarship-in-azerbaijan-for-2026-2027</t>
+          <t>https://opportunitydesk.org/2026/10/15/tmu-global-migration-institute-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Toronto Metropolitan University Global Migration Institute Scholarships 2027-2028</t>
+          <t>France Excellence Eiffel Scholarship Program 2026-2027</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/15/tmu-global-migration-institute-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/10/14/france-excellence-eiffel-scholarship-program-2026-2027/</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>France Excellence Eiffel Scholarship Program 2026-2027</t>
+          <t>AHRC Doctoral Landscape Award at the University of Sheffield 2027/2028</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/14/france-excellence-eiffel-scholarship-program-2026-2027/</t>
+          <t>https://opportunitydesk.org/2026/10/01/ahrc-doctoral-landscape-award-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>AHRC Doctoral Landscape Award at the University of Sheffield 2027/2028</t>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/ahrc-doctoral-landscape-award-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+          <t>Glendon Chase McCormick Scholarship 2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Glendon Chase McCormick Scholarship 2026</t>
+          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
+          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
+          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
+          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
+          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -2513,33 +2513,6 @@
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>phd</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
         </is>

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -879,7 +879,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation Scholars Program at the University of Rwanda 2026/2027 (Fully-funded)</t>
+          <t>Science, Mathematics, and Research for Transformation (SMART) Scholarship-for-Service Program 2027/2028</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/mastercard-foundation-scholars-program-at-the-university-of-rwanda-2026-2027/</t>
+          <t>https://opportunitydesk.org/2026/10/28/smart-scholarship-for-service-program-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SHE-CAN Scholar Program 2026-2027 (Funded)</t>
+          <t>Mastercard Foundation Scholars Program at the University of Rwanda 2026/2027 (Fully-funded)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/she-can-scholar-program-2026-2027/</t>
+          <t>https://opportunitydesk.org/2026/10/01/mastercard-foundation-scholars-program-at-the-university-of-rwanda-2026-2027/</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Girls On Campus She Leads Scholarship 2026 (up to $1,500)</t>
+          <t>SHE-CAN Scholar Program 2026-2027 (Funded)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/27/girls-on-campus-she-leads-scholarship-2026/</t>
+          <t>https://opportunitydesk.org/2026/07/28/she-can-scholar-program-2026-2027/</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>50 Scholarships, Grants and Global Opportunities With Deadline Fast Approaching  – February 24, 2026</t>
+          <t>Girls On Campus She Leads Scholarship 2026 (up to $1,500)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -975,34 +975,34 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/02/24/50-scholarships-grants-and-global-opportunities-with-deadline-fast-approaching-february-24-2026/</t>
+          <t>https://opportunitydesk.org/2026/07/27/girls-on-campus-she-leads-scholarship-2026/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD Fellowship at New York University 2026 in Artificial Intelligence and Computer Science</t>
+          <t>50 Scholarships, Grants and Global Opportunities With Deadline Fast Approaching  – February 24, 2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 54 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/nyuad-global-phd-student-fellowship-for-computer-science-2026</t>
+          <t>https://opportunitydesk.org/2026/02/24/50-scholarships-grants-and-global-opportunities-with-deadline-fast-approaching-february-24-2026/</t>
         </is>
       </c>
     </row>
@@ -1014,22 +1014,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>University of Oregon Scholarship 2027 for Undergraduate and Master’s Students with Funding of Up to US$5,000</t>
+          <t>Fully Funded PhD Fellowship at New York University 2026 in Artificial Intelligence and Computer Science</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 27 days</t>
+          <t>Application closes in 54 days</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-study-abroad-scholarship</t>
+          <t>https://www.for9a.com/en/opportunity/nyuad-global-phd-student-fellowship-for-computer-science-2026</t>
         </is>
       </c>
     </row>
@@ -1041,22 +1041,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
+          <t>University of Oregon Scholarship 2027 for Undergraduate and Master’s Students with Funding of Up to US$5,000</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Application closes in 27 days</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-study-abroad-scholarship</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Master’s Opportunity at the University of Cambridge 2027 with Funding of Up to GBP 70,000</t>
+          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 79 days</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-opportunity-at-the-university-of-cambridge-2027-with-funding-of-up-to-gbp-70000</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
         </is>
       </c>
     </row>
@@ -1095,22 +1095,22 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>University of Sydney Scholarship for International Students to Pursue Bachelor’s and Master’s Studies with Funding of Up to AUD 60,000</t>
+          <t>Fully Funded Master’s Opportunity at the University of Cambridge 2027 with Funding of Up to GBP 70,000</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 28 days</t>
+          <t>Application closes in 79 days</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-sydney-scholarship-for-international-students-to-pursue-bachelors-and-masters-studies-with-funding-of-up-to-aud-60000</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-opportunity-at-the-university-of-cambridge-2027-with-funding-of-up-to-gbp-70000</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Funded UNSW Scholarship in Australia for Undergraduate and Master’s Studies</t>
+          <t>University of Sydney Scholarship for International Students to Pursue Bachelor’s and Master’s Studies with Funding of Up to AUD 60,000</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 11 days</t>
+          <t>Application closes in 28 days</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-unsw-scholarship-australia-undergraduate-masters-studies</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-sydney-scholarship-for-international-students-to-pursue-bachelors-and-masters-studies-with-funding-of-up-to-aud-60000</t>
         </is>
       </c>
     </row>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Master’s Scholarship at Peking University 2027 for International Students</t>
+          <t>Funded UNSW Scholarship in Australia for Undergraduate and Master’s Studies</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 42 days</t>
+          <t>Application closes in 11 days</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-scholarship-at-peking-university-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/funded-unsw-scholarship-australia-undergraduate-masters-studies</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Partially Funded Master’s Scholarship in Australia Worth AUD 20,000 for International Students</t>
+          <t>Fully Funded Master’s Scholarship at Peking University 2027 for International Students</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/partially-funded-masters-scholarship-in-australia-worth-aud-20000</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-masters-scholarship-at-peking-university-international-students</t>
         </is>
       </c>
     </row>
@@ -1203,22 +1203,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s in Canada at the University of Waterloo in Artificial Intelligence and Cybersecurity for International Students</t>
+          <t>Partially Funded Master’s Scholarship in Australia Worth AUD 20,000 for International Students</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Application closes in 42 days</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-in-canada-at-the-university-of-waterloo-in-artificial-intelligence-and-cybersecurity-for-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/partially-funded-masters-scholarship-in-australia-worth-aud-20000</t>
         </is>
       </c>
     </row>
@@ -1230,22 +1230,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Al Akhawayn University Scholarship for International Students 2027 to Pursue a Master’s Degree in Morocco</t>
+          <t>Funded Master’s in Canada at the University of Waterloo in Artificial Intelligence and Cybersecurity for International Students</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 12 days</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/al-akhawayn-university-scholarship-for-international-students-pursue-masters-degree-in-morocco</t>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-in-canada-at-the-university-of-waterloo-in-artificial-intelligence-and-cybersecurity-for-international-students</t>
         </is>
       </c>
     </row>
@@ -1257,22 +1257,22 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>Al Akhawayn University Scholarship for International Students 2027 to Pursue a Master’s Degree in Morocco</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 1 day</t>
+          <t>Application closes in 12 days</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>https://www.for9a.com/en/opportunity/al-akhawayn-university-scholarship-for-international-students-pursue-masters-degree-in-morocco</t>
         </is>
       </c>
     </row>
@@ -1284,22 +1284,22 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Kolding School of Design Scholarship 2027 for a Master’s in Design in Denmark</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>Application closes in 1 day</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/kolding-school-of-design-scholarship-for-a-masters-in-design-in-denmark-bwlon</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>IT University of Copenhagen Scholarship 2027 for Master’s Study in Denmark</t>
+          <t>Kolding School of Design Scholarship 2027 for a Master’s in Design in Denmark</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/it-university-of-copenhagen-scholarship-2027-for-masters-study-in-denmark</t>
+          <t>https://www.for9a.com/en/opportunity/kolding-school-of-design-scholarship-for-a-masters-in-design-in-denmark-bwlon</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Erasmus Mundus CYBERSURE Scholarship 2027 for a Master’s in Cybersecurity with a EUR 1,400 Monthly Stipend</t>
+          <t>IT University of Copenhagen Scholarship 2027 for Master’s Study in Denmark</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/erasmus-mundus-cybersure-scholarship-a-masters-in-cybersecurity-with-monthly-stipend</t>
+          <t>https://www.for9a.com/en/opportunity/it-university-of-copenhagen-scholarship-2027-for-masters-study-in-denmark</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>Erasmus Mundus CYBERSURE Scholarship 2027 for a Master’s in Cybersecurity with a EUR 1,400 Monthly Stipend</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Always Open</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>https://www.for9a.com/en/opportunity/erasmus-mundus-cybersure-scholarship-a-masters-in-cybersecurity-with-monthly-stipend</t>
         </is>
       </c>
     </row>
@@ -1392,22 +1392,22 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Swedish Institute (SI) Scholarship for Global Professionals 2027 (Fully-funded)</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Always Open</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/22/si-scholarship-for-global-professionals-2027/</t>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Toronto Metropolitan University Global Migration Institute Scholarships 2027-2028</t>
+          <t>Science, Mathematics, and Research for Transformation (SMART) Scholarship-for-Service Program 2027/2028</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/15/tmu-global-migration-institute-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/10/28/smart-scholarship-for-service-program-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>France Excellence Eiffel Scholarship Program 2026-2027</t>
+          <t>Swedish Institute (SI) Scholarship for Global Professionals 2027 (Fully-funded)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/14/france-excellence-eiffel-scholarship-program-2026-2027/</t>
+          <t>https://opportunitydesk.org/2026/10/22/si-scholarship-for-global-professionals-2027/</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
+          <t>Toronto Metropolitan University Global Migration Institute Scholarships 2027-2028</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
+          <t>https://opportunitydesk.org/2026/10/15/tmu-global-migration-institute-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
+          <t>France Excellence Eiffel Scholarship Program 2026-2027</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
+          <t>https://opportunitydesk.org/2026/10/14/france-excellence-eiffel-scholarship-program-2026-2027/</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
+          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
+          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
+          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
+          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
+          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
+          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -1785,61 +1785,61 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>master</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
+          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 43 days</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
+          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
         </is>
       </c>
     </row>
@@ -1851,22 +1851,22 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
+          <t>Fully Funded University of Cambridge Scholarship in the UK for Master’s and PhD Studies</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 6 days</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-university-of-cambridge-scholarship-for-masters-and-phd-studies</t>
         </is>
       </c>
     </row>
@@ -1878,22 +1878,22 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
+          <t>Fully Funded PhD in Cancer Sciences at McGill University in Canada</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 27 days</t>
+          <t>Application closes in 43 days</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-cancer-sciences-mcgill-university-canada</t>
         </is>
       </c>
     </row>
@@ -1905,22 +1905,22 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
+          <t>Funded PhD Scholarship at the University of Melbourne in Australia Worth Up to AUD 140,000</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Application closes in 6 days</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
+          <t>https://www.for9a.com/en/opportunity/funded-phd-scholarship-at-the-university-of-melbourne-in-australia-worth-up-to-aud-140000</t>
         </is>
       </c>
     </row>
@@ -1932,22 +1932,22 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
+          <t>Fully Funded PhD Scholarship in Japan 2027 at OIST</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Application closes in 1 day</t>
+          <t>Application closes in 27 days</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-scholarship-in-japan-2027-at-oist</t>
         </is>
       </c>
     </row>
@@ -1959,22 +1959,22 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
+          <t>Fully Funded PhD in Computer Science at the University of Waterloo in Canada 2027</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Always Open</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-phd-in-computer-science-at-the-university-of-waterloo-in-canada-2027</t>
         </is>
       </c>
     </row>
@@ -1986,22 +1986,22 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
+          <t>University of Queensland Scholarship 2027 in Australia for Master’s and PhD Programs with Full Funding</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Always Open</t>
+          <t>Application closes in 1 day</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
+          <t>https://www.for9a.com/en/opportunity/university-of-queensland-scholarship-2027-for-masters-and-phd-programs-with-full-funding</t>
         </is>
       </c>
     </row>
@@ -2013,22 +2013,22 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
+          <t>University of Auckland Doctoral Scholarship 2026 for PhD Study in New Zealand</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>Always Open</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
+          <t>https://www.for9a.com/en/opportunity/new-zealand-phd-scholarship</t>
         </is>
       </c>
     </row>
@@ -2040,22 +2040,22 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
+          <t>Multimedia University Scholarship 2026 for International Students in Malaysia</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Always Open</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
+          <t>https://www.for9a.com/en/opportunity/multimedia-university-scholarship-for-international-students-malaysia</t>
         </is>
       </c>
     </row>
@@ -2067,12 +2067,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
+          <t>Funded Master’s and PhD Scholarships for Arab Students in the Netherlands  Up to €15,000</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
+          <t>https://www.for9a.com/en/opportunity/funded-masters-and-phd-scholarships-for-arab-students-in-the-netherlands-up-to-15000</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
+          <t>Friedrich Naumann Scholarship in Germany 2026 for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
+          <t>https://www.for9a.com/en/opportunity/friedrich-naumann-scholarship-in-germany-2026-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
+          <t>Funded Rosa Luxemburg Foundation Scholarship in Germany for Master’s and PhD Students</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Open Now</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
+          <t>https://www.for9a.com/en/opportunity/funded-rosa-luxemburg-foundation-scholarship-in-germany-for-masters-and-phd-students</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>KAS Scholarships in Germany 2026 for Master’s, PhD, and International Students</t>
+          <t>FES Scholarship in Germany 2026 with Monthly Funding for Students and Doctoral Candidates</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/kas-scholarships-in-germany-2026-for-masters-phd-and-international-students</t>
+          <t>https://www.for9a.com/en/opportunity/fes-scholarship-in-germany-2026-with-monthly-funding-for-students-and-doctoral-candidates</t>
         </is>
       </c>
     </row>
@@ -2175,22 +2175,22 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Fully Funded Scholarship in Azerbaijan for 2026-2027</t>
+          <t>Heinrich Böll Foundation Scholarship 2026 for Master’s and PhD Study in Germany</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>Open Now</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.for9a.com/en/opportunity/fully-funded-scholarship-in-azerbaijan-for-2026-2027</t>
+          <t>https://www.for9a.com/en/opportunity/heinrich-b%C3%B6ll-foundation-scholarship-2026-for-masters-and-phd-study-in-germany</t>
         </is>
       </c>
     </row>
@@ -2202,22 +2202,22 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Toronto Metropolitan University Global Migration Institute Scholarships 2027-2028</t>
+          <t>KAS Scholarships in Germany 2026 for Master’s, PhD, and International Students</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/15/tmu-global-migration-institute-scholarships-2027-2028/</t>
+          <t>https://www.for9a.com/en/opportunity/kas-scholarships-in-germany-2026-for-masters-phd-and-international-students</t>
         </is>
       </c>
     </row>
@@ -2229,22 +2229,22 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>France Excellence Eiffel Scholarship Program 2026-2027</t>
+          <t>Fully Funded Scholarship in Azerbaijan for 2026-2027</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Coming Soon</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/14/france-excellence-eiffel-scholarship-program-2026-2027/</t>
+          <t>https://www.for9a.com/en/opportunity/fully-funded-scholarship-in-azerbaijan-for-2026-2027</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>AHRC Doctoral Landscape Award at the University of Sheffield 2027/2028</t>
+          <t>Science, Mathematics, and Research for Transformation (SMART) Scholarship-for-Service Program 2027/2028</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/ahrc-doctoral-landscape-award-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/10/28/smart-scholarship-for-service-program-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
+          <t>AHRC Doctoral Landscape Scholarship Awards at Birmingham City University 2027</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
+          <t>https://opportunitydesk.org/2026/10/28/ahrc-doctoral-landscape-awards-at-birmingham-city-university-2027/</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
+          <t>Toronto Metropolitan University Global Migration Institute Scholarships 2027-2028</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
+          <t>https://opportunitydesk.org/2026/10/15/tmu-global-migration-institute-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+          <t>France Excellence Eiffel Scholarship Program 2026-2027</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/10/14/france-excellence-eiffel-scholarship-program-2026-2027/</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+          <t>AHRC Doctoral Landscape Award at the University of Sheffield 2027/2028</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+          <t>https://opportunitydesk.org/2026/10/01/ahrc-doctoral-landscape-award-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Glendon Chase McCormick Scholarship 2026</t>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>33 Fully Funded Scholarships, Grants, Fellowships and More Currently Open  – March 30, 2026</t>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -2514,7 +2514,88 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/03/30/33-fully-funded-scholarships-grants-fellowships-and-more-currently-open-march-30-2026/</t>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Glendon Chase McCormick Scholarship 2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/06/17/glendon-chase-mccormick-scholarship-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>10 Scholarship and Study Abroad Opportunities Currently Open – May 30, 2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/05/30/10-scholarship-study-abroad-opportunities-currently-open-may-30-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>137 Grants, Scholarships, Travel Abroad Opportunities Closing in May – May 2, 2026</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>https://opportunitydesk.org/2026/05/01/137-grants-scholarships-travel-abroad-opportunities-closing-in-may-may-2-2026/</t>
         </is>
       </c>
     </row>

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -1419,7 +1419,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Science, Mathematics, and Research for Transformation (SMART) Scholarship-for-Service Program 2027/2028</t>
+          <t>Columbia HBCU Fellowship Program Fall 2027</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/28/smart-scholarship-for-service-program-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/10/29/columbia-hbcu-fellowship-program-fall-2027/</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Swedish Institute (SI) Scholarship for Global Professionals 2027 (Fully-funded)</t>
+          <t>Science, Mathematics, and Research for Transformation (SMART) Scholarship-for-Service Program 2027/2028</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/22/si-scholarship-for-global-professionals-2027/</t>
+          <t>https://opportunitydesk.org/2026/10/28/smart-scholarship-for-service-program-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Toronto Metropolitan University Global Migration Institute Scholarships 2027-2028</t>
+          <t>Swedish Institute (SI) Scholarship for Global Professionals 2027 (Fully-funded)</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/15/tmu-global-migration-institute-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/10/22/si-scholarship-for-global-professionals-2027/</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>France Excellence Eiffel Scholarship Program 2026-2027</t>
+          <t>Toronto Metropolitan University Global Migration Institute Scholarships 2027-2028</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/14/france-excellence-eiffel-scholarship-program-2026-2027/</t>
+          <t>https://opportunitydesk.org/2026/10/15/tmu-global-migration-institute-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
+          <t>France Excellence Eiffel Scholarship Program 2026-2027</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
+          <t>https://opportunitydesk.org/2026/10/14/france-excellence-eiffel-scholarship-program-2026-2027/</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
+          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
+          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
+          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
+          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
         </is>
       </c>
     </row>

--- a/scholarships.xlsx
+++ b/scholarships.xlsx
@@ -1419,7 +1419,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Columbia HBCU Fellowship Program Fall 2027</t>
+          <t>Science, Mathematics, and Research for Transformation (SMART) Scholarship-for-Service Program 2027/2028</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/29/columbia-hbcu-fellowship-program-fall-2027/</t>
+          <t>https://opportunitydesk.org/2026/10/28/smart-scholarship-for-service-program-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Science, Mathematics, and Research for Transformation (SMART) Scholarship-for-Service Program 2027/2028</t>
+          <t>Swedish Institute (SI) Scholarship for Global Professionals 2027 (Fully-funded)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/28/smart-scholarship-for-service-program-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/10/22/si-scholarship-for-global-professionals-2027/</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Swedish Institute (SI) Scholarship for Global Professionals 2027 (Fully-funded)</t>
+          <t>Toronto Metropolitan University Global Migration Institute Scholarships 2027-2028</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/22/si-scholarship-for-global-professionals-2027/</t>
+          <t>https://opportunitydesk.org/2026/10/15/tmu-global-migration-institute-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Toronto Metropolitan University Global Migration Institute Scholarships 2027-2028</t>
+          <t>France Excellence Eiffel Scholarship Program 2026-2027</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/15/tmu-global-migration-institute-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/10/14/france-excellence-eiffel-scholarship-program-2026-2027/</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>France Excellence Eiffel Scholarship Program 2026-2027</t>
+          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/14/france-excellence-eiffel-scholarship-program-2026-2027/</t>
+          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>69 Master’s and PhD Scholarships and Fellowships You Can Apply for Now – October 1, 2026</t>
+          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/10/01/69-masters-phd-scholarships-and-fellowships-you-can-apply-for-now-october-1-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Planning to Study Abroad? Prepare These 22 Essential Documents Before Applications Open</t>
+          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/30/planning-to-study-abroad-prepare-these-22-essential-documents-before-applications-open/</t>
+          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Maria Rosario Lazzati Niada Scholarship for Afghan Women 2027-2028</t>
+          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/29/maria-rosario-lazzati-niada-scholarship-for-afghan-women-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>30 Masters, Ph.D and Other Scholarship Opportunities  Currently Open –  September 16, 2026</t>
+          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/16/30-masters-ph-d-and-other-scholarship-opportunities-currently-open-september-16-2026/</t>
+          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Yenching Academy at Peking University 2027 – Full Scholarship for Master’s Study in China</t>
+          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/09/yenching-academy-at-peking-university-2027-scholarship/</t>
+          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation Scholarships: What Sets the Programme Apart, Who Can Apply and How to Get Started</t>
+          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/06/mastercard-foundation-scholarships-what-sets-the-programme-apart-who-can-apply-and-how-to-get-started/</t>
+          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Swiss Government Excellence Scholarships 2027-2028 for Foreign Scholars &amp; Artists</t>
+          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/09/02/swiss-government-excellence-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Asian Development Bank-Japan Scholarship Program 2026</t>
+          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/26/asian-development-bank-japan-scholarship-program-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>12 Study Abroad Scholarship Opportunities Currently Open – August 18, 2026</t>
+          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/18/12-study-abroad-scholarship-opportunities-currently-open-august-18-2026/</t>
+          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Mastercard Foundation AfOx Graduate Scholarships 2027-2028</t>
+          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/08/11/mastercard-foundation-afox-graduate-scholarships-2027-2028/</t>
+          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>17 Scholarships, Study Abroad Opportunities  and Competitions Closing in August 2026 – July 28, 2026</t>
+          <t>13 Global Scholarships and Fellowships Currently Open – July 9, 2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://opportunitydesk.org/2026/07/28/17-scholarships-study-abroad-opportunities-and-competitions-closing-in-august-2026-july-28-2026/</t>
+          <t>https://opportunitydesk.org/2026/07/09/13-global-scholarships-and-fellowships-currently-open-july-9-2026/</t>
         </is>
       </c>
     </row>
